--- a/Week_7/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_7/Capstone Timesheet_Ripal Patel.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\HealthCare Plus\Week_7\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId5"/>
+    <sheet name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
   <si>
     <t>Week_1</t>
   </si>
@@ -186,61 +194,70 @@
   <si>
     <t>Worked on homepage UI improvements including navbar hover effects, updated Register button to primary blue, refined hero section layout and styling, adjusted text colors, and improved overall visual clarity.</t>
   </si>
+  <si>
+    <t>Completed Home page (Services section)</t>
+  </si>
+  <si>
+    <t>Completed Home page (Hero section)</t>
+  </si>
+  <si>
+    <t>Completed Home page (Footer section)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd-mmm"/>
-    <numFmt numFmtId="165" formatCode="d-mmm"/>
+    <numFmt numFmtId="164" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="165" formatCode="d\-mmm"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -250,7 +267,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -314,7 +331,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -328,220 +351,200 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="67">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="2" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="165" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,7 +552,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -739,23 +742,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AA954"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="62.25"/>
-    <col customWidth="1" min="3" max="3" width="12.25"/>
-    <col customWidth="1" min="4" max="4" width="12.13"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="62.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,13 +798,13 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D2" s="6">
         <v>1.3</v>
@@ -827,13 +833,13 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D3" s="6">
         <v>0.15</v>
@@ -862,16 +868,16 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D4" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -897,16 +903,16 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5">
-        <v>46037.0</v>
+        <v>46037</v>
       </c>
       <c r="D5" s="4">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -932,13 +938,13 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="5">
-        <v>46038.0</v>
+        <v>46038</v>
       </c>
       <c r="D6" s="4">
         <v>4.75</v>
@@ -967,13 +973,13 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>46038.0</v>
+        <v>46038</v>
       </c>
       <c r="D7" s="4">
         <v>3.5</v>
@@ -1002,13 +1008,13 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="5">
-        <v>46038.0</v>
+        <v>46038</v>
       </c>
       <c r="D8" s="4">
         <v>5.75</v>
@@ -1037,16 +1043,16 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>46039.0</v>
+        <v>46039</v>
       </c>
       <c r="D9" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1072,13 +1078,13 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="5">
-        <v>46039.0</v>
+        <v>46039</v>
       </c>
       <c r="D10" s="4">
         <v>5.5</v>
@@ -1107,13 +1113,13 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>46041.0</v>
+        <v>46041</v>
       </c>
       <c r="D11" s="4">
         <v>4.75</v>
@@ -1142,13 +1148,13 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="5">
-        <v>46043.0</v>
+        <v>46043</v>
       </c>
       <c r="D12" s="4">
         <v>4.75</v>
@@ -1177,7 +1183,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1206,14 +1212,14 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="7">
-        <f>sum(D2:D12)</f>
+        <f>SUM(D2:D12)</f>
         <v>38.6</v>
       </c>
       <c r="E14" s="2"/>
@@ -1240,7 +1246,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1269,7 +1275,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1298,7 +1304,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
@@ -1335,13 +1341,13 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="12">
-        <v>46044.0</v>
+        <v>46044</v>
       </c>
       <c r="D18" s="13">
         <v>1.5</v>
@@ -1370,16 +1376,16 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="12">
-        <v>46044.0</v>
+        <v>46044</v>
       </c>
       <c r="D19" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1405,16 +1411,16 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="12">
-        <v>46044.0</v>
+        <v>46044</v>
       </c>
       <c r="D20" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1440,16 +1446,16 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="12">
-        <v>46045.0</v>
+        <v>46045</v>
       </c>
       <c r="D21" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1475,16 +1481,16 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="12">
-        <v>46045.0</v>
+        <v>46045</v>
       </c>
       <c r="D22" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1510,13 +1516,13 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="12">
-        <v>46046.0</v>
+        <v>46046</v>
       </c>
       <c r="D23" s="13">
         <v>1.5</v>
@@ -1545,13 +1551,13 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="12">
-        <v>46046.0</v>
+        <v>46046</v>
       </c>
       <c r="D24" s="13">
         <v>2.5</v>
@@ -1580,16 +1586,16 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="12">
-        <v>46046.0</v>
+        <v>46046</v>
       </c>
       <c r="D25" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1615,13 +1621,13 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="12">
-        <v>46047.0</v>
+        <v>46047</v>
       </c>
       <c r="D26" s="13">
         <v>1.75</v>
@@ -1650,16 +1656,16 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="12">
-        <v>46047.0</v>
+        <v>46047</v>
       </c>
       <c r="D27" s="13">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1685,13 +1691,13 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="12">
-        <v>46047.0</v>
+        <v>46047</v>
       </c>
       <c r="D28" s="13">
         <v>2.75</v>
@@ -1720,16 +1726,16 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="16">
-        <v>46048.0</v>
+        <v>46048</v>
       </c>
       <c r="D29" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1755,16 +1761,16 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="16">
-        <v>46048.0</v>
+        <v>46048</v>
       </c>
       <c r="D30" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1790,16 +1796,16 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="16">
-        <v>46048.0</v>
+        <v>46048</v>
       </c>
       <c r="D31" s="17">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1825,13 +1831,13 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="16">
-        <v>46049.0</v>
+        <v>46049</v>
       </c>
       <c r="D32" s="17">
         <v>2.5</v>
@@ -1860,13 +1866,13 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A33" s="14"/>
       <c r="B33" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="19">
-        <v>46049.0</v>
+        <v>46049</v>
       </c>
       <c r="D33" s="20">
         <v>3.75</v>
@@ -1895,14 +1901,14 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="21">
-        <f>sum(D18:D33)</f>
+        <f>SUM(D18:D33)</f>
         <v>33.4</v>
       </c>
       <c r="E34" s="2"/>
@@ -1929,7 +1935,7 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1958,7 +1964,7 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1987,7 +1993,7 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A37" s="23" t="s">
         <v>33</v>
       </c>
@@ -2024,13 +2030,13 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A38" s="24"/>
       <c r="B38" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="26">
-        <v>46052.0</v>
+        <v>46052</v>
       </c>
       <c r="D38" s="27">
         <v>1.5</v>
@@ -2059,13 +2065,13 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A39" s="24"/>
       <c r="B39" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="26">
-        <v>46052.0</v>
+        <v>46052</v>
       </c>
       <c r="D39" s="27">
         <v>1.75</v>
@@ -2094,13 +2100,13 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A40" s="24"/>
       <c r="B40" s="25" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="26">
-        <v>46052.0</v>
+        <v>46052</v>
       </c>
       <c r="D40" s="27">
         <v>2.15</v>
@@ -2129,13 +2135,13 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A41" s="24"/>
       <c r="B41" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="26">
-        <v>46054.0</v>
+        <v>46054</v>
       </c>
       <c r="D41" s="27">
         <v>2.75</v>
@@ -2164,13 +2170,13 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A42" s="24"/>
       <c r="B42" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="26">
-        <v>46055.0</v>
+        <v>46055</v>
       </c>
       <c r="D42" s="27">
         <v>3.75</v>
@@ -2199,7 +2205,7 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2228,14 +2234,14 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="24">
-        <f>sum(D38:D42)</f>
+        <f>SUM(D38:D42)</f>
         <v>11.9</v>
       </c>
       <c r="E44" s="3"/>
@@ -2262,7 +2268,7 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2291,7 +2297,7 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2320,7 +2326,7 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A47" s="31" t="s">
         <v>39</v>
       </c>
@@ -2357,13 +2363,13 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A48" s="32"/>
       <c r="B48" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="34">
-        <v>46059.0</v>
+        <v>46059</v>
       </c>
       <c r="D48" s="35">
         <v>3.75</v>
@@ -2392,13 +2398,13 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A49" s="32"/>
       <c r="B49" s="33" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="34">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="D49" s="35">
         <v>3.25</v>
@@ -2427,13 +2433,13 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A50" s="32"/>
       <c r="B50" s="33" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="34">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="D50" s="35">
         <v>4.5</v>
@@ -2462,13 +2468,13 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A51" s="32"/>
       <c r="B51" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="34">
-        <v>46062.0</v>
+        <v>46062</v>
       </c>
       <c r="D51" s="35">
         <v>3.75</v>
@@ -2497,13 +2503,13 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A52" s="32"/>
       <c r="B52" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="34">
-        <v>46063.0</v>
+        <v>46063</v>
       </c>
       <c r="D52" s="35">
         <v>3.5</v>
@@ -2532,7 +2538,7 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2561,14 +2567,14 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A54" s="36"/>
       <c r="B54" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="39">
-        <f>sum(D48:D52)</f>
+        <f>SUM(D48:D52)</f>
         <v>18.75</v>
       </c>
       <c r="E54" s="3"/>
@@ -2595,7 +2601,7 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2624,7 +2630,7 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2653,7 +2659,7 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A57" s="40" t="s">
         <v>45</v>
       </c>
@@ -2690,13 +2696,13 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A58" s="41"/>
       <c r="B58" s="42" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="43">
-        <v>46066.0</v>
+        <v>46066</v>
       </c>
       <c r="D58" s="44">
         <v>2.15</v>
@@ -2725,13 +2731,13 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A59" s="41"/>
       <c r="B59" s="42" t="s">
         <v>47</v>
       </c>
       <c r="C59" s="43">
-        <v>46066.0</v>
+        <v>46066</v>
       </c>
       <c r="D59" s="44">
         <v>3.75</v>
@@ -2760,13 +2766,13 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A60" s="41"/>
       <c r="B60" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="43">
-        <v>46069.0</v>
+        <v>46069</v>
       </c>
       <c r="D60" s="44">
         <v>3.5</v>
@@ -2795,13 +2801,13 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A61" s="41"/>
       <c r="B61" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="43">
-        <v>46069.0</v>
+        <v>46069</v>
       </c>
       <c r="D61" s="44">
         <v>2.5</v>
@@ -2830,7 +2836,7 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2859,14 +2865,14 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A63" s="45"/>
       <c r="B63" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="47"/>
       <c r="D63" s="41">
-        <f>sum(D58:D61)</f>
+        <f>SUM(D58:D61)</f>
         <v>11.9</v>
       </c>
       <c r="E63" s="3"/>
@@ -2893,7 +2899,7 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2922,7 +2928,7 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2951,7 +2957,7 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A66" s="48" t="s">
         <v>50</v>
       </c>
@@ -2988,13 +2994,13 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A67" s="49"/>
       <c r="B67" s="50" t="s">
         <v>51</v>
       </c>
       <c r="C67" s="51">
-        <v>46073.0</v>
+        <v>46073</v>
       </c>
       <c r="D67" s="52">
         <v>1.75</v>
@@ -3023,16 +3029,16 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A68" s="49"/>
       <c r="B68" s="50" t="s">
         <v>52</v>
       </c>
       <c r="C68" s="51">
-        <v>46074.0</v>
+        <v>46074</v>
       </c>
       <c r="D68" s="52">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
@@ -3057,13 +3063,13 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A69" s="49"/>
       <c r="B69" s="50" t="s">
         <v>53</v>
       </c>
       <c r="C69" s="51">
-        <v>46075.0</v>
+        <v>46075</v>
       </c>
       <c r="D69" s="52">
         <v>0.25</v>
@@ -3092,13 +3098,13 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A70" s="49"/>
       <c r="B70" s="50" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="51">
-        <v>46076.0</v>
+        <v>46076</v>
       </c>
       <c r="D70" s="52">
         <v>1.75</v>
@@ -3127,13 +3133,13 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:27" ht="62" x14ac:dyDescent="0.35">
       <c r="A71" s="49"/>
       <c r="B71" s="53" t="s">
         <v>55</v>
       </c>
       <c r="C71" s="51">
-        <v>46076.0</v>
+        <v>46076</v>
       </c>
       <c r="D71" s="52">
         <v>3.75</v>
@@ -3162,7 +3168,7 @@
       <c r="Z71" s="3"/>
       <c r="AA71" s="3"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3191,14 +3197,14 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A73" s="54"/>
       <c r="B73" s="55" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="56"/>
       <c r="D73" s="49">
-        <f>sum(D67:D71)</f>
+        <f>SUM(D67:D71)</f>
         <v>9.5</v>
       </c>
       <c r="E73" s="3"/>
@@ -3225,7 +3231,7 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3254,7 +3260,7 @@
       <c r="Z74" s="3"/>
       <c r="AA74" s="3"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3283,7 +3289,7 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A76" s="57" t="s">
         <v>56</v>
       </c>
@@ -3320,13 +3326,13 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:27" ht="62" x14ac:dyDescent="0.35">
       <c r="A77" s="58"/>
       <c r="B77" s="59" t="s">
         <v>57</v>
       </c>
       <c r="C77" s="60">
-        <v>46080.0</v>
+        <v>46080</v>
       </c>
       <c r="D77" s="61">
         <v>3.75</v>
@@ -3355,11 +3361,17 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A78" s="58"/>
-      <c r="B78" s="62"/>
-      <c r="C78" s="60"/>
-      <c r="D78" s="61"/>
+      <c r="B78" s="62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C78" s="60">
+        <v>46081</v>
+      </c>
+      <c r="D78" s="61">
+        <v>2</v>
+      </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -3384,11 +3396,17 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A79" s="58"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="60"/>
-      <c r="D79" s="61"/>
+      <c r="B79" s="62" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" s="60">
+        <v>46081</v>
+      </c>
+      <c r="D79" s="61">
+        <v>4</v>
+      </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -3413,10 +3431,14 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A80" s="58"/>
-      <c r="B80" s="62"/>
-      <c r="C80" s="60"/>
+      <c r="B80" s="62" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" s="60">
+        <v>46081</v>
+      </c>
       <c r="D80" s="61"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -3442,7 +3464,7 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A81" s="58"/>
       <c r="B81" s="59"/>
       <c r="C81" s="60"/>
@@ -3471,7 +3493,7 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A82" s="63"/>
       <c r="B82" s="63"/>
       <c r="C82" s="63"/>
@@ -3500,15 +3522,15 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A83" s="64"/>
       <c r="B83" s="65" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="66"/>
       <c r="D83" s="58">
-        <f>sum(D77:D81)</f>
-        <v>3.75</v>
+        <f>SUM(D77:D81)</f>
+        <v>9.75</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -3534,7 +3556,7 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3563,7 +3585,7 @@
       <c r="Z84" s="3"/>
       <c r="AA84" s="3"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3592,7 +3614,7 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3621,7 +3643,7 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3650,7 +3672,7 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3679,7 +3701,7 @@
       <c r="Z88" s="3"/>
       <c r="AA88" s="3"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3708,7 +3730,7 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3737,7 +3759,7 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3766,7 +3788,7 @@
       <c r="Z91" s="3"/>
       <c r="AA91" s="3"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3795,7 +3817,7 @@
       <c r="Z92" s="3"/>
       <c r="AA92" s="3"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3824,7 +3846,7 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3853,7 +3875,7 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3882,7 +3904,7 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3911,7 +3933,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3940,7 +3962,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3969,7 +3991,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3998,7 +4020,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4027,7 +4049,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4056,7 +4078,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4085,7 +4107,7 @@
       <c r="Z102" s="3"/>
       <c r="AA102" s="3"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4114,7 +4136,7 @@
       <c r="Z103" s="3"/>
       <c r="AA103" s="3"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4143,7 +4165,7 @@
       <c r="Z104" s="3"/>
       <c r="AA104" s="3"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4172,7 +4194,7 @@
       <c r="Z105" s="3"/>
       <c r="AA105" s="3"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4201,7 +4223,7 @@
       <c r="Z106" s="3"/>
       <c r="AA106" s="3"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4230,7 +4252,7 @@
       <c r="Z107" s="3"/>
       <c r="AA107" s="3"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4259,7 +4281,7 @@
       <c r="Z108" s="3"/>
       <c r="AA108" s="3"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4288,7 +4310,7 @@
       <c r="Z109" s="3"/>
       <c r="AA109" s="3"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4317,7 +4339,7 @@
       <c r="Z110" s="3"/>
       <c r="AA110" s="3"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4346,7 +4368,7 @@
       <c r="Z111" s="3"/>
       <c r="AA111" s="3"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4375,7 +4397,7 @@
       <c r="Z112" s="3"/>
       <c r="AA112" s="3"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4404,7 +4426,7 @@
       <c r="Z113" s="3"/>
       <c r="AA113" s="3"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4433,7 +4455,7 @@
       <c r="Z114" s="3"/>
       <c r="AA114" s="3"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4462,7 +4484,7 @@
       <c r="Z115" s="3"/>
       <c r="AA115" s="3"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4491,7 +4513,7 @@
       <c r="Z116" s="3"/>
       <c r="AA116" s="3"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4520,7 +4542,7 @@
       <c r="Z117" s="3"/>
       <c r="AA117" s="3"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4549,7 +4571,7 @@
       <c r="Z118" s="3"/>
       <c r="AA118" s="3"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4578,7 +4600,7 @@
       <c r="Z119" s="3"/>
       <c r="AA119" s="3"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4607,7 +4629,7 @@
       <c r="Z120" s="3"/>
       <c r="AA120" s="3"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4636,7 +4658,7 @@
       <c r="Z121" s="3"/>
       <c r="AA121" s="3"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4665,7 +4687,7 @@
       <c r="Z122" s="3"/>
       <c r="AA122" s="3"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4694,7 +4716,7 @@
       <c r="Z123" s="3"/>
       <c r="AA123" s="3"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4723,7 +4745,7 @@
       <c r="Z124" s="3"/>
       <c r="AA124" s="3"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4752,7 +4774,7 @@
       <c r="Z125" s="3"/>
       <c r="AA125" s="3"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4781,7 +4803,7 @@
       <c r="Z126" s="3"/>
       <c r="AA126" s="3"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4810,7 +4832,7 @@
       <c r="Z127" s="3"/>
       <c r="AA127" s="3"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4839,7 +4861,7 @@
       <c r="Z128" s="3"/>
       <c r="AA128" s="3"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4868,7 +4890,7 @@
       <c r="Z129" s="3"/>
       <c r="AA129" s="3"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4897,7 +4919,7 @@
       <c r="Z130" s="3"/>
       <c r="AA130" s="3"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4926,7 +4948,7 @@
       <c r="Z131" s="3"/>
       <c r="AA131" s="3"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4955,7 +4977,7 @@
       <c r="Z132" s="3"/>
       <c r="AA132" s="3"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -4984,7 +5006,7 @@
       <c r="Z133" s="3"/>
       <c r="AA133" s="3"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5013,7 +5035,7 @@
       <c r="Z134" s="3"/>
       <c r="AA134" s="3"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5042,7 +5064,7 @@
       <c r="Z135" s="3"/>
       <c r="AA135" s="3"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5071,7 +5093,7 @@
       <c r="Z136" s="3"/>
       <c r="AA136" s="3"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5100,7 +5122,7 @@
       <c r="Z137" s="3"/>
       <c r="AA137" s="3"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5129,7 +5151,7 @@
       <c r="Z138" s="3"/>
       <c r="AA138" s="3"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5158,7 +5180,7 @@
       <c r="Z139" s="3"/>
       <c r="AA139" s="3"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5187,7 +5209,7 @@
       <c r="Z140" s="3"/>
       <c r="AA140" s="3"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5216,7 +5238,7 @@
       <c r="Z141" s="3"/>
       <c r="AA141" s="3"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5245,7 +5267,7 @@
       <c r="Z142" s="3"/>
       <c r="AA142" s="3"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5274,7 +5296,7 @@
       <c r="Z143" s="3"/>
       <c r="AA143" s="3"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5303,7 +5325,7 @@
       <c r="Z144" s="3"/>
       <c r="AA144" s="3"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5332,7 +5354,7 @@
       <c r="Z145" s="3"/>
       <c r="AA145" s="3"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5361,7 +5383,7 @@
       <c r="Z146" s="3"/>
       <c r="AA146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5390,7 +5412,7 @@
       <c r="Z147" s="3"/>
       <c r="AA147" s="3"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5419,7 +5441,7 @@
       <c r="Z148" s="3"/>
       <c r="AA148" s="3"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5448,7 +5470,7 @@
       <c r="Z149" s="3"/>
       <c r="AA149" s="3"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5477,7 +5499,7 @@
       <c r="Z150" s="3"/>
       <c r="AA150" s="3"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5506,7 +5528,7 @@
       <c r="Z151" s="3"/>
       <c r="AA151" s="3"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5535,7 +5557,7 @@
       <c r="Z152" s="3"/>
       <c r="AA152" s="3"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5564,7 +5586,7 @@
       <c r="Z153" s="3"/>
       <c r="AA153" s="3"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5593,7 +5615,7 @@
       <c r="Z154" s="3"/>
       <c r="AA154" s="3"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5622,7 +5644,7 @@
       <c r="Z155" s="3"/>
       <c r="AA155" s="3"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5651,7 +5673,7 @@
       <c r="Z156" s="3"/>
       <c r="AA156" s="3"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5680,7 +5702,7 @@
       <c r="Z157" s="3"/>
       <c r="AA157" s="3"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5709,7 +5731,7 @@
       <c r="Z158" s="3"/>
       <c r="AA158" s="3"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5738,7 +5760,7 @@
       <c r="Z159" s="3"/>
       <c r="AA159" s="3"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5767,7 +5789,7 @@
       <c r="Z160" s="3"/>
       <c r="AA160" s="3"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5796,7 +5818,7 @@
       <c r="Z161" s="3"/>
       <c r="AA161" s="3"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5825,7 +5847,7 @@
       <c r="Z162" s="3"/>
       <c r="AA162" s="3"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5854,7 +5876,7 @@
       <c r="Z163" s="3"/>
       <c r="AA163" s="3"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -5883,7 +5905,7 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -5912,7 +5934,7 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -5941,7 +5963,7 @@
       <c r="Z166" s="3"/>
       <c r="AA166" s="3"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5970,7 +5992,7 @@
       <c r="Z167" s="3"/>
       <c r="AA167" s="3"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -5999,7 +6021,7 @@
       <c r="Z168" s="3"/>
       <c r="AA168" s="3"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -6028,7 +6050,7 @@
       <c r="Z169" s="3"/>
       <c r="AA169" s="3"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -6057,7 +6079,7 @@
       <c r="Z170" s="3"/>
       <c r="AA170" s="3"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6086,7 +6108,7 @@
       <c r="Z171" s="3"/>
       <c r="AA171" s="3"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6115,7 +6137,7 @@
       <c r="Z172" s="3"/>
       <c r="AA172" s="3"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6144,7 +6166,7 @@
       <c r="Z173" s="3"/>
       <c r="AA173" s="3"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6173,7 +6195,7 @@
       <c r="Z174" s="3"/>
       <c r="AA174" s="3"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6202,7 +6224,7 @@
       <c r="Z175" s="3"/>
       <c r="AA175" s="3"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6231,7 +6253,7 @@
       <c r="Z176" s="3"/>
       <c r="AA176" s="3"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6260,7 +6282,7 @@
       <c r="Z177" s="3"/>
       <c r="AA177" s="3"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6289,7 +6311,7 @@
       <c r="Z178" s="3"/>
       <c r="AA178" s="3"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6318,7 +6340,7 @@
       <c r="Z179" s="3"/>
       <c r="AA179" s="3"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6347,7 +6369,7 @@
       <c r="Z180" s="3"/>
       <c r="AA180" s="3"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6376,7 +6398,7 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="3"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6405,7 +6427,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="3"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6434,7 +6456,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="3"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6463,7 +6485,7 @@
       <c r="Z184" s="3"/>
       <c r="AA184" s="3"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6492,7 +6514,7 @@
       <c r="Z185" s="3"/>
       <c r="AA185" s="3"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6521,7 +6543,7 @@
       <c r="Z186" s="3"/>
       <c r="AA186" s="3"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6550,7 +6572,7 @@
       <c r="Z187" s="3"/>
       <c r="AA187" s="3"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6579,7 +6601,7 @@
       <c r="Z188" s="3"/>
       <c r="AA188" s="3"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6608,7 +6630,7 @@
       <c r="Z189" s="3"/>
       <c r="AA189" s="3"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6637,7 +6659,7 @@
       <c r="Z190" s="3"/>
       <c r="AA190" s="3"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6666,7 +6688,7 @@
       <c r="Z191" s="3"/>
       <c r="AA191" s="3"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6695,7 +6717,7 @@
       <c r="Z192" s="3"/>
       <c r="AA192" s="3"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6724,7 +6746,7 @@
       <c r="Z193" s="3"/>
       <c r="AA193" s="3"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6753,7 +6775,7 @@
       <c r="Z194" s="3"/>
       <c r="AA194" s="3"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6782,7 +6804,7 @@
       <c r="Z195" s="3"/>
       <c r="AA195" s="3"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6811,7 +6833,7 @@
       <c r="Z196" s="3"/>
       <c r="AA196" s="3"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6840,7 +6862,7 @@
       <c r="Z197" s="3"/>
       <c r="AA197" s="3"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -6869,7 +6891,7 @@
       <c r="Z198" s="3"/>
       <c r="AA198" s="3"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -6898,7 +6920,7 @@
       <c r="Z199" s="3"/>
       <c r="AA199" s="3"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6927,7 +6949,7 @@
       <c r="Z200" s="3"/>
       <c r="AA200" s="3"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -6956,7 +6978,7 @@
       <c r="Z201" s="3"/>
       <c r="AA201" s="3"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -6985,7 +7007,7 @@
       <c r="Z202" s="3"/>
       <c r="AA202" s="3"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -7014,7 +7036,7 @@
       <c r="Z203" s="3"/>
       <c r="AA203" s="3"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -7043,7 +7065,7 @@
       <c r="Z204" s="3"/>
       <c r="AA204" s="3"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7072,7 +7094,7 @@
       <c r="Z205" s="3"/>
       <c r="AA205" s="3"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7101,7 +7123,7 @@
       <c r="Z206" s="3"/>
       <c r="AA206" s="3"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7130,7 +7152,7 @@
       <c r="Z207" s="3"/>
       <c r="AA207" s="3"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7159,7 +7181,7 @@
       <c r="Z208" s="3"/>
       <c r="AA208" s="3"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7188,7 +7210,7 @@
       <c r="Z209" s="3"/>
       <c r="AA209" s="3"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7217,7 +7239,7 @@
       <c r="Z210" s="3"/>
       <c r="AA210" s="3"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7246,7 +7268,7 @@
       <c r="Z211" s="3"/>
       <c r="AA211" s="3"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7275,7 +7297,7 @@
       <c r="Z212" s="3"/>
       <c r="AA212" s="3"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7304,7 +7326,7 @@
       <c r="Z213" s="3"/>
       <c r="AA213" s="3"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7333,7 +7355,7 @@
       <c r="Z214" s="3"/>
       <c r="AA214" s="3"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7362,7 +7384,7 @@
       <c r="Z215" s="3"/>
       <c r="AA215" s="3"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7391,7 +7413,7 @@
       <c r="Z216" s="3"/>
       <c r="AA216" s="3"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7420,7 +7442,7 @@
       <c r="Z217" s="3"/>
       <c r="AA217" s="3"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7449,7 +7471,7 @@
       <c r="Z218" s="3"/>
       <c r="AA218" s="3"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7478,7 +7500,7 @@
       <c r="Z219" s="3"/>
       <c r="AA219" s="3"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7507,7 +7529,7 @@
       <c r="Z220" s="3"/>
       <c r="AA220" s="3"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -7536,7 +7558,7 @@
       <c r="Z221" s="3"/>
       <c r="AA221" s="3"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -7565,7 +7587,7 @@
       <c r="Z222" s="3"/>
       <c r="AA222" s="3"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -7594,7 +7616,7 @@
       <c r="Z223" s="3"/>
       <c r="AA223" s="3"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -7623,7 +7645,7 @@
       <c r="Z224" s="3"/>
       <c r="AA224" s="3"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -7652,7 +7674,7 @@
       <c r="Z225" s="3"/>
       <c r="AA225" s="3"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -7681,7 +7703,7 @@
       <c r="Z226" s="3"/>
       <c r="AA226" s="3"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -7710,7 +7732,7 @@
       <c r="Z227" s="3"/>
       <c r="AA227" s="3"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -7739,7 +7761,7 @@
       <c r="Z228" s="3"/>
       <c r="AA228" s="3"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -7768,7 +7790,7 @@
       <c r="Z229" s="3"/>
       <c r="AA229" s="3"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -7797,7 +7819,7 @@
       <c r="Z230" s="3"/>
       <c r="AA230" s="3"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -7826,7 +7848,7 @@
       <c r="Z231" s="3"/>
       <c r="AA231" s="3"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -7855,7 +7877,7 @@
       <c r="Z232" s="3"/>
       <c r="AA232" s="3"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -7884,7 +7906,7 @@
       <c r="Z233" s="3"/>
       <c r="AA233" s="3"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -7913,7 +7935,7 @@
       <c r="Z234" s="3"/>
       <c r="AA234" s="3"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -7942,7 +7964,7 @@
       <c r="Z235" s="3"/>
       <c r="AA235" s="3"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -7971,7 +7993,7 @@
       <c r="Z236" s="3"/>
       <c r="AA236" s="3"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -8000,7 +8022,7 @@
       <c r="Z237" s="3"/>
       <c r="AA237" s="3"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -8029,7 +8051,7 @@
       <c r="Z238" s="3"/>
       <c r="AA238" s="3"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -8058,7 +8080,7 @@
       <c r="Z239" s="3"/>
       <c r="AA239" s="3"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -8087,7 +8109,7 @@
       <c r="Z240" s="3"/>
       <c r="AA240" s="3"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -8116,7 +8138,7 @@
       <c r="Z241" s="3"/>
       <c r="AA241" s="3"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -8145,7 +8167,7 @@
       <c r="Z242" s="3"/>
       <c r="AA242" s="3"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -8174,7 +8196,7 @@
       <c r="Z243" s="3"/>
       <c r="AA243" s="3"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -8203,7 +8225,7 @@
       <c r="Z244" s="3"/>
       <c r="AA244" s="3"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -8232,7 +8254,7 @@
       <c r="Z245" s="3"/>
       <c r="AA245" s="3"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -8261,7 +8283,7 @@
       <c r="Z246" s="3"/>
       <c r="AA246" s="3"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -8290,7 +8312,7 @@
       <c r="Z247" s="3"/>
       <c r="AA247" s="3"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -8319,7 +8341,7 @@
       <c r="Z248" s="3"/>
       <c r="AA248" s="3"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -8348,7 +8370,7 @@
       <c r="Z249" s="3"/>
       <c r="AA249" s="3"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -8377,7 +8399,7 @@
       <c r="Z250" s="3"/>
       <c r="AA250" s="3"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -8406,7 +8428,7 @@
       <c r="Z251" s="3"/>
       <c r="AA251" s="3"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -8435,7 +8457,7 @@
       <c r="Z252" s="3"/>
       <c r="AA252" s="3"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -8464,7 +8486,7 @@
       <c r="Z253" s="3"/>
       <c r="AA253" s="3"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -8493,7 +8515,7 @@
       <c r="Z254" s="3"/>
       <c r="AA254" s="3"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -8522,7 +8544,7 @@
       <c r="Z255" s="3"/>
       <c r="AA255" s="3"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -8551,7 +8573,7 @@
       <c r="Z256" s="3"/>
       <c r="AA256" s="3"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -8580,7 +8602,7 @@
       <c r="Z257" s="3"/>
       <c r="AA257" s="3"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -8609,7 +8631,7 @@
       <c r="Z258" s="3"/>
       <c r="AA258" s="3"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -8638,7 +8660,7 @@
       <c r="Z259" s="3"/>
       <c r="AA259" s="3"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -8667,7 +8689,7 @@
       <c r="Z260" s="3"/>
       <c r="AA260" s="3"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -8696,7 +8718,7 @@
       <c r="Z261" s="3"/>
       <c r="AA261" s="3"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -8725,7 +8747,7 @@
       <c r="Z262" s="3"/>
       <c r="AA262" s="3"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -8754,7 +8776,7 @@
       <c r="Z263" s="3"/>
       <c r="AA263" s="3"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -8783,7 +8805,7 @@
       <c r="Z264" s="3"/>
       <c r="AA264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -8812,7 +8834,7 @@
       <c r="Z265" s="3"/>
       <c r="AA265" s="3"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -8841,7 +8863,7 @@
       <c r="Z266" s="3"/>
       <c r="AA266" s="3"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -8870,7 +8892,7 @@
       <c r="Z267" s="3"/>
       <c r="AA267" s="3"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -8899,7 +8921,7 @@
       <c r="Z268" s="3"/>
       <c r="AA268" s="3"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -8928,7 +8950,7 @@
       <c r="Z269" s="3"/>
       <c r="AA269" s="3"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -8957,7 +8979,7 @@
       <c r="Z270" s="3"/>
       <c r="AA270" s="3"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -8986,7 +9008,7 @@
       <c r="Z271" s="3"/>
       <c r="AA271" s="3"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -9015,7 +9037,7 @@
       <c r="Z272" s="3"/>
       <c r="AA272" s="3"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -9044,7 +9066,7 @@
       <c r="Z273" s="3"/>
       <c r="AA273" s="3"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -9073,7 +9095,7 @@
       <c r="Z274" s="3"/>
       <c r="AA274" s="3"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -9102,7 +9124,7 @@
       <c r="Z275" s="3"/>
       <c r="AA275" s="3"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -9131,7 +9153,7 @@
       <c r="Z276" s="3"/>
       <c r="AA276" s="3"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -9160,7 +9182,7 @@
       <c r="Z277" s="3"/>
       <c r="AA277" s="3"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -9189,7 +9211,7 @@
       <c r="Z278" s="3"/>
       <c r="AA278" s="3"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -9218,7 +9240,7 @@
       <c r="Z279" s="3"/>
       <c r="AA279" s="3"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -9247,7 +9269,7 @@
       <c r="Z280" s="3"/>
       <c r="AA280" s="3"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -9276,7 +9298,7 @@
       <c r="Z281" s="3"/>
       <c r="AA281" s="3"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -9305,7 +9327,7 @@
       <c r="Z282" s="3"/>
       <c r="AA282" s="3"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -9334,7 +9356,7 @@
       <c r="Z283" s="3"/>
       <c r="AA283" s="3"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -9363,7 +9385,7 @@
       <c r="Z284" s="3"/>
       <c r="AA284" s="3"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -9392,7 +9414,7 @@
       <c r="Z285" s="3"/>
       <c r="AA285" s="3"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -9421,7 +9443,7 @@
       <c r="Z286" s="3"/>
       <c r="AA286" s="3"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -9450,7 +9472,7 @@
       <c r="Z287" s="3"/>
       <c r="AA287" s="3"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -9479,7 +9501,7 @@
       <c r="Z288" s="3"/>
       <c r="AA288" s="3"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -9508,7 +9530,7 @@
       <c r="Z289" s="3"/>
       <c r="AA289" s="3"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -9537,7 +9559,7 @@
       <c r="Z290" s="3"/>
       <c r="AA290" s="3"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -9566,7 +9588,7 @@
       <c r="Z291" s="3"/>
       <c r="AA291" s="3"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -9595,7 +9617,7 @@
       <c r="Z292" s="3"/>
       <c r="AA292" s="3"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -9624,7 +9646,7 @@
       <c r="Z293" s="3"/>
       <c r="AA293" s="3"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -9653,7 +9675,7 @@
       <c r="Z294" s="3"/>
       <c r="AA294" s="3"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -9682,7 +9704,7 @@
       <c r="Z295" s="3"/>
       <c r="AA295" s="3"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -9711,7 +9733,7 @@
       <c r="Z296" s="3"/>
       <c r="AA296" s="3"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -9740,7 +9762,7 @@
       <c r="Z297" s="3"/>
       <c r="AA297" s="3"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -9769,7 +9791,7 @@
       <c r="Z298" s="3"/>
       <c r="AA298" s="3"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -9798,7 +9820,7 @@
       <c r="Z299" s="3"/>
       <c r="AA299" s="3"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -9827,7 +9849,7 @@
       <c r="Z300" s="3"/>
       <c r="AA300" s="3"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -9856,7 +9878,7 @@
       <c r="Z301" s="3"/>
       <c r="AA301" s="3"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -9885,7 +9907,7 @@
       <c r="Z302" s="3"/>
       <c r="AA302" s="3"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -9914,7 +9936,7 @@
       <c r="Z303" s="3"/>
       <c r="AA303" s="3"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -9943,7 +9965,7 @@
       <c r="Z304" s="3"/>
       <c r="AA304" s="3"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -9972,7 +9994,7 @@
       <c r="Z305" s="3"/>
       <c r="AA305" s="3"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -10001,7 +10023,7 @@
       <c r="Z306" s="3"/>
       <c r="AA306" s="3"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -10030,7 +10052,7 @@
       <c r="Z307" s="3"/>
       <c r="AA307" s="3"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -10059,7 +10081,7 @@
       <c r="Z308" s="3"/>
       <c r="AA308" s="3"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -10088,7 +10110,7 @@
       <c r="Z309" s="3"/>
       <c r="AA309" s="3"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -10117,7 +10139,7 @@
       <c r="Z310" s="3"/>
       <c r="AA310" s="3"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -10146,7 +10168,7 @@
       <c r="Z311" s="3"/>
       <c r="AA311" s="3"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -10175,7 +10197,7 @@
       <c r="Z312" s="3"/>
       <c r="AA312" s="3"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -10204,7 +10226,7 @@
       <c r="Z313" s="3"/>
       <c r="AA313" s="3"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -10233,7 +10255,7 @@
       <c r="Z314" s="3"/>
       <c r="AA314" s="3"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -10262,7 +10284,7 @@
       <c r="Z315" s="3"/>
       <c r="AA315" s="3"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -10291,7 +10313,7 @@
       <c r="Z316" s="3"/>
       <c r="AA316" s="3"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -10320,7 +10342,7 @@
       <c r="Z317" s="3"/>
       <c r="AA317" s="3"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -10349,7 +10371,7 @@
       <c r="Z318" s="3"/>
       <c r="AA318" s="3"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -10378,7 +10400,7 @@
       <c r="Z319" s="3"/>
       <c r="AA319" s="3"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -10407,7 +10429,7 @@
       <c r="Z320" s="3"/>
       <c r="AA320" s="3"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -10436,7 +10458,7 @@
       <c r="Z321" s="3"/>
       <c r="AA321" s="3"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -10465,7 +10487,7 @@
       <c r="Z322" s="3"/>
       <c r="AA322" s="3"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -10494,7 +10516,7 @@
       <c r="Z323" s="3"/>
       <c r="AA323" s="3"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -10523,7 +10545,7 @@
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -10552,7 +10574,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -10581,7 +10603,7 @@
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -10610,7 +10632,7 @@
       <c r="Z327" s="3"/>
       <c r="AA327" s="3"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -10639,7 +10661,7 @@
       <c r="Z328" s="3"/>
       <c r="AA328" s="3"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -10668,7 +10690,7 @@
       <c r="Z329" s="3"/>
       <c r="AA329" s="3"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -10697,7 +10719,7 @@
       <c r="Z330" s="3"/>
       <c r="AA330" s="3"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -10726,7 +10748,7 @@
       <c r="Z331" s="3"/>
       <c r="AA331" s="3"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -10755,7 +10777,7 @@
       <c r="Z332" s="3"/>
       <c r="AA332" s="3"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -10784,7 +10806,7 @@
       <c r="Z333" s="3"/>
       <c r="AA333" s="3"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -10813,7 +10835,7 @@
       <c r="Z334" s="3"/>
       <c r="AA334" s="3"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -10842,7 +10864,7 @@
       <c r="Z335" s="3"/>
       <c r="AA335" s="3"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -10871,7 +10893,7 @@
       <c r="Z336" s="3"/>
       <c r="AA336" s="3"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -10900,7 +10922,7 @@
       <c r="Z337" s="3"/>
       <c r="AA337" s="3"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -10929,7 +10951,7 @@
       <c r="Z338" s="3"/>
       <c r="AA338" s="3"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -10958,7 +10980,7 @@
       <c r="Z339" s="3"/>
       <c r="AA339" s="3"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -10987,7 +11009,7 @@
       <c r="Z340" s="3"/>
       <c r="AA340" s="3"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -11016,7 +11038,7 @@
       <c r="Z341" s="3"/>
       <c r="AA341" s="3"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -11045,7 +11067,7 @@
       <c r="Z342" s="3"/>
       <c r="AA342" s="3"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -11074,7 +11096,7 @@
       <c r="Z343" s="3"/>
       <c r="AA343" s="3"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -11103,7 +11125,7 @@
       <c r="Z344" s="3"/>
       <c r="AA344" s="3"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -11132,7 +11154,7 @@
       <c r="Z345" s="3"/>
       <c r="AA345" s="3"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -11161,7 +11183,7 @@
       <c r="Z346" s="3"/>
       <c r="AA346" s="3"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -11190,7 +11212,7 @@
       <c r="Z347" s="3"/>
       <c r="AA347" s="3"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -11219,7 +11241,7 @@
       <c r="Z348" s="3"/>
       <c r="AA348" s="3"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -11248,7 +11270,7 @@
       <c r="Z349" s="3"/>
       <c r="AA349" s="3"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -11277,7 +11299,7 @@
       <c r="Z350" s="3"/>
       <c r="AA350" s="3"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -11306,7 +11328,7 @@
       <c r="Z351" s="3"/>
       <c r="AA351" s="3"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -11335,7 +11357,7 @@
       <c r="Z352" s="3"/>
       <c r="AA352" s="3"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -11364,7 +11386,7 @@
       <c r="Z353" s="3"/>
       <c r="AA353" s="3"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -11393,7 +11415,7 @@
       <c r="Z354" s="3"/>
       <c r="AA354" s="3"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -11422,7 +11444,7 @@
       <c r="Z355" s="3"/>
       <c r="AA355" s="3"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -11451,7 +11473,7 @@
       <c r="Z356" s="3"/>
       <c r="AA356" s="3"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -11480,7 +11502,7 @@
       <c r="Z357" s="3"/>
       <c r="AA357" s="3"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -11509,7 +11531,7 @@
       <c r="Z358" s="3"/>
       <c r="AA358" s="3"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -11538,7 +11560,7 @@
       <c r="Z359" s="3"/>
       <c r="AA359" s="3"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -11567,7 +11589,7 @@
       <c r="Z360" s="3"/>
       <c r="AA360" s="3"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -11596,7 +11618,7 @@
       <c r="Z361" s="3"/>
       <c r="AA361" s="3"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -11625,7 +11647,7 @@
       <c r="Z362" s="3"/>
       <c r="AA362" s="3"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -11654,7 +11676,7 @@
       <c r="Z363" s="3"/>
       <c r="AA363" s="3"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -11683,7 +11705,7 @@
       <c r="Z364" s="3"/>
       <c r="AA364" s="3"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -11712,7 +11734,7 @@
       <c r="Z365" s="3"/>
       <c r="AA365" s="3"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -11741,7 +11763,7 @@
       <c r="Z366" s="3"/>
       <c r="AA366" s="3"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -11770,7 +11792,7 @@
       <c r="Z367" s="3"/>
       <c r="AA367" s="3"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -11799,7 +11821,7 @@
       <c r="Z368" s="3"/>
       <c r="AA368" s="3"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -11828,7 +11850,7 @@
       <c r="Z369" s="3"/>
       <c r="AA369" s="3"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -11857,7 +11879,7 @@
       <c r="Z370" s="3"/>
       <c r="AA370" s="3"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -11886,7 +11908,7 @@
       <c r="Z371" s="3"/>
       <c r="AA371" s="3"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -11915,7 +11937,7 @@
       <c r="Z372" s="3"/>
       <c r="AA372" s="3"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -11944,7 +11966,7 @@
       <c r="Z373" s="3"/>
       <c r="AA373" s="3"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -11973,7 +11995,7 @@
       <c r="Z374" s="3"/>
       <c r="AA374" s="3"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -12002,7 +12024,7 @@
       <c r="Z375" s="3"/>
       <c r="AA375" s="3"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -12031,7 +12053,7 @@
       <c r="Z376" s="3"/>
       <c r="AA376" s="3"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -12060,7 +12082,7 @@
       <c r="Z377" s="3"/>
       <c r="AA377" s="3"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -12089,7 +12111,7 @@
       <c r="Z378" s="3"/>
       <c r="AA378" s="3"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -12118,7 +12140,7 @@
       <c r="Z379" s="3"/>
       <c r="AA379" s="3"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -12147,7 +12169,7 @@
       <c r="Z380" s="3"/>
       <c r="AA380" s="3"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -12176,7 +12198,7 @@
       <c r="Z381" s="3"/>
       <c r="AA381" s="3"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -12205,7 +12227,7 @@
       <c r="Z382" s="3"/>
       <c r="AA382" s="3"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -12234,7 +12256,7 @@
       <c r="Z383" s="3"/>
       <c r="AA383" s="3"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -12263,7 +12285,7 @@
       <c r="Z384" s="3"/>
       <c r="AA384" s="3"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -12292,7 +12314,7 @@
       <c r="Z385" s="3"/>
       <c r="AA385" s="3"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -12321,7 +12343,7 @@
       <c r="Z386" s="3"/>
       <c r="AA386" s="3"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -12350,7 +12372,7 @@
       <c r="Z387" s="3"/>
       <c r="AA387" s="3"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -12379,7 +12401,7 @@
       <c r="Z388" s="3"/>
       <c r="AA388" s="3"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -12408,7 +12430,7 @@
       <c r="Z389" s="3"/>
       <c r="AA389" s="3"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -12437,7 +12459,7 @@
       <c r="Z390" s="3"/>
       <c r="AA390" s="3"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -12466,7 +12488,7 @@
       <c r="Z391" s="3"/>
       <c r="AA391" s="3"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -12495,7 +12517,7 @@
       <c r="Z392" s="3"/>
       <c r="AA392" s="3"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -12524,7 +12546,7 @@
       <c r="Z393" s="3"/>
       <c r="AA393" s="3"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -12553,7 +12575,7 @@
       <c r="Z394" s="3"/>
       <c r="AA394" s="3"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -12582,7 +12604,7 @@
       <c r="Z395" s="3"/>
       <c r="AA395" s="3"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -12611,7 +12633,7 @@
       <c r="Z396" s="3"/>
       <c r="AA396" s="3"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -12640,7 +12662,7 @@
       <c r="Z397" s="3"/>
       <c r="AA397" s="3"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -12669,7 +12691,7 @@
       <c r="Z398" s="3"/>
       <c r="AA398" s="3"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -12698,7 +12720,7 @@
       <c r="Z399" s="3"/>
       <c r="AA399" s="3"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -12727,7 +12749,7 @@
       <c r="Z400" s="3"/>
       <c r="AA400" s="3"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -12756,7 +12778,7 @@
       <c r="Z401" s="3"/>
       <c r="AA401" s="3"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -12785,7 +12807,7 @@
       <c r="Z402" s="3"/>
       <c r="AA402" s="3"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -12814,7 +12836,7 @@
       <c r="Z403" s="3"/>
       <c r="AA403" s="3"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -12843,7 +12865,7 @@
       <c r="Z404" s="3"/>
       <c r="AA404" s="3"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -12872,7 +12894,7 @@
       <c r="Z405" s="3"/>
       <c r="AA405" s="3"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -12901,7 +12923,7 @@
       <c r="Z406" s="3"/>
       <c r="AA406" s="3"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -12930,7 +12952,7 @@
       <c r="Z407" s="3"/>
       <c r="AA407" s="3"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -12959,7 +12981,7 @@
       <c r="Z408" s="3"/>
       <c r="AA408" s="3"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -12988,7 +13010,7 @@
       <c r="Z409" s="3"/>
       <c r="AA409" s="3"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -13017,7 +13039,7 @@
       <c r="Z410" s="3"/>
       <c r="AA410" s="3"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -13046,7 +13068,7 @@
       <c r="Z411" s="3"/>
       <c r="AA411" s="3"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -13075,7 +13097,7 @@
       <c r="Z412" s="3"/>
       <c r="AA412" s="3"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -13104,7 +13126,7 @@
       <c r="Z413" s="3"/>
       <c r="AA413" s="3"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -13133,7 +13155,7 @@
       <c r="Z414" s="3"/>
       <c r="AA414" s="3"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -13162,7 +13184,7 @@
       <c r="Z415" s="3"/>
       <c r="AA415" s="3"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -13191,7 +13213,7 @@
       <c r="Z416" s="3"/>
       <c r="AA416" s="3"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -13220,7 +13242,7 @@
       <c r="Z417" s="3"/>
       <c r="AA417" s="3"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -13249,7 +13271,7 @@
       <c r="Z418" s="3"/>
       <c r="AA418" s="3"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -13278,7 +13300,7 @@
       <c r="Z419" s="3"/>
       <c r="AA419" s="3"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -13307,7 +13329,7 @@
       <c r="Z420" s="3"/>
       <c r="AA420" s="3"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -13336,7 +13358,7 @@
       <c r="Z421" s="3"/>
       <c r="AA421" s="3"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -13365,7 +13387,7 @@
       <c r="Z422" s="3"/>
       <c r="AA422" s="3"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -13394,7 +13416,7 @@
       <c r="Z423" s="3"/>
       <c r="AA423" s="3"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -13423,7 +13445,7 @@
       <c r="Z424" s="3"/>
       <c r="AA424" s="3"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -13452,7 +13474,7 @@
       <c r="Z425" s="3"/>
       <c r="AA425" s="3"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -13481,7 +13503,7 @@
       <c r="Z426" s="3"/>
       <c r="AA426" s="3"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -13510,7 +13532,7 @@
       <c r="Z427" s="3"/>
       <c r="AA427" s="3"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -13539,7 +13561,7 @@
       <c r="Z428" s="3"/>
       <c r="AA428" s="3"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -13568,7 +13590,7 @@
       <c r="Z429" s="3"/>
       <c r="AA429" s="3"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -13597,7 +13619,7 @@
       <c r="Z430" s="3"/>
       <c r="AA430" s="3"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -13626,7 +13648,7 @@
       <c r="Z431" s="3"/>
       <c r="AA431" s="3"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -13655,7 +13677,7 @@
       <c r="Z432" s="3"/>
       <c r="AA432" s="3"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -13684,7 +13706,7 @@
       <c r="Z433" s="3"/>
       <c r="AA433" s="3"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -13713,7 +13735,7 @@
       <c r="Z434" s="3"/>
       <c r="AA434" s="3"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -13742,7 +13764,7 @@
       <c r="Z435" s="3"/>
       <c r="AA435" s="3"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -13771,7 +13793,7 @@
       <c r="Z436" s="3"/>
       <c r="AA436" s="3"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -13800,7 +13822,7 @@
       <c r="Z437" s="3"/>
       <c r="AA437" s="3"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -13829,7 +13851,7 @@
       <c r="Z438" s="3"/>
       <c r="AA438" s="3"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -13858,7 +13880,7 @@
       <c r="Z439" s="3"/>
       <c r="AA439" s="3"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -13887,7 +13909,7 @@
       <c r="Z440" s="3"/>
       <c r="AA440" s="3"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -13916,7 +13938,7 @@
       <c r="Z441" s="3"/>
       <c r="AA441" s="3"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -13945,7 +13967,7 @@
       <c r="Z442" s="3"/>
       <c r="AA442" s="3"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -13974,7 +13996,7 @@
       <c r="Z443" s="3"/>
       <c r="AA443" s="3"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -14003,7 +14025,7 @@
       <c r="Z444" s="3"/>
       <c r="AA444" s="3"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -14032,7 +14054,7 @@
       <c r="Z445" s="3"/>
       <c r="AA445" s="3"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -14061,7 +14083,7 @@
       <c r="Z446" s="3"/>
       <c r="AA446" s="3"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -14090,7 +14112,7 @@
       <c r="Z447" s="3"/>
       <c r="AA447" s="3"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -14119,7 +14141,7 @@
       <c r="Z448" s="3"/>
       <c r="AA448" s="3"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -14148,7 +14170,7 @@
       <c r="Z449" s="3"/>
       <c r="AA449" s="3"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -14177,7 +14199,7 @@
       <c r="Z450" s="3"/>
       <c r="AA450" s="3"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -14206,7 +14228,7 @@
       <c r="Z451" s="3"/>
       <c r="AA451" s="3"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -14235,7 +14257,7 @@
       <c r="Z452" s="3"/>
       <c r="AA452" s="3"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -14264,7 +14286,7 @@
       <c r="Z453" s="3"/>
       <c r="AA453" s="3"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -14293,7 +14315,7 @@
       <c r="Z454" s="3"/>
       <c r="AA454" s="3"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -14322,7 +14344,7 @@
       <c r="Z455" s="3"/>
       <c r="AA455" s="3"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -14351,7 +14373,7 @@
       <c r="Z456" s="3"/>
       <c r="AA456" s="3"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -14380,7 +14402,7 @@
       <c r="Z457" s="3"/>
       <c r="AA457" s="3"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -14409,7 +14431,7 @@
       <c r="Z458" s="3"/>
       <c r="AA458" s="3"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -14438,7 +14460,7 @@
       <c r="Z459" s="3"/>
       <c r="AA459" s="3"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -14467,7 +14489,7 @@
       <c r="Z460" s="3"/>
       <c r="AA460" s="3"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -14496,7 +14518,7 @@
       <c r="Z461" s="3"/>
       <c r="AA461" s="3"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -14525,7 +14547,7 @@
       <c r="Z462" s="3"/>
       <c r="AA462" s="3"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -14554,7 +14576,7 @@
       <c r="Z463" s="3"/>
       <c r="AA463" s="3"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -14583,7 +14605,7 @@
       <c r="Z464" s="3"/>
       <c r="AA464" s="3"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -14612,7 +14634,7 @@
       <c r="Z465" s="3"/>
       <c r="AA465" s="3"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -14641,7 +14663,7 @@
       <c r="Z466" s="3"/>
       <c r="AA466" s="3"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -14670,7 +14692,7 @@
       <c r="Z467" s="3"/>
       <c r="AA467" s="3"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -14699,7 +14721,7 @@
       <c r="Z468" s="3"/>
       <c r="AA468" s="3"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -14728,7 +14750,7 @@
       <c r="Z469" s="3"/>
       <c r="AA469" s="3"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -14757,7 +14779,7 @@
       <c r="Z470" s="3"/>
       <c r="AA470" s="3"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -14786,7 +14808,7 @@
       <c r="Z471" s="3"/>
       <c r="AA471" s="3"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -14815,7 +14837,7 @@
       <c r="Z472" s="3"/>
       <c r="AA472" s="3"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -14844,7 +14866,7 @@
       <c r="Z473" s="3"/>
       <c r="AA473" s="3"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -14873,7 +14895,7 @@
       <c r="Z474" s="3"/>
       <c r="AA474" s="3"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -14902,7 +14924,7 @@
       <c r="Z475" s="3"/>
       <c r="AA475" s="3"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -14931,7 +14953,7 @@
       <c r="Z476" s="3"/>
       <c r="AA476" s="3"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -14960,7 +14982,7 @@
       <c r="Z477" s="3"/>
       <c r="AA477" s="3"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -14989,7 +15011,7 @@
       <c r="Z478" s="3"/>
       <c r="AA478" s="3"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -15018,7 +15040,7 @@
       <c r="Z479" s="3"/>
       <c r="AA479" s="3"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -15047,7 +15069,7 @@
       <c r="Z480" s="3"/>
       <c r="AA480" s="3"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -15076,7 +15098,7 @@
       <c r="Z481" s="3"/>
       <c r="AA481" s="3"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -15105,7 +15127,7 @@
       <c r="Z482" s="3"/>
       <c r="AA482" s="3"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -15134,7 +15156,7 @@
       <c r="Z483" s="3"/>
       <c r="AA483" s="3"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -15163,7 +15185,7 @@
       <c r="Z484" s="3"/>
       <c r="AA484" s="3"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -15192,7 +15214,7 @@
       <c r="Z485" s="3"/>
       <c r="AA485" s="3"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -15221,7 +15243,7 @@
       <c r="Z486" s="3"/>
       <c r="AA486" s="3"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -15250,7 +15272,7 @@
       <c r="Z487" s="3"/>
       <c r="AA487" s="3"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -15279,7 +15301,7 @@
       <c r="Z488" s="3"/>
       <c r="AA488" s="3"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -15308,7 +15330,7 @@
       <c r="Z489" s="3"/>
       <c r="AA489" s="3"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -15337,7 +15359,7 @@
       <c r="Z490" s="3"/>
       <c r="AA490" s="3"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -15366,7 +15388,7 @@
       <c r="Z491" s="3"/>
       <c r="AA491" s="3"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -15395,7 +15417,7 @@
       <c r="Z492" s="3"/>
       <c r="AA492" s="3"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -15424,7 +15446,7 @@
       <c r="Z493" s="3"/>
       <c r="AA493" s="3"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -15453,7 +15475,7 @@
       <c r="Z494" s="3"/>
       <c r="AA494" s="3"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -15482,7 +15504,7 @@
       <c r="Z495" s="3"/>
       <c r="AA495" s="3"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -15511,7 +15533,7 @@
       <c r="Z496" s="3"/>
       <c r="AA496" s="3"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -15540,7 +15562,7 @@
       <c r="Z497" s="3"/>
       <c r="AA497" s="3"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -15569,7 +15591,7 @@
       <c r="Z498" s="3"/>
       <c r="AA498" s="3"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -15598,7 +15620,7 @@
       <c r="Z499" s="3"/>
       <c r="AA499" s="3"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -15627,7 +15649,7 @@
       <c r="Z500" s="3"/>
       <c r="AA500" s="3"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -15656,7 +15678,7 @@
       <c r="Z501" s="3"/>
       <c r="AA501" s="3"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -15685,7 +15707,7 @@
       <c r="Z502" s="3"/>
       <c r="AA502" s="3"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -15714,7 +15736,7 @@
       <c r="Z503" s="3"/>
       <c r="AA503" s="3"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -15743,7 +15765,7 @@
       <c r="Z504" s="3"/>
       <c r="AA504" s="3"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -15772,7 +15794,7 @@
       <c r="Z505" s="3"/>
       <c r="AA505" s="3"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -15801,7 +15823,7 @@
       <c r="Z506" s="3"/>
       <c r="AA506" s="3"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -15830,7 +15852,7 @@
       <c r="Z507" s="3"/>
       <c r="AA507" s="3"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -15859,7 +15881,7 @@
       <c r="Z508" s="3"/>
       <c r="AA508" s="3"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -15888,7 +15910,7 @@
       <c r="Z509" s="3"/>
       <c r="AA509" s="3"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -15917,7 +15939,7 @@
       <c r="Z510" s="3"/>
       <c r="AA510" s="3"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -15946,7 +15968,7 @@
       <c r="Z511" s="3"/>
       <c r="AA511" s="3"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -15975,7 +15997,7 @@
       <c r="Z512" s="3"/>
       <c r="AA512" s="3"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -16004,7 +16026,7 @@
       <c r="Z513" s="3"/>
       <c r="AA513" s="3"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -16033,7 +16055,7 @@
       <c r="Z514" s="3"/>
       <c r="AA514" s="3"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -16062,7 +16084,7 @@
       <c r="Z515" s="3"/>
       <c r="AA515" s="3"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -16091,7 +16113,7 @@
       <c r="Z516" s="3"/>
       <c r="AA516" s="3"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -16120,7 +16142,7 @@
       <c r="Z517" s="3"/>
       <c r="AA517" s="3"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -16149,7 +16171,7 @@
       <c r="Z518" s="3"/>
       <c r="AA518" s="3"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -16178,7 +16200,7 @@
       <c r="Z519" s="3"/>
       <c r="AA519" s="3"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -16207,7 +16229,7 @@
       <c r="Z520" s="3"/>
       <c r="AA520" s="3"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -16236,7 +16258,7 @@
       <c r="Z521" s="3"/>
       <c r="AA521" s="3"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -16265,7 +16287,7 @@
       <c r="Z522" s="3"/>
       <c r="AA522" s="3"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -16294,7 +16316,7 @@
       <c r="Z523" s="3"/>
       <c r="AA523" s="3"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -16323,7 +16345,7 @@
       <c r="Z524" s="3"/>
       <c r="AA524" s="3"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -16352,7 +16374,7 @@
       <c r="Z525" s="3"/>
       <c r="AA525" s="3"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -16381,7 +16403,7 @@
       <c r="Z526" s="3"/>
       <c r="AA526" s="3"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -16410,7 +16432,7 @@
       <c r="Z527" s="3"/>
       <c r="AA527" s="3"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -16439,7 +16461,7 @@
       <c r="Z528" s="3"/>
       <c r="AA528" s="3"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -16468,7 +16490,7 @@
       <c r="Z529" s="3"/>
       <c r="AA529" s="3"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -16497,7 +16519,7 @@
       <c r="Z530" s="3"/>
       <c r="AA530" s="3"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -16526,7 +16548,7 @@
       <c r="Z531" s="3"/>
       <c r="AA531" s="3"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -16555,7 +16577,7 @@
       <c r="Z532" s="3"/>
       <c r="AA532" s="3"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -16584,7 +16606,7 @@
       <c r="Z533" s="3"/>
       <c r="AA533" s="3"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -16613,7 +16635,7 @@
       <c r="Z534" s="3"/>
       <c r="AA534" s="3"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -16642,7 +16664,7 @@
       <c r="Z535" s="3"/>
       <c r="AA535" s="3"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -16671,7 +16693,7 @@
       <c r="Z536" s="3"/>
       <c r="AA536" s="3"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -16700,7 +16722,7 @@
       <c r="Z537" s="3"/>
       <c r="AA537" s="3"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -16729,7 +16751,7 @@
       <c r="Z538" s="3"/>
       <c r="AA538" s="3"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -16758,7 +16780,7 @@
       <c r="Z539" s="3"/>
       <c r="AA539" s="3"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -16787,7 +16809,7 @@
       <c r="Z540" s="3"/>
       <c r="AA540" s="3"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -16816,7 +16838,7 @@
       <c r="Z541" s="3"/>
       <c r="AA541" s="3"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -16845,7 +16867,7 @@
       <c r="Z542" s="3"/>
       <c r="AA542" s="3"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -16874,7 +16896,7 @@
       <c r="Z543" s="3"/>
       <c r="AA543" s="3"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -16903,7 +16925,7 @@
       <c r="Z544" s="3"/>
       <c r="AA544" s="3"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -16932,7 +16954,7 @@
       <c r="Z545" s="3"/>
       <c r="AA545" s="3"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -16961,7 +16983,7 @@
       <c r="Z546" s="3"/>
       <c r="AA546" s="3"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -16990,7 +17012,7 @@
       <c r="Z547" s="3"/>
       <c r="AA547" s="3"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -17019,7 +17041,7 @@
       <c r="Z548" s="3"/>
       <c r="AA548" s="3"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -17048,7 +17070,7 @@
       <c r="Z549" s="3"/>
       <c r="AA549" s="3"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -17077,7 +17099,7 @@
       <c r="Z550" s="3"/>
       <c r="AA550" s="3"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -17106,7 +17128,7 @@
       <c r="Z551" s="3"/>
       <c r="AA551" s="3"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -17135,7 +17157,7 @@
       <c r="Z552" s="3"/>
       <c r="AA552" s="3"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -17164,7 +17186,7 @@
       <c r="Z553" s="3"/>
       <c r="AA553" s="3"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -17193,7 +17215,7 @@
       <c r="Z554" s="3"/>
       <c r="AA554" s="3"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -17222,7 +17244,7 @@
       <c r="Z555" s="3"/>
       <c r="AA555" s="3"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -17251,7 +17273,7 @@
       <c r="Z556" s="3"/>
       <c r="AA556" s="3"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -17280,7 +17302,7 @@
       <c r="Z557" s="3"/>
       <c r="AA557" s="3"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -17309,7 +17331,7 @@
       <c r="Z558" s="3"/>
       <c r="AA558" s="3"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -17338,7 +17360,7 @@
       <c r="Z559" s="3"/>
       <c r="AA559" s="3"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -17367,7 +17389,7 @@
       <c r="Z560" s="3"/>
       <c r="AA560" s="3"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -17396,7 +17418,7 @@
       <c r="Z561" s="3"/>
       <c r="AA561" s="3"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -17425,7 +17447,7 @@
       <c r="Z562" s="3"/>
       <c r="AA562" s="3"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -17454,7 +17476,7 @@
       <c r="Z563" s="3"/>
       <c r="AA563" s="3"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -17483,7 +17505,7 @@
       <c r="Z564" s="3"/>
       <c r="AA564" s="3"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -17512,7 +17534,7 @@
       <c r="Z565" s="3"/>
       <c r="AA565" s="3"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -17541,7 +17563,7 @@
       <c r="Z566" s="3"/>
       <c r="AA566" s="3"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -17570,7 +17592,7 @@
       <c r="Z567" s="3"/>
       <c r="AA567" s="3"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -17599,7 +17621,7 @@
       <c r="Z568" s="3"/>
       <c r="AA568" s="3"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -17628,7 +17650,7 @@
       <c r="Z569" s="3"/>
       <c r="AA569" s="3"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -17657,7 +17679,7 @@
       <c r="Z570" s="3"/>
       <c r="AA570" s="3"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -17686,7 +17708,7 @@
       <c r="Z571" s="3"/>
       <c r="AA571" s="3"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -17715,7 +17737,7 @@
       <c r="Z572" s="3"/>
       <c r="AA572" s="3"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -17744,7 +17766,7 @@
       <c r="Z573" s="3"/>
       <c r="AA573" s="3"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -17773,7 +17795,7 @@
       <c r="Z574" s="3"/>
       <c r="AA574" s="3"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -17802,7 +17824,7 @@
       <c r="Z575" s="3"/>
       <c r="AA575" s="3"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -17831,7 +17853,7 @@
       <c r="Z576" s="3"/>
       <c r="AA576" s="3"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -17860,7 +17882,7 @@
       <c r="Z577" s="3"/>
       <c r="AA577" s="3"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -17889,7 +17911,7 @@
       <c r="Z578" s="3"/>
       <c r="AA578" s="3"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -17918,7 +17940,7 @@
       <c r="Z579" s="3"/>
       <c r="AA579" s="3"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -17947,7 +17969,7 @@
       <c r="Z580" s="3"/>
       <c r="AA580" s="3"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -17976,7 +17998,7 @@
       <c r="Z581" s="3"/>
       <c r="AA581" s="3"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -18005,7 +18027,7 @@
       <c r="Z582" s="3"/>
       <c r="AA582" s="3"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -18034,7 +18056,7 @@
       <c r="Z583" s="3"/>
       <c r="AA583" s="3"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -18063,7 +18085,7 @@
       <c r="Z584" s="3"/>
       <c r="AA584" s="3"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -18092,7 +18114,7 @@
       <c r="Z585" s="3"/>
       <c r="AA585" s="3"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -18121,7 +18143,7 @@
       <c r="Z586" s="3"/>
       <c r="AA586" s="3"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -18150,7 +18172,7 @@
       <c r="Z587" s="3"/>
       <c r="AA587" s="3"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -18179,7 +18201,7 @@
       <c r="Z588" s="3"/>
       <c r="AA588" s="3"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -18208,7 +18230,7 @@
       <c r="Z589" s="3"/>
       <c r="AA589" s="3"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -18237,7 +18259,7 @@
       <c r="Z590" s="3"/>
       <c r="AA590" s="3"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -18266,7 +18288,7 @@
       <c r="Z591" s="3"/>
       <c r="AA591" s="3"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -18295,7 +18317,7 @@
       <c r="Z592" s="3"/>
       <c r="AA592" s="3"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -18324,7 +18346,7 @@
       <c r="Z593" s="3"/>
       <c r="AA593" s="3"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -18353,7 +18375,7 @@
       <c r="Z594" s="3"/>
       <c r="AA594" s="3"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -18382,7 +18404,7 @@
       <c r="Z595" s="3"/>
       <c r="AA595" s="3"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -18411,7 +18433,7 @@
       <c r="Z596" s="3"/>
       <c r="AA596" s="3"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -18440,7 +18462,7 @@
       <c r="Z597" s="3"/>
       <c r="AA597" s="3"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -18469,7 +18491,7 @@
       <c r="Z598" s="3"/>
       <c r="AA598" s="3"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -18498,7 +18520,7 @@
       <c r="Z599" s="3"/>
       <c r="AA599" s="3"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -18527,7 +18549,7 @@
       <c r="Z600" s="3"/>
       <c r="AA600" s="3"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -18556,7 +18578,7 @@
       <c r="Z601" s="3"/>
       <c r="AA601" s="3"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -18585,7 +18607,7 @@
       <c r="Z602" s="3"/>
       <c r="AA602" s="3"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -18614,7 +18636,7 @@
       <c r="Z603" s="3"/>
       <c r="AA603" s="3"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -18643,7 +18665,7 @@
       <c r="Z604" s="3"/>
       <c r="AA604" s="3"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -18672,7 +18694,7 @@
       <c r="Z605" s="3"/>
       <c r="AA605" s="3"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -18701,7 +18723,7 @@
       <c r="Z606" s="3"/>
       <c r="AA606" s="3"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -18730,7 +18752,7 @@
       <c r="Z607" s="3"/>
       <c r="AA607" s="3"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -18759,7 +18781,7 @@
       <c r="Z608" s="3"/>
       <c r="AA608" s="3"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -18788,7 +18810,7 @@
       <c r="Z609" s="3"/>
       <c r="AA609" s="3"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -18817,7 +18839,7 @@
       <c r="Z610" s="3"/>
       <c r="AA610" s="3"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -18846,7 +18868,7 @@
       <c r="Z611" s="3"/>
       <c r="AA611" s="3"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -18875,7 +18897,7 @@
       <c r="Z612" s="3"/>
       <c r="AA612" s="3"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -18904,7 +18926,7 @@
       <c r="Z613" s="3"/>
       <c r="AA613" s="3"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -18933,7 +18955,7 @@
       <c r="Z614" s="3"/>
       <c r="AA614" s="3"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -18962,7 +18984,7 @@
       <c r="Z615" s="3"/>
       <c r="AA615" s="3"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -18991,7 +19013,7 @@
       <c r="Z616" s="3"/>
       <c r="AA616" s="3"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -19020,7 +19042,7 @@
       <c r="Z617" s="3"/>
       <c r="AA617" s="3"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -19049,7 +19071,7 @@
       <c r="Z618" s="3"/>
       <c r="AA618" s="3"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -19078,7 +19100,7 @@
       <c r="Z619" s="3"/>
       <c r="AA619" s="3"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -19107,7 +19129,7 @@
       <c r="Z620" s="3"/>
       <c r="AA620" s="3"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -19136,7 +19158,7 @@
       <c r="Z621" s="3"/>
       <c r="AA621" s="3"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -19165,7 +19187,7 @@
       <c r="Z622" s="3"/>
       <c r="AA622" s="3"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -19194,7 +19216,7 @@
       <c r="Z623" s="3"/>
       <c r="AA623" s="3"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -19223,7 +19245,7 @@
       <c r="Z624" s="3"/>
       <c r="AA624" s="3"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -19252,7 +19274,7 @@
       <c r="Z625" s="3"/>
       <c r="AA625" s="3"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -19281,7 +19303,7 @@
       <c r="Z626" s="3"/>
       <c r="AA626" s="3"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -19310,7 +19332,7 @@
       <c r="Z627" s="3"/>
       <c r="AA627" s="3"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -19339,7 +19361,7 @@
       <c r="Z628" s="3"/>
       <c r="AA628" s="3"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -19368,7 +19390,7 @@
       <c r="Z629" s="3"/>
       <c r="AA629" s="3"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -19397,7 +19419,7 @@
       <c r="Z630" s="3"/>
       <c r="AA630" s="3"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -19426,7 +19448,7 @@
       <c r="Z631" s="3"/>
       <c r="AA631" s="3"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -19455,7 +19477,7 @@
       <c r="Z632" s="3"/>
       <c r="AA632" s="3"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -19484,7 +19506,7 @@
       <c r="Z633" s="3"/>
       <c r="AA633" s="3"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -19513,7 +19535,7 @@
       <c r="Z634" s="3"/>
       <c r="AA634" s="3"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -19542,7 +19564,7 @@
       <c r="Z635" s="3"/>
       <c r="AA635" s="3"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -19571,7 +19593,7 @@
       <c r="Z636" s="3"/>
       <c r="AA636" s="3"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -19600,7 +19622,7 @@
       <c r="Z637" s="3"/>
       <c r="AA637" s="3"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -19629,7 +19651,7 @@
       <c r="Z638" s="3"/>
       <c r="AA638" s="3"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -19658,7 +19680,7 @@
       <c r="Z639" s="3"/>
       <c r="AA639" s="3"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -19687,7 +19709,7 @@
       <c r="Z640" s="3"/>
       <c r="AA640" s="3"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -19716,7 +19738,7 @@
       <c r="Z641" s="3"/>
       <c r="AA641" s="3"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -19745,7 +19767,7 @@
       <c r="Z642" s="3"/>
       <c r="AA642" s="3"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -19774,7 +19796,7 @@
       <c r="Z643" s="3"/>
       <c r="AA643" s="3"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -19803,7 +19825,7 @@
       <c r="Z644" s="3"/>
       <c r="AA644" s="3"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -19832,7 +19854,7 @@
       <c r="Z645" s="3"/>
       <c r="AA645" s="3"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -19861,7 +19883,7 @@
       <c r="Z646" s="3"/>
       <c r="AA646" s="3"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -19890,7 +19912,7 @@
       <c r="Z647" s="3"/>
       <c r="AA647" s="3"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -19919,7 +19941,7 @@
       <c r="Z648" s="3"/>
       <c r="AA648" s="3"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -19948,7 +19970,7 @@
       <c r="Z649" s="3"/>
       <c r="AA649" s="3"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -19977,7 +19999,7 @@
       <c r="Z650" s="3"/>
       <c r="AA650" s="3"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -20006,7 +20028,7 @@
       <c r="Z651" s="3"/>
       <c r="AA651" s="3"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -20035,7 +20057,7 @@
       <c r="Z652" s="3"/>
       <c r="AA652" s="3"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -20064,7 +20086,7 @@
       <c r="Z653" s="3"/>
       <c r="AA653" s="3"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -20093,7 +20115,7 @@
       <c r="Z654" s="3"/>
       <c r="AA654" s="3"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -20122,7 +20144,7 @@
       <c r="Z655" s="3"/>
       <c r="AA655" s="3"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -20151,7 +20173,7 @@
       <c r="Z656" s="3"/>
       <c r="AA656" s="3"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -20180,7 +20202,7 @@
       <c r="Z657" s="3"/>
       <c r="AA657" s="3"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -20209,7 +20231,7 @@
       <c r="Z658" s="3"/>
       <c r="AA658" s="3"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -20238,7 +20260,7 @@
       <c r="Z659" s="3"/>
       <c r="AA659" s="3"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -20267,7 +20289,7 @@
       <c r="Z660" s="3"/>
       <c r="AA660" s="3"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -20296,7 +20318,7 @@
       <c r="Z661" s="3"/>
       <c r="AA661" s="3"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -20325,7 +20347,7 @@
       <c r="Z662" s="3"/>
       <c r="AA662" s="3"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -20354,7 +20376,7 @@
       <c r="Z663" s="3"/>
       <c r="AA663" s="3"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -20383,7 +20405,7 @@
       <c r="Z664" s="3"/>
       <c r="AA664" s="3"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -20412,7 +20434,7 @@
       <c r="Z665" s="3"/>
       <c r="AA665" s="3"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -20441,7 +20463,7 @@
       <c r="Z666" s="3"/>
       <c r="AA666" s="3"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -20470,7 +20492,7 @@
       <c r="Z667" s="3"/>
       <c r="AA667" s="3"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -20499,7 +20521,7 @@
       <c r="Z668" s="3"/>
       <c r="AA668" s="3"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -20528,7 +20550,7 @@
       <c r="Z669" s="3"/>
       <c r="AA669" s="3"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -20557,7 +20579,7 @@
       <c r="Z670" s="3"/>
       <c r="AA670" s="3"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -20586,7 +20608,7 @@
       <c r="Z671" s="3"/>
       <c r="AA671" s="3"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -20615,7 +20637,7 @@
       <c r="Z672" s="3"/>
       <c r="AA672" s="3"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -20644,7 +20666,7 @@
       <c r="Z673" s="3"/>
       <c r="AA673" s="3"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -20673,7 +20695,7 @@
       <c r="Z674" s="3"/>
       <c r="AA674" s="3"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -20702,7 +20724,7 @@
       <c r="Z675" s="3"/>
       <c r="AA675" s="3"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -20731,7 +20753,7 @@
       <c r="Z676" s="3"/>
       <c r="AA676" s="3"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -20760,7 +20782,7 @@
       <c r="Z677" s="3"/>
       <c r="AA677" s="3"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -20789,7 +20811,7 @@
       <c r="Z678" s="3"/>
       <c r="AA678" s="3"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -20818,7 +20840,7 @@
       <c r="Z679" s="3"/>
       <c r="AA679" s="3"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -20847,7 +20869,7 @@
       <c r="Z680" s="3"/>
       <c r="AA680" s="3"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -20876,7 +20898,7 @@
       <c r="Z681" s="3"/>
       <c r="AA681" s="3"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -20905,7 +20927,7 @@
       <c r="Z682" s="3"/>
       <c r="AA682" s="3"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -20934,7 +20956,7 @@
       <c r="Z683" s="3"/>
       <c r="AA683" s="3"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -20963,7 +20985,7 @@
       <c r="Z684" s="3"/>
       <c r="AA684" s="3"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -20992,7 +21014,7 @@
       <c r="Z685" s="3"/>
       <c r="AA685" s="3"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -21021,7 +21043,7 @@
       <c r="Z686" s="3"/>
       <c r="AA686" s="3"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -21050,7 +21072,7 @@
       <c r="Z687" s="3"/>
       <c r="AA687" s="3"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -21079,7 +21101,7 @@
       <c r="Z688" s="3"/>
       <c r="AA688" s="3"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -21108,7 +21130,7 @@
       <c r="Z689" s="3"/>
       <c r="AA689" s="3"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -21137,7 +21159,7 @@
       <c r="Z690" s="3"/>
       <c r="AA690" s="3"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -21166,7 +21188,7 @@
       <c r="Z691" s="3"/>
       <c r="AA691" s="3"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -21195,7 +21217,7 @@
       <c r="Z692" s="3"/>
       <c r="AA692" s="3"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -21224,7 +21246,7 @@
       <c r="Z693" s="3"/>
       <c r="AA693" s="3"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -21253,7 +21275,7 @@
       <c r="Z694" s="3"/>
       <c r="AA694" s="3"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -21282,7 +21304,7 @@
       <c r="Z695" s="3"/>
       <c r="AA695" s="3"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -21311,7 +21333,7 @@
       <c r="Z696" s="3"/>
       <c r="AA696" s="3"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -21340,7 +21362,7 @@
       <c r="Z697" s="3"/>
       <c r="AA697" s="3"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -21369,7 +21391,7 @@
       <c r="Z698" s="3"/>
       <c r="AA698" s="3"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -21398,7 +21420,7 @@
       <c r="Z699" s="3"/>
       <c r="AA699" s="3"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -21427,7 +21449,7 @@
       <c r="Z700" s="3"/>
       <c r="AA700" s="3"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -21456,7 +21478,7 @@
       <c r="Z701" s="3"/>
       <c r="AA701" s="3"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -21485,7 +21507,7 @@
       <c r="Z702" s="3"/>
       <c r="AA702" s="3"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -21514,7 +21536,7 @@
       <c r="Z703" s="3"/>
       <c r="AA703" s="3"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -21543,7 +21565,7 @@
       <c r="Z704" s="3"/>
       <c r="AA704" s="3"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -21572,7 +21594,7 @@
       <c r="Z705" s="3"/>
       <c r="AA705" s="3"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -21601,7 +21623,7 @@
       <c r="Z706" s="3"/>
       <c r="AA706" s="3"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -21630,7 +21652,7 @@
       <c r="Z707" s="3"/>
       <c r="AA707" s="3"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -21659,7 +21681,7 @@
       <c r="Z708" s="3"/>
       <c r="AA708" s="3"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -21688,7 +21710,7 @@
       <c r="Z709" s="3"/>
       <c r="AA709" s="3"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -21717,7 +21739,7 @@
       <c r="Z710" s="3"/>
       <c r="AA710" s="3"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -21746,7 +21768,7 @@
       <c r="Z711" s="3"/>
       <c r="AA711" s="3"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -21775,7 +21797,7 @@
       <c r="Z712" s="3"/>
       <c r="AA712" s="3"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -21804,7 +21826,7 @@
       <c r="Z713" s="3"/>
       <c r="AA713" s="3"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -21833,7 +21855,7 @@
       <c r="Z714" s="3"/>
       <c r="AA714" s="3"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -21862,7 +21884,7 @@
       <c r="Z715" s="3"/>
       <c r="AA715" s="3"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -21891,7 +21913,7 @@
       <c r="Z716" s="3"/>
       <c r="AA716" s="3"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -21920,7 +21942,7 @@
       <c r="Z717" s="3"/>
       <c r="AA717" s="3"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -21949,7 +21971,7 @@
       <c r="Z718" s="3"/>
       <c r="AA718" s="3"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -21978,7 +22000,7 @@
       <c r="Z719" s="3"/>
       <c r="AA719" s="3"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -22007,7 +22029,7 @@
       <c r="Z720" s="3"/>
       <c r="AA720" s="3"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -22036,7 +22058,7 @@
       <c r="Z721" s="3"/>
       <c r="AA721" s="3"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -22065,7 +22087,7 @@
       <c r="Z722" s="3"/>
       <c r="AA722" s="3"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -22094,7 +22116,7 @@
       <c r="Z723" s="3"/>
       <c r="AA723" s="3"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -22123,7 +22145,7 @@
       <c r="Z724" s="3"/>
       <c r="AA724" s="3"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -22152,7 +22174,7 @@
       <c r="Z725" s="3"/>
       <c r="AA725" s="3"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -22181,7 +22203,7 @@
       <c r="Z726" s="3"/>
       <c r="AA726" s="3"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -22210,7 +22232,7 @@
       <c r="Z727" s="3"/>
       <c r="AA727" s="3"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -22239,7 +22261,7 @@
       <c r="Z728" s="3"/>
       <c r="AA728" s="3"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -22268,7 +22290,7 @@
       <c r="Z729" s="3"/>
       <c r="AA729" s="3"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -22297,7 +22319,7 @@
       <c r="Z730" s="3"/>
       <c r="AA730" s="3"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -22326,7 +22348,7 @@
       <c r="Z731" s="3"/>
       <c r="AA731" s="3"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -22355,7 +22377,7 @@
       <c r="Z732" s="3"/>
       <c r="AA732" s="3"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -22384,7 +22406,7 @@
       <c r="Z733" s="3"/>
       <c r="AA733" s="3"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -22413,7 +22435,7 @@
       <c r="Z734" s="3"/>
       <c r="AA734" s="3"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -22442,7 +22464,7 @@
       <c r="Z735" s="3"/>
       <c r="AA735" s="3"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -22471,7 +22493,7 @@
       <c r="Z736" s="3"/>
       <c r="AA736" s="3"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -22500,7 +22522,7 @@
       <c r="Z737" s="3"/>
       <c r="AA737" s="3"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -22529,7 +22551,7 @@
       <c r="Z738" s="3"/>
       <c r="AA738" s="3"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -22558,7 +22580,7 @@
       <c r="Z739" s="3"/>
       <c r="AA739" s="3"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -22587,7 +22609,7 @@
       <c r="Z740" s="3"/>
       <c r="AA740" s="3"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -22616,7 +22638,7 @@
       <c r="Z741" s="3"/>
       <c r="AA741" s="3"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -22645,7 +22667,7 @@
       <c r="Z742" s="3"/>
       <c r="AA742" s="3"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -22674,7 +22696,7 @@
       <c r="Z743" s="3"/>
       <c r="AA743" s="3"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -22703,7 +22725,7 @@
       <c r="Z744" s="3"/>
       <c r="AA744" s="3"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -22732,7 +22754,7 @@
       <c r="Z745" s="3"/>
       <c r="AA745" s="3"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -22761,7 +22783,7 @@
       <c r="Z746" s="3"/>
       <c r="AA746" s="3"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -22790,7 +22812,7 @@
       <c r="Z747" s="3"/>
       <c r="AA747" s="3"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -22819,7 +22841,7 @@
       <c r="Z748" s="3"/>
       <c r="AA748" s="3"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -22848,7 +22870,7 @@
       <c r="Z749" s="3"/>
       <c r="AA749" s="3"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -22877,7 +22899,7 @@
       <c r="Z750" s="3"/>
       <c r="AA750" s="3"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -22906,7 +22928,7 @@
       <c r="Z751" s="3"/>
       <c r="AA751" s="3"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -22935,7 +22957,7 @@
       <c r="Z752" s="3"/>
       <c r="AA752" s="3"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -22964,7 +22986,7 @@
       <c r="Z753" s="3"/>
       <c r="AA753" s="3"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -22993,7 +23015,7 @@
       <c r="Z754" s="3"/>
       <c r="AA754" s="3"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -23022,7 +23044,7 @@
       <c r="Z755" s="3"/>
       <c r="AA755" s="3"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -23051,7 +23073,7 @@
       <c r="Z756" s="3"/>
       <c r="AA756" s="3"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -23080,7 +23102,7 @@
       <c r="Z757" s="3"/>
       <c r="AA757" s="3"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -23109,7 +23131,7 @@
       <c r="Z758" s="3"/>
       <c r="AA758" s="3"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -23138,7 +23160,7 @@
       <c r="Z759" s="3"/>
       <c r="AA759" s="3"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -23167,7 +23189,7 @@
       <c r="Z760" s="3"/>
       <c r="AA760" s="3"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -23196,7 +23218,7 @@
       <c r="Z761" s="3"/>
       <c r="AA761" s="3"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -23225,7 +23247,7 @@
       <c r="Z762" s="3"/>
       <c r="AA762" s="3"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -23254,7 +23276,7 @@
       <c r="Z763" s="3"/>
       <c r="AA763" s="3"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -23283,7 +23305,7 @@
       <c r="Z764" s="3"/>
       <c r="AA764" s="3"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -23312,7 +23334,7 @@
       <c r="Z765" s="3"/>
       <c r="AA765" s="3"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -23341,7 +23363,7 @@
       <c r="Z766" s="3"/>
       <c r="AA766" s="3"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -23370,7 +23392,7 @@
       <c r="Z767" s="3"/>
       <c r="AA767" s="3"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -23399,7 +23421,7 @@
       <c r="Z768" s="3"/>
       <c r="AA768" s="3"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -23428,7 +23450,7 @@
       <c r="Z769" s="3"/>
       <c r="AA769" s="3"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -23457,7 +23479,7 @@
       <c r="Z770" s="3"/>
       <c r="AA770" s="3"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -23486,7 +23508,7 @@
       <c r="Z771" s="3"/>
       <c r="AA771" s="3"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -23515,7 +23537,7 @@
       <c r="Z772" s="3"/>
       <c r="AA772" s="3"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -23544,7 +23566,7 @@
       <c r="Z773" s="3"/>
       <c r="AA773" s="3"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -23573,7 +23595,7 @@
       <c r="Z774" s="3"/>
       <c r="AA774" s="3"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -23602,7 +23624,7 @@
       <c r="Z775" s="3"/>
       <c r="AA775" s="3"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -23631,7 +23653,7 @@
       <c r="Z776" s="3"/>
       <c r="AA776" s="3"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -23660,7 +23682,7 @@
       <c r="Z777" s="3"/>
       <c r="AA777" s="3"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -23689,7 +23711,7 @@
       <c r="Z778" s="3"/>
       <c r="AA778" s="3"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -23718,7 +23740,7 @@
       <c r="Z779" s="3"/>
       <c r="AA779" s="3"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -23747,7 +23769,7 @@
       <c r="Z780" s="3"/>
       <c r="AA780" s="3"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -23776,7 +23798,7 @@
       <c r="Z781" s="3"/>
       <c r="AA781" s="3"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -23805,7 +23827,7 @@
       <c r="Z782" s="3"/>
       <c r="AA782" s="3"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -23834,7 +23856,7 @@
       <c r="Z783" s="3"/>
       <c r="AA783" s="3"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -23863,7 +23885,7 @@
       <c r="Z784" s="3"/>
       <c r="AA784" s="3"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -23892,7 +23914,7 @@
       <c r="Z785" s="3"/>
       <c r="AA785" s="3"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -23921,7 +23943,7 @@
       <c r="Z786" s="3"/>
       <c r="AA786" s="3"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -23950,7 +23972,7 @@
       <c r="Z787" s="3"/>
       <c r="AA787" s="3"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -23979,7 +24001,7 @@
       <c r="Z788" s="3"/>
       <c r="AA788" s="3"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -24008,7 +24030,7 @@
       <c r="Z789" s="3"/>
       <c r="AA789" s="3"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -24037,7 +24059,7 @@
       <c r="Z790" s="3"/>
       <c r="AA790" s="3"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -24066,7 +24088,7 @@
       <c r="Z791" s="3"/>
       <c r="AA791" s="3"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -24095,7 +24117,7 @@
       <c r="Z792" s="3"/>
       <c r="AA792" s="3"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -24124,7 +24146,7 @@
       <c r="Z793" s="3"/>
       <c r="AA793" s="3"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -24153,7 +24175,7 @@
       <c r="Z794" s="3"/>
       <c r="AA794" s="3"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -24182,7 +24204,7 @@
       <c r="Z795" s="3"/>
       <c r="AA795" s="3"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -24211,7 +24233,7 @@
       <c r="Z796" s="3"/>
       <c r="AA796" s="3"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -24240,7 +24262,7 @@
       <c r="Z797" s="3"/>
       <c r="AA797" s="3"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -24269,7 +24291,7 @@
       <c r="Z798" s="3"/>
       <c r="AA798" s="3"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -24298,7 +24320,7 @@
       <c r="Z799" s="3"/>
       <c r="AA799" s="3"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -24327,7 +24349,7 @@
       <c r="Z800" s="3"/>
       <c r="AA800" s="3"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -24356,7 +24378,7 @@
       <c r="Z801" s="3"/>
       <c r="AA801" s="3"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -24385,7 +24407,7 @@
       <c r="Z802" s="3"/>
       <c r="AA802" s="3"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -24414,7 +24436,7 @@
       <c r="Z803" s="3"/>
       <c r="AA803" s="3"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -24443,7 +24465,7 @@
       <c r="Z804" s="3"/>
       <c r="AA804" s="3"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -24472,7 +24494,7 @@
       <c r="Z805" s="3"/>
       <c r="AA805" s="3"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -24501,7 +24523,7 @@
       <c r="Z806" s="3"/>
       <c r="AA806" s="3"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -24530,7 +24552,7 @@
       <c r="Z807" s="3"/>
       <c r="AA807" s="3"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -24559,7 +24581,7 @@
       <c r="Z808" s="3"/>
       <c r="AA808" s="3"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -24588,7 +24610,7 @@
       <c r="Z809" s="3"/>
       <c r="AA809" s="3"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -24617,7 +24639,7 @@
       <c r="Z810" s="3"/>
       <c r="AA810" s="3"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -24646,7 +24668,7 @@
       <c r="Z811" s="3"/>
       <c r="AA811" s="3"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -24675,7 +24697,7 @@
       <c r="Z812" s="3"/>
       <c r="AA812" s="3"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -24704,7 +24726,7 @@
       <c r="Z813" s="3"/>
       <c r="AA813" s="3"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -24733,7 +24755,7 @@
       <c r="Z814" s="3"/>
       <c r="AA814" s="3"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -24762,7 +24784,7 @@
       <c r="Z815" s="3"/>
       <c r="AA815" s="3"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -24791,7 +24813,7 @@
       <c r="Z816" s="3"/>
       <c r="AA816" s="3"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -24820,7 +24842,7 @@
       <c r="Z817" s="3"/>
       <c r="AA817" s="3"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -24849,7 +24871,7 @@
       <c r="Z818" s="3"/>
       <c r="AA818" s="3"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -24878,7 +24900,7 @@
       <c r="Z819" s="3"/>
       <c r="AA819" s="3"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -24907,7 +24929,7 @@
       <c r="Z820" s="3"/>
       <c r="AA820" s="3"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -24936,7 +24958,7 @@
       <c r="Z821" s="3"/>
       <c r="AA821" s="3"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -24965,7 +24987,7 @@
       <c r="Z822" s="3"/>
       <c r="AA822" s="3"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -24994,7 +25016,7 @@
       <c r="Z823" s="3"/>
       <c r="AA823" s="3"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -25023,7 +25045,7 @@
       <c r="Z824" s="3"/>
       <c r="AA824" s="3"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -25052,7 +25074,7 @@
       <c r="Z825" s="3"/>
       <c r="AA825" s="3"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -25081,7 +25103,7 @@
       <c r="Z826" s="3"/>
       <c r="AA826" s="3"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -25110,7 +25132,7 @@
       <c r="Z827" s="3"/>
       <c r="AA827" s="3"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -25139,7 +25161,7 @@
       <c r="Z828" s="3"/>
       <c r="AA828" s="3"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -25168,7 +25190,7 @@
       <c r="Z829" s="3"/>
       <c r="AA829" s="3"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -25197,7 +25219,7 @@
       <c r="Z830" s="3"/>
       <c r="AA830" s="3"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -25226,7 +25248,7 @@
       <c r="Z831" s="3"/>
       <c r="AA831" s="3"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -25255,7 +25277,7 @@
       <c r="Z832" s="3"/>
       <c r="AA832" s="3"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -25284,7 +25306,7 @@
       <c r="Z833" s="3"/>
       <c r="AA833" s="3"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -25313,7 +25335,7 @@
       <c r="Z834" s="3"/>
       <c r="AA834" s="3"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -25342,7 +25364,7 @@
       <c r="Z835" s="3"/>
       <c r="AA835" s="3"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -25371,7 +25393,7 @@
       <c r="Z836" s="3"/>
       <c r="AA836" s="3"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -25400,7 +25422,7 @@
       <c r="Z837" s="3"/>
       <c r="AA837" s="3"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -25429,7 +25451,7 @@
       <c r="Z838" s="3"/>
       <c r="AA838" s="3"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -25458,7 +25480,7 @@
       <c r="Z839" s="3"/>
       <c r="AA839" s="3"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -25487,7 +25509,7 @@
       <c r="Z840" s="3"/>
       <c r="AA840" s="3"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -25516,7 +25538,7 @@
       <c r="Z841" s="3"/>
       <c r="AA841" s="3"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -25545,7 +25567,7 @@
       <c r="Z842" s="3"/>
       <c r="AA842" s="3"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -25574,7 +25596,7 @@
       <c r="Z843" s="3"/>
       <c r="AA843" s="3"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -25603,7 +25625,7 @@
       <c r="Z844" s="3"/>
       <c r="AA844" s="3"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -25632,7 +25654,7 @@
       <c r="Z845" s="3"/>
       <c r="AA845" s="3"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -25661,7 +25683,7 @@
       <c r="Z846" s="3"/>
       <c r="AA846" s="3"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -25690,7 +25712,7 @@
       <c r="Z847" s="3"/>
       <c r="AA847" s="3"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -25719,7 +25741,7 @@
       <c r="Z848" s="3"/>
       <c r="AA848" s="3"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -25748,7 +25770,7 @@
       <c r="Z849" s="3"/>
       <c r="AA849" s="3"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -25777,7 +25799,7 @@
       <c r="Z850" s="3"/>
       <c r="AA850" s="3"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -25806,7 +25828,7 @@
       <c r="Z851" s="3"/>
       <c r="AA851" s="3"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -25835,7 +25857,7 @@
       <c r="Z852" s="3"/>
       <c r="AA852" s="3"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -25864,7 +25886,7 @@
       <c r="Z853" s="3"/>
       <c r="AA853" s="3"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -25893,7 +25915,7 @@
       <c r="Z854" s="3"/>
       <c r="AA854" s="3"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -25922,7 +25944,7 @@
       <c r="Z855" s="3"/>
       <c r="AA855" s="3"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -25951,7 +25973,7 @@
       <c r="Z856" s="3"/>
       <c r="AA856" s="3"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -25980,7 +26002,7 @@
       <c r="Z857" s="3"/>
       <c r="AA857" s="3"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -26009,7 +26031,7 @@
       <c r="Z858" s="3"/>
       <c r="AA858" s="3"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -26038,7 +26060,7 @@
       <c r="Z859" s="3"/>
       <c r="AA859" s="3"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -26067,7 +26089,7 @@
       <c r="Z860" s="3"/>
       <c r="AA860" s="3"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -26096,7 +26118,7 @@
       <c r="Z861" s="3"/>
       <c r="AA861" s="3"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -26125,7 +26147,7 @@
       <c r="Z862" s="3"/>
       <c r="AA862" s="3"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -26154,7 +26176,7 @@
       <c r="Z863" s="3"/>
       <c r="AA863" s="3"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -26183,7 +26205,7 @@
       <c r="Z864" s="3"/>
       <c r="AA864" s="3"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -26212,7 +26234,7 @@
       <c r="Z865" s="3"/>
       <c r="AA865" s="3"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -26241,7 +26263,7 @@
       <c r="Z866" s="3"/>
       <c r="AA866" s="3"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -26270,7 +26292,7 @@
       <c r="Z867" s="3"/>
       <c r="AA867" s="3"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -26299,7 +26321,7 @@
       <c r="Z868" s="3"/>
       <c r="AA868" s="3"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -26328,7 +26350,7 @@
       <c r="Z869" s="3"/>
       <c r="AA869" s="3"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -26357,7 +26379,7 @@
       <c r="Z870" s="3"/>
       <c r="AA870" s="3"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -26386,7 +26408,7 @@
       <c r="Z871" s="3"/>
       <c r="AA871" s="3"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -26415,7 +26437,7 @@
       <c r="Z872" s="3"/>
       <c r="AA872" s="3"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -26444,7 +26466,7 @@
       <c r="Z873" s="3"/>
       <c r="AA873" s="3"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -26473,7 +26495,7 @@
       <c r="Z874" s="3"/>
       <c r="AA874" s="3"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -26502,7 +26524,7 @@
       <c r="Z875" s="3"/>
       <c r="AA875" s="3"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -26531,7 +26553,7 @@
       <c r="Z876" s="3"/>
       <c r="AA876" s="3"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -26560,7 +26582,7 @@
       <c r="Z877" s="3"/>
       <c r="AA877" s="3"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -26589,7 +26611,7 @@
       <c r="Z878" s="3"/>
       <c r="AA878" s="3"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -26618,7 +26640,7 @@
       <c r="Z879" s="3"/>
       <c r="AA879" s="3"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -26647,7 +26669,7 @@
       <c r="Z880" s="3"/>
       <c r="AA880" s="3"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -26676,7 +26698,7 @@
       <c r="Z881" s="3"/>
       <c r="AA881" s="3"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -26705,7 +26727,7 @@
       <c r="Z882" s="3"/>
       <c r="AA882" s="3"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -26734,7 +26756,7 @@
       <c r="Z883" s="3"/>
       <c r="AA883" s="3"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -26763,7 +26785,7 @@
       <c r="Z884" s="3"/>
       <c r="AA884" s="3"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -26792,7 +26814,7 @@
       <c r="Z885" s="3"/>
       <c r="AA885" s="3"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -26821,7 +26843,7 @@
       <c r="Z886" s="3"/>
       <c r="AA886" s="3"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -26850,7 +26872,7 @@
       <c r="Z887" s="3"/>
       <c r="AA887" s="3"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -26879,7 +26901,7 @@
       <c r="Z888" s="3"/>
       <c r="AA888" s="3"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -26908,7 +26930,7 @@
       <c r="Z889" s="3"/>
       <c r="AA889" s="3"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -26937,7 +26959,7 @@
       <c r="Z890" s="3"/>
       <c r="AA890" s="3"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -26966,7 +26988,7 @@
       <c r="Z891" s="3"/>
       <c r="AA891" s="3"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -26995,7 +27017,7 @@
       <c r="Z892" s="3"/>
       <c r="AA892" s="3"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -27024,7 +27046,7 @@
       <c r="Z893" s="3"/>
       <c r="AA893" s="3"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -27053,7 +27075,7 @@
       <c r="Z894" s="3"/>
       <c r="AA894" s="3"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -27082,7 +27104,7 @@
       <c r="Z895" s="3"/>
       <c r="AA895" s="3"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -27111,7 +27133,7 @@
       <c r="Z896" s="3"/>
       <c r="AA896" s="3"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -27140,7 +27162,7 @@
       <c r="Z897" s="3"/>
       <c r="AA897" s="3"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -27169,7 +27191,7 @@
       <c r="Z898" s="3"/>
       <c r="AA898" s="3"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -27198,7 +27220,7 @@
       <c r="Z899" s="3"/>
       <c r="AA899" s="3"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -27227,7 +27249,7 @@
       <c r="Z900" s="3"/>
       <c r="AA900" s="3"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -27256,7 +27278,7 @@
       <c r="Z901" s="3"/>
       <c r="AA901" s="3"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -27285,7 +27307,7 @@
       <c r="Z902" s="3"/>
       <c r="AA902" s="3"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -27314,7 +27336,7 @@
       <c r="Z903" s="3"/>
       <c r="AA903" s="3"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -27343,7 +27365,7 @@
       <c r="Z904" s="3"/>
       <c r="AA904" s="3"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -27372,7 +27394,7 @@
       <c r="Z905" s="3"/>
       <c r="AA905" s="3"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -27401,7 +27423,7 @@
       <c r="Z906" s="3"/>
       <c r="AA906" s="3"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -27430,7 +27452,7 @@
       <c r="Z907" s="3"/>
       <c r="AA907" s="3"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -27459,7 +27481,7 @@
       <c r="Z908" s="3"/>
       <c r="AA908" s="3"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -27488,7 +27510,7 @@
       <c r="Z909" s="3"/>
       <c r="AA909" s="3"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -27517,7 +27539,7 @@
       <c r="Z910" s="3"/>
       <c r="AA910" s="3"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -27546,7 +27568,7 @@
       <c r="Z911" s="3"/>
       <c r="AA911" s="3"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -27575,7 +27597,7 @@
       <c r="Z912" s="3"/>
       <c r="AA912" s="3"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -27604,7 +27626,7 @@
       <c r="Z913" s="3"/>
       <c r="AA913" s="3"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -27633,7 +27655,7 @@
       <c r="Z914" s="3"/>
       <c r="AA914" s="3"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -27662,7 +27684,7 @@
       <c r="Z915" s="3"/>
       <c r="AA915" s="3"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -27691,7 +27713,7 @@
       <c r="Z916" s="3"/>
       <c r="AA916" s="3"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -27720,7 +27742,7 @@
       <c r="Z917" s="3"/>
       <c r="AA917" s="3"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -27749,7 +27771,7 @@
       <c r="Z918" s="3"/>
       <c r="AA918" s="3"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -27778,7 +27800,7 @@
       <c r="Z919" s="3"/>
       <c r="AA919" s="3"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -27807,7 +27829,7 @@
       <c r="Z920" s="3"/>
       <c r="AA920" s="3"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -27836,7 +27858,7 @@
       <c r="Z921" s="3"/>
       <c r="AA921" s="3"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -27865,7 +27887,7 @@
       <c r="Z922" s="3"/>
       <c r="AA922" s="3"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -27894,7 +27916,7 @@
       <c r="Z923" s="3"/>
       <c r="AA923" s="3"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -27923,7 +27945,7 @@
       <c r="Z924" s="3"/>
       <c r="AA924" s="3"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -27952,7 +27974,7 @@
       <c r="Z925" s="3"/>
       <c r="AA925" s="3"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -27981,7 +28003,7 @@
       <c r="Z926" s="3"/>
       <c r="AA926" s="3"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -28010,7 +28032,7 @@
       <c r="Z927" s="3"/>
       <c r="AA927" s="3"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -28039,7 +28061,7 @@
       <c r="Z928" s="3"/>
       <c r="AA928" s="3"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -28068,7 +28090,7 @@
       <c r="Z929" s="3"/>
       <c r="AA929" s="3"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -28097,7 +28119,7 @@
       <c r="Z930" s="3"/>
       <c r="AA930" s="3"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -28126,7 +28148,7 @@
       <c r="Z931" s="3"/>
       <c r="AA931" s="3"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -28155,7 +28177,7 @@
       <c r="Z932" s="3"/>
       <c r="AA932" s="3"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -28184,7 +28206,7 @@
       <c r="Z933" s="3"/>
       <c r="AA933" s="3"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -28213,7 +28235,7 @@
       <c r="Z934" s="3"/>
       <c r="AA934" s="3"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -28242,7 +28264,7 @@
       <c r="Z935" s="3"/>
       <c r="AA935" s="3"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -28271,7 +28293,7 @@
       <c r="Z936" s="3"/>
       <c r="AA936" s="3"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -28300,7 +28322,7 @@
       <c r="Z937" s="3"/>
       <c r="AA937" s="3"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -28329,7 +28351,7 @@
       <c r="Z938" s="3"/>
       <c r="AA938" s="3"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -28358,7 +28380,7 @@
       <c r="Z939" s="3"/>
       <c r="AA939" s="3"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -28387,7 +28409,7 @@
       <c r="Z940" s="3"/>
       <c r="AA940" s="3"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -28416,7 +28438,7 @@
       <c r="Z941" s="3"/>
       <c r="AA941" s="3"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -28445,7 +28467,7 @@
       <c r="Z942" s="3"/>
       <c r="AA942" s="3"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -28474,7 +28496,7 @@
       <c r="Z943" s="3"/>
       <c r="AA943" s="3"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -28503,7 +28525,7 @@
       <c r="Z944" s="3"/>
       <c r="AA944" s="3"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -28532,7 +28554,7 @@
       <c r="Z945" s="3"/>
       <c r="AA945" s="3"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -28561,7 +28583,7 @@
       <c r="Z946" s="3"/>
       <c r="AA946" s="3"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -28590,7 +28612,7 @@
       <c r="Z947" s="3"/>
       <c r="AA947" s="3"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -28619,7 +28641,7 @@
       <c r="Z948" s="3"/>
       <c r="AA948" s="3"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -28648,7 +28670,7 @@
       <c r="Z949" s="3"/>
       <c r="AA949" s="3"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -28677,7 +28699,7 @@
       <c r="Z950" s="3"/>
       <c r="AA950" s="3"/>
     </row>
-    <row r="951">
+    <row r="951" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -28706,7 +28728,7 @@
       <c r="Z951" s="3"/>
       <c r="AA951" s="3"/>
     </row>
-    <row r="952">
+    <row r="952" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -28735,7 +28757,7 @@
       <c r="Z952" s="3"/>
       <c r="AA952" s="3"/>
     </row>
-    <row r="953">
+    <row r="953" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -28764,7 +28786,7 @@
       <c r="Z953" s="3"/>
       <c r="AA953" s="3"/>
     </row>
-    <row r="954">
+    <row r="954" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -28794,6 +28816,7 @@
       <c r="AA954" s="3"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Week_7/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_7/Capstone Timesheet_Ripal Patel.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\HealthCare Plus\Week_7\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380"/>
-  </bookViews>
   <sheets>
-    <sheet name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
   <si>
     <t>Week_1</t>
   </si>
@@ -195,69 +187,72 @@
     <t>Worked on homepage UI improvements including navbar hover effects, updated Register button to primary blue, refined hero section layout and styling, adjusted text colors, and improved overall visual clarity.</t>
   </si>
   <si>
+    <t>Completed Home page (Hero section)</t>
+  </si>
+  <si>
     <t>Completed Home page (Services section)</t>
   </si>
   <si>
-    <t>Completed Home page (Hero section)</t>
+    <t>Completed Home page (Footer section)</t>
   </si>
   <si>
-    <t>Completed Home page (Footer section)</t>
+    <t>Revised User Testing Report</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="165" formatCode="d\-mmm"/>
+    <numFmt numFmtId="164" formatCode="dd-mmm"/>
+    <numFmt numFmtId="165" formatCode="d-mmm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -267,7 +262,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -331,13 +326,7 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -351,200 +340,220 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="67">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="2" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="2" fillId="7" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="2" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -552,7 +561,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -742,26 +751,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA954"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="62.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.0"/>
+    <col customWidth="1" min="2" max="2" width="62.25"/>
+    <col customWidth="1" min="3" max="3" width="12.25"/>
+    <col customWidth="1" min="4" max="4" width="12.13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -798,13 +804,13 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D2" s="6">
         <v>1.3</v>
@@ -833,13 +839,13 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D3" s="6">
         <v>0.15</v>
@@ -868,16 +874,16 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -903,16 +909,16 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D5" s="4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -938,13 +944,13 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D6" s="4">
         <v>4.75</v>
@@ -973,13 +979,13 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D7" s="4">
         <v>3.5</v>
@@ -1008,13 +1014,13 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D8" s="4">
         <v>5.75</v>
@@ -1043,16 +1049,16 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="D9" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1078,13 +1084,13 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="5">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="D10" s="4">
         <v>5.5</v>
@@ -1113,13 +1119,13 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>46041</v>
+        <v>46041.0</v>
       </c>
       <c r="D11" s="4">
         <v>4.75</v>
@@ -1148,13 +1154,13 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="5">
-        <v>46043</v>
+        <v>46043.0</v>
       </c>
       <c r="D12" s="4">
         <v>4.75</v>
@@ -1183,7 +1189,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1212,14 +1218,14 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="7">
-        <f>SUM(D2:D12)</f>
+        <f>sum(D2:D12)</f>
         <v>38.6</v>
       </c>
       <c r="E14" s="2"/>
@@ -1246,7 +1252,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1275,7 +1281,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1304,7 +1310,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17">
       <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
@@ -1341,13 +1347,13 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D18" s="13">
         <v>1.5</v>
@@ -1376,16 +1382,16 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D19" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1411,16 +1417,16 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D20" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1446,16 +1452,16 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="12">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="D21" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1481,16 +1487,16 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="12">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="D22" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1516,13 +1522,13 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D23" s="13">
         <v>1.5</v>
@@ -1551,13 +1557,13 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D24" s="13">
         <v>2.5</v>
@@ -1586,16 +1592,16 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D25" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1621,13 +1627,13 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D26" s="13">
         <v>1.75</v>
@@ -1656,16 +1662,16 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
     </row>
-    <row r="27" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D27" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1691,13 +1697,13 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
     </row>
-    <row r="28" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D28" s="13">
         <v>2.75</v>
@@ -1726,16 +1732,16 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D29" s="17">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1761,16 +1767,16 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
     </row>
-    <row r="30" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D30" s="17">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1796,16 +1802,16 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
     </row>
-    <row r="31" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D31" s="17">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1831,13 +1837,13 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
     </row>
-    <row r="32" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="16">
-        <v>46049</v>
+        <v>46049.0</v>
       </c>
       <c r="D32" s="17">
         <v>2.5</v>
@@ -1866,13 +1872,13 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
     </row>
-    <row r="33" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="14"/>
       <c r="B33" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="19">
-        <v>46049</v>
+        <v>46049.0</v>
       </c>
       <c r="D33" s="20">
         <v>3.75</v>
@@ -1901,14 +1907,14 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
     </row>
-    <row r="34" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="21">
-        <f>SUM(D18:D33)</f>
+        <f>sum(D18:D33)</f>
         <v>33.4</v>
       </c>
       <c r="E34" s="2"/>
@@ -1935,7 +1941,7 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
     </row>
-    <row r="35" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1964,7 +1970,7 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
     </row>
-    <row r="36" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1993,7 +1999,7 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
     </row>
-    <row r="37" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="23" t="s">
         <v>33</v>
       </c>
@@ -2030,13 +2036,13 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
     </row>
-    <row r="38" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="24"/>
       <c r="B38" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D38" s="27">
         <v>1.5</v>
@@ -2065,13 +2071,13 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
     </row>
-    <row r="39" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="24"/>
       <c r="B39" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D39" s="27">
         <v>1.75</v>
@@ -2100,13 +2106,13 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
     </row>
-    <row r="40" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="24"/>
       <c r="B40" s="25" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D40" s="27">
         <v>2.15</v>
@@ -2135,13 +2141,13 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
     </row>
-    <row r="41" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="24"/>
       <c r="B41" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="26">
-        <v>46054</v>
+        <v>46054.0</v>
       </c>
       <c r="D41" s="27">
         <v>2.75</v>
@@ -2170,13 +2176,13 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
     </row>
-    <row r="42" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="24"/>
       <c r="B42" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="26">
-        <v>46055</v>
+        <v>46055.0</v>
       </c>
       <c r="D42" s="27">
         <v>3.75</v>
@@ -2205,7 +2211,7 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
     </row>
-    <row r="43" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2234,14 +2240,14 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
     </row>
-    <row r="44" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="24">
-        <f>SUM(D38:D42)</f>
+        <f>sum(D38:D42)</f>
         <v>11.9</v>
       </c>
       <c r="E44" s="3"/>
@@ -2268,7 +2274,7 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
     </row>
-    <row r="45" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2297,7 +2303,7 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
     </row>
-    <row r="46" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2326,7 +2332,7 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
     </row>
-    <row r="47" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="31" t="s">
         <v>39</v>
       </c>
@@ -2363,13 +2369,13 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
     </row>
-    <row r="48" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="32"/>
       <c r="B48" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="34">
-        <v>46059</v>
+        <v>46059.0</v>
       </c>
       <c r="D48" s="35">
         <v>3.75</v>
@@ -2398,13 +2404,13 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3"/>
     </row>
-    <row r="49" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="32"/>
       <c r="B49" s="33" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="34">
-        <v>46061</v>
+        <v>46061.0</v>
       </c>
       <c r="D49" s="35">
         <v>3.25</v>
@@ -2433,13 +2439,13 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
     </row>
-    <row r="50" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="32"/>
       <c r="B50" s="33" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="34">
-        <v>46061</v>
+        <v>46061.0</v>
       </c>
       <c r="D50" s="35">
         <v>4.5</v>
@@ -2468,13 +2474,13 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
     </row>
-    <row r="51" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51" s="32"/>
       <c r="B51" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="34">
-        <v>46062</v>
+        <v>46062.0</v>
       </c>
       <c r="D51" s="35">
         <v>3.75</v>
@@ -2503,13 +2509,13 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3"/>
     </row>
-    <row r="52" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="32"/>
       <c r="B52" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="34">
-        <v>46063</v>
+        <v>46063.0</v>
       </c>
       <c r="D52" s="35">
         <v>3.5</v>
@@ -2538,7 +2544,7 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3"/>
     </row>
-    <row r="53" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2567,14 +2573,14 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3"/>
     </row>
-    <row r="54" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="36"/>
       <c r="B54" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="39">
-        <f>SUM(D48:D52)</f>
+        <f>sum(D48:D52)</f>
         <v>18.75</v>
       </c>
       <c r="E54" s="3"/>
@@ -2601,7 +2607,7 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
     </row>
-    <row r="55" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2630,7 +2636,7 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
     </row>
-    <row r="56" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2659,7 +2665,7 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
     </row>
-    <row r="57" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="40" t="s">
         <v>45</v>
       </c>
@@ -2696,13 +2702,13 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3"/>
     </row>
-    <row r="58" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="41"/>
       <c r="B58" s="42" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="43">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="D58" s="44">
         <v>2.15</v>
@@ -2731,13 +2737,13 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3"/>
     </row>
-    <row r="59" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="41"/>
       <c r="B59" s="42" t="s">
         <v>47</v>
       </c>
       <c r="C59" s="43">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="D59" s="44">
         <v>3.75</v>
@@ -2766,13 +2772,13 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3"/>
     </row>
-    <row r="60" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="41"/>
       <c r="B60" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="43">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="D60" s="44">
         <v>3.5</v>
@@ -2801,13 +2807,13 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3"/>
     </row>
-    <row r="61" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="41"/>
       <c r="B61" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="43">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="D61" s="44">
         <v>2.5</v>
@@ -2836,7 +2842,7 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3"/>
     </row>
-    <row r="62" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2865,14 +2871,14 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3"/>
     </row>
-    <row r="63" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="45"/>
       <c r="B63" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="47"/>
       <c r="D63" s="41">
-        <f>SUM(D58:D61)</f>
+        <f>sum(D58:D61)</f>
         <v>11.9</v>
       </c>
       <c r="E63" s="3"/>
@@ -2899,7 +2905,7 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3"/>
     </row>
-    <row r="64" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2928,7 +2934,7 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3"/>
     </row>
-    <row r="65" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2957,7 +2963,7 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
     </row>
-    <row r="66" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66" s="48" t="s">
         <v>50</v>
       </c>
@@ -2994,13 +3000,13 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
-    <row r="67" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67" s="49"/>
       <c r="B67" s="50" t="s">
         <v>51</v>
       </c>
       <c r="C67" s="51">
-        <v>46073</v>
+        <v>46073.0</v>
       </c>
       <c r="D67" s="52">
         <v>1.75</v>
@@ -3029,16 +3035,16 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
     </row>
-    <row r="68" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68" s="49"/>
       <c r="B68" s="50" t="s">
         <v>52</v>
       </c>
       <c r="C68" s="51">
-        <v>46074</v>
+        <v>46074.0</v>
       </c>
       <c r="D68" s="52">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
@@ -3063,13 +3069,13 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3"/>
     </row>
-    <row r="69" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69" s="49"/>
       <c r="B69" s="50" t="s">
         <v>53</v>
       </c>
       <c r="C69" s="51">
-        <v>46075</v>
+        <v>46075.0</v>
       </c>
       <c r="D69" s="52">
         <v>0.25</v>
@@ -3098,13 +3104,13 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3"/>
     </row>
-    <row r="70" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70" s="49"/>
       <c r="B70" s="50" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="51">
-        <v>46076</v>
+        <v>46076.0</v>
       </c>
       <c r="D70" s="52">
         <v>1.75</v>
@@ -3133,13 +3139,13 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3"/>
     </row>
-    <row r="71" spans="1:27" ht="62" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="49"/>
       <c r="B71" s="53" t="s">
         <v>55</v>
       </c>
       <c r="C71" s="51">
-        <v>46076</v>
+        <v>46076.0</v>
       </c>
       <c r="D71" s="52">
         <v>3.75</v>
@@ -3168,7 +3174,7 @@
       <c r="Z71" s="3"/>
       <c r="AA71" s="3"/>
     </row>
-    <row r="72" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3197,14 +3203,14 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3"/>
     </row>
-    <row r="73" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="54"/>
       <c r="B73" s="55" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="56"/>
       <c r="D73" s="49">
-        <f>SUM(D67:D71)</f>
+        <f>sum(D67:D71)</f>
         <v>9.5</v>
       </c>
       <c r="E73" s="3"/>
@@ -3231,7 +3237,7 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3"/>
     </row>
-    <row r="74" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3260,7 +3266,7 @@
       <c r="Z74" s="3"/>
       <c r="AA74" s="3"/>
     </row>
-    <row r="75" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3289,7 +3295,7 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3"/>
     </row>
-    <row r="76" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76" s="57" t="s">
         <v>56</v>
       </c>
@@ -3326,13 +3332,13 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
     </row>
-    <row r="77" spans="1:27" ht="62" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77" s="58"/>
       <c r="B77" s="59" t="s">
         <v>57</v>
       </c>
       <c r="C77" s="60">
-        <v>46080</v>
+        <v>46080.0</v>
       </c>
       <c r="D77" s="61">
         <v>3.75</v>
@@ -3361,16 +3367,16 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
     </row>
-    <row r="78" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78" s="58"/>
       <c r="B78" s="62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C78" s="60">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
       <c r="D78" s="61">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -3396,16 +3402,16 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3"/>
     </row>
-    <row r="79" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79" s="58"/>
       <c r="B79" s="62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C79" s="60">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
       <c r="D79" s="61">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -3431,15 +3437,17 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
     </row>
-    <row r="80" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80" s="58"/>
       <c r="B80" s="62" t="s">
         <v>60</v>
       </c>
       <c r="C80" s="60">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
-      <c r="D80" s="61"/>
+      <c r="D80" s="61">
+        <v>0.45</v>
+      </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -3464,11 +3472,17 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3"/>
     </row>
-    <row r="81" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81" s="58"/>
-      <c r="B81" s="59"/>
-      <c r="C81" s="60"/>
-      <c r="D81" s="61"/>
+      <c r="B81" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="C81" s="60">
+        <v>46082.0</v>
+      </c>
+      <c r="D81" s="61">
+        <v>2.5</v>
+      </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -3493,7 +3507,7 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3"/>
     </row>
-    <row r="82" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82" s="63"/>
       <c r="B82" s="63"/>
       <c r="C82" s="63"/>
@@ -3522,15 +3536,15 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
     </row>
-    <row r="83" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83" s="64"/>
       <c r="B83" s="65" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="66"/>
       <c r="D83" s="58">
-        <f>SUM(D77:D81)</f>
-        <v>9.75</v>
+        <f>sum(D77:D81)</f>
+        <v>10.6</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -3556,7 +3570,7 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3"/>
     </row>
-    <row r="84" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3585,7 +3599,7 @@
       <c r="Z84" s="3"/>
       <c r="AA84" s="3"/>
     </row>
-    <row r="85" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3614,7 +3628,7 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3"/>
     </row>
-    <row r="86" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3643,7 +3657,7 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3"/>
     </row>
-    <row r="87" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3672,7 +3686,7 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3"/>
     </row>
-    <row r="88" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3701,7 +3715,7 @@
       <c r="Z88" s="3"/>
       <c r="AA88" s="3"/>
     </row>
-    <row r="89" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3730,7 +3744,7 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3"/>
     </row>
-    <row r="90" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3759,7 +3773,7 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
     </row>
-    <row r="91" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3788,7 +3802,7 @@
       <c r="Z91" s="3"/>
       <c r="AA91" s="3"/>
     </row>
-    <row r="92" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3817,7 +3831,7 @@
       <c r="Z92" s="3"/>
       <c r="AA92" s="3"/>
     </row>
-    <row r="93" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3846,7 +3860,7 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3"/>
     </row>
-    <row r="94" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3875,7 +3889,7 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3"/>
     </row>
-    <row r="95" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3904,7 +3918,7 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
     </row>
-    <row r="96" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3933,7 +3947,7 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
     </row>
-    <row r="97" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3962,7 +3976,7 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
     </row>
-    <row r="98" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3991,7 +4005,7 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
     </row>
-    <row r="99" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -4020,7 +4034,7 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
     </row>
-    <row r="100" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="100">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4049,7 +4063,7 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
     </row>
-    <row r="101" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4078,7 +4092,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
     </row>
-    <row r="102" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="102">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4107,7 +4121,7 @@
       <c r="Z102" s="3"/>
       <c r="AA102" s="3"/>
     </row>
-    <row r="103" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="103">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4136,7 +4150,7 @@
       <c r="Z103" s="3"/>
       <c r="AA103" s="3"/>
     </row>
-    <row r="104" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4165,7 +4179,7 @@
       <c r="Z104" s="3"/>
       <c r="AA104" s="3"/>
     </row>
-    <row r="105" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4194,7 +4208,7 @@
       <c r="Z105" s="3"/>
       <c r="AA105" s="3"/>
     </row>
-    <row r="106" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4223,7 +4237,7 @@
       <c r="Z106" s="3"/>
       <c r="AA106" s="3"/>
     </row>
-    <row r="107" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="107">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4252,7 +4266,7 @@
       <c r="Z107" s="3"/>
       <c r="AA107" s="3"/>
     </row>
-    <row r="108" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="108">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4281,7 +4295,7 @@
       <c r="Z108" s="3"/>
       <c r="AA108" s="3"/>
     </row>
-    <row r="109" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="109">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4310,7 +4324,7 @@
       <c r="Z109" s="3"/>
       <c r="AA109" s="3"/>
     </row>
-    <row r="110" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="110">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4339,7 +4353,7 @@
       <c r="Z110" s="3"/>
       <c r="AA110" s="3"/>
     </row>
-    <row r="111" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="111">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4368,7 +4382,7 @@
       <c r="Z111" s="3"/>
       <c r="AA111" s="3"/>
     </row>
-    <row r="112" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="112">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4397,7 +4411,7 @@
       <c r="Z112" s="3"/>
       <c r="AA112" s="3"/>
     </row>
-    <row r="113" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="113">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4426,7 +4440,7 @@
       <c r="Z113" s="3"/>
       <c r="AA113" s="3"/>
     </row>
-    <row r="114" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="114">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4455,7 +4469,7 @@
       <c r="Z114" s="3"/>
       <c r="AA114" s="3"/>
     </row>
-    <row r="115" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="115">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4484,7 +4498,7 @@
       <c r="Z115" s="3"/>
       <c r="AA115" s="3"/>
     </row>
-    <row r="116" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="116">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4513,7 +4527,7 @@
       <c r="Z116" s="3"/>
       <c r="AA116" s="3"/>
     </row>
-    <row r="117" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="117">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4542,7 +4556,7 @@
       <c r="Z117" s="3"/>
       <c r="AA117" s="3"/>
     </row>
-    <row r="118" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="118">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4571,7 +4585,7 @@
       <c r="Z118" s="3"/>
       <c r="AA118" s="3"/>
     </row>
-    <row r="119" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="119">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4600,7 +4614,7 @@
       <c r="Z119" s="3"/>
       <c r="AA119" s="3"/>
     </row>
-    <row r="120" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="120">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4629,7 +4643,7 @@
       <c r="Z120" s="3"/>
       <c r="AA120" s="3"/>
     </row>
-    <row r="121" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="121">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4658,7 +4672,7 @@
       <c r="Z121" s="3"/>
       <c r="AA121" s="3"/>
     </row>
-    <row r="122" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="122">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4687,7 +4701,7 @@
       <c r="Z122" s="3"/>
       <c r="AA122" s="3"/>
     </row>
-    <row r="123" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="123">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4716,7 +4730,7 @@
       <c r="Z123" s="3"/>
       <c r="AA123" s="3"/>
     </row>
-    <row r="124" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="124">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4745,7 +4759,7 @@
       <c r="Z124" s="3"/>
       <c r="AA124" s="3"/>
     </row>
-    <row r="125" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="125">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4774,7 +4788,7 @@
       <c r="Z125" s="3"/>
       <c r="AA125" s="3"/>
     </row>
-    <row r="126" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="126">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4803,7 +4817,7 @@
       <c r="Z126" s="3"/>
       <c r="AA126" s="3"/>
     </row>
-    <row r="127" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="127">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4832,7 +4846,7 @@
       <c r="Z127" s="3"/>
       <c r="AA127" s="3"/>
     </row>
-    <row r="128" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="128">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4861,7 +4875,7 @@
       <c r="Z128" s="3"/>
       <c r="AA128" s="3"/>
     </row>
-    <row r="129" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="129">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4890,7 +4904,7 @@
       <c r="Z129" s="3"/>
       <c r="AA129" s="3"/>
     </row>
-    <row r="130" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="130">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4919,7 +4933,7 @@
       <c r="Z130" s="3"/>
       <c r="AA130" s="3"/>
     </row>
-    <row r="131" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="131">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4948,7 +4962,7 @@
       <c r="Z131" s="3"/>
       <c r="AA131" s="3"/>
     </row>
-    <row r="132" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="132">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4977,7 +4991,7 @@
       <c r="Z132" s="3"/>
       <c r="AA132" s="3"/>
     </row>
-    <row r="133" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="133">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -5006,7 +5020,7 @@
       <c r="Z133" s="3"/>
       <c r="AA133" s="3"/>
     </row>
-    <row r="134" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="134">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5035,7 +5049,7 @@
       <c r="Z134" s="3"/>
       <c r="AA134" s="3"/>
     </row>
-    <row r="135" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="135">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5064,7 +5078,7 @@
       <c r="Z135" s="3"/>
       <c r="AA135" s="3"/>
     </row>
-    <row r="136" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="136">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5093,7 +5107,7 @@
       <c r="Z136" s="3"/>
       <c r="AA136" s="3"/>
     </row>
-    <row r="137" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="137">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5122,7 +5136,7 @@
       <c r="Z137" s="3"/>
       <c r="AA137" s="3"/>
     </row>
-    <row r="138" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="138">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5151,7 +5165,7 @@
       <c r="Z138" s="3"/>
       <c r="AA138" s="3"/>
     </row>
-    <row r="139" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="139">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5180,7 +5194,7 @@
       <c r="Z139" s="3"/>
       <c r="AA139" s="3"/>
     </row>
-    <row r="140" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="140">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5209,7 +5223,7 @@
       <c r="Z140" s="3"/>
       <c r="AA140" s="3"/>
     </row>
-    <row r="141" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="141">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5238,7 +5252,7 @@
       <c r="Z141" s="3"/>
       <c r="AA141" s="3"/>
     </row>
-    <row r="142" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="142">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5267,7 +5281,7 @@
       <c r="Z142" s="3"/>
       <c r="AA142" s="3"/>
     </row>
-    <row r="143" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="143">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5296,7 +5310,7 @@
       <c r="Z143" s="3"/>
       <c r="AA143" s="3"/>
     </row>
-    <row r="144" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="144">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5325,7 +5339,7 @@
       <c r="Z144" s="3"/>
       <c r="AA144" s="3"/>
     </row>
-    <row r="145" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="145">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5354,7 +5368,7 @@
       <c r="Z145" s="3"/>
       <c r="AA145" s="3"/>
     </row>
-    <row r="146" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="146">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5383,7 +5397,7 @@
       <c r="Z146" s="3"/>
       <c r="AA146" s="3"/>
     </row>
-    <row r="147" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="147">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5412,7 +5426,7 @@
       <c r="Z147" s="3"/>
       <c r="AA147" s="3"/>
     </row>
-    <row r="148" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="148">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5441,7 +5455,7 @@
       <c r="Z148" s="3"/>
       <c r="AA148" s="3"/>
     </row>
-    <row r="149" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="149">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5470,7 +5484,7 @@
       <c r="Z149" s="3"/>
       <c r="AA149" s="3"/>
     </row>
-    <row r="150" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="150">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5499,7 +5513,7 @@
       <c r="Z150" s="3"/>
       <c r="AA150" s="3"/>
     </row>
-    <row r="151" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="151">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5528,7 +5542,7 @@
       <c r="Z151" s="3"/>
       <c r="AA151" s="3"/>
     </row>
-    <row r="152" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="152">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5557,7 +5571,7 @@
       <c r="Z152" s="3"/>
       <c r="AA152" s="3"/>
     </row>
-    <row r="153" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="153">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5586,7 +5600,7 @@
       <c r="Z153" s="3"/>
       <c r="AA153" s="3"/>
     </row>
-    <row r="154" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="154">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5615,7 +5629,7 @@
       <c r="Z154" s="3"/>
       <c r="AA154" s="3"/>
     </row>
-    <row r="155" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="155">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5644,7 +5658,7 @@
       <c r="Z155" s="3"/>
       <c r="AA155" s="3"/>
     </row>
-    <row r="156" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="156">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5673,7 +5687,7 @@
       <c r="Z156" s="3"/>
       <c r="AA156" s="3"/>
     </row>
-    <row r="157" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="157">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5702,7 +5716,7 @@
       <c r="Z157" s="3"/>
       <c r="AA157" s="3"/>
     </row>
-    <row r="158" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="158">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5731,7 +5745,7 @@
       <c r="Z158" s="3"/>
       <c r="AA158" s="3"/>
     </row>
-    <row r="159" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="159">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5760,7 +5774,7 @@
       <c r="Z159" s="3"/>
       <c r="AA159" s="3"/>
     </row>
-    <row r="160" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="160">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5789,7 +5803,7 @@
       <c r="Z160" s="3"/>
       <c r="AA160" s="3"/>
     </row>
-    <row r="161" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="161">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5818,7 +5832,7 @@
       <c r="Z161" s="3"/>
       <c r="AA161" s="3"/>
     </row>
-    <row r="162" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="162">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5847,7 +5861,7 @@
       <c r="Z162" s="3"/>
       <c r="AA162" s="3"/>
     </row>
-    <row r="163" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="163">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5876,7 +5890,7 @@
       <c r="Z163" s="3"/>
       <c r="AA163" s="3"/>
     </row>
-    <row r="164" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="164">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -5905,7 +5919,7 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
     </row>
-    <row r="165" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="165">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -5934,7 +5948,7 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
     </row>
-    <row r="166" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="166">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -5963,7 +5977,7 @@
       <c r="Z166" s="3"/>
       <c r="AA166" s="3"/>
     </row>
-    <row r="167" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="167">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5992,7 +6006,7 @@
       <c r="Z167" s="3"/>
       <c r="AA167" s="3"/>
     </row>
-    <row r="168" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="168">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -6021,7 +6035,7 @@
       <c r="Z168" s="3"/>
       <c r="AA168" s="3"/>
     </row>
-    <row r="169" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="169">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -6050,7 +6064,7 @@
       <c r="Z169" s="3"/>
       <c r="AA169" s="3"/>
     </row>
-    <row r="170" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="170">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -6079,7 +6093,7 @@
       <c r="Z170" s="3"/>
       <c r="AA170" s="3"/>
     </row>
-    <row r="171" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="171">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6108,7 +6122,7 @@
       <c r="Z171" s="3"/>
       <c r="AA171" s="3"/>
     </row>
-    <row r="172" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="172">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6137,7 +6151,7 @@
       <c r="Z172" s="3"/>
       <c r="AA172" s="3"/>
     </row>
-    <row r="173" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="173">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6166,7 +6180,7 @@
       <c r="Z173" s="3"/>
       <c r="AA173" s="3"/>
     </row>
-    <row r="174" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="174">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6195,7 +6209,7 @@
       <c r="Z174" s="3"/>
       <c r="AA174" s="3"/>
     </row>
-    <row r="175" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="175">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6224,7 +6238,7 @@
       <c r="Z175" s="3"/>
       <c r="AA175" s="3"/>
     </row>
-    <row r="176" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="176">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6253,7 +6267,7 @@
       <c r="Z176" s="3"/>
       <c r="AA176" s="3"/>
     </row>
-    <row r="177" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="177">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6282,7 +6296,7 @@
       <c r="Z177" s="3"/>
       <c r="AA177" s="3"/>
     </row>
-    <row r="178" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="178">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6311,7 +6325,7 @@
       <c r="Z178" s="3"/>
       <c r="AA178" s="3"/>
     </row>
-    <row r="179" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="179">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6340,7 +6354,7 @@
       <c r="Z179" s="3"/>
       <c r="AA179" s="3"/>
     </row>
-    <row r="180" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="180">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6369,7 +6383,7 @@
       <c r="Z180" s="3"/>
       <c r="AA180" s="3"/>
     </row>
-    <row r="181" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="181">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6398,7 +6412,7 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="3"/>
     </row>
-    <row r="182" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="182">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6427,7 +6441,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="3"/>
     </row>
-    <row r="183" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="183">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6456,7 +6470,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="3"/>
     </row>
-    <row r="184" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="184">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6485,7 +6499,7 @@
       <c r="Z184" s="3"/>
       <c r="AA184" s="3"/>
     </row>
-    <row r="185" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="185">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6514,7 +6528,7 @@
       <c r="Z185" s="3"/>
       <c r="AA185" s="3"/>
     </row>
-    <row r="186" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="186">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6543,7 +6557,7 @@
       <c r="Z186" s="3"/>
       <c r="AA186" s="3"/>
     </row>
-    <row r="187" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="187">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6572,7 +6586,7 @@
       <c r="Z187" s="3"/>
       <c r="AA187" s="3"/>
     </row>
-    <row r="188" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="188">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6601,7 +6615,7 @@
       <c r="Z188" s="3"/>
       <c r="AA188" s="3"/>
     </row>
-    <row r="189" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="189">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6630,7 +6644,7 @@
       <c r="Z189" s="3"/>
       <c r="AA189" s="3"/>
     </row>
-    <row r="190" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="190">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6659,7 +6673,7 @@
       <c r="Z190" s="3"/>
       <c r="AA190" s="3"/>
     </row>
-    <row r="191" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="191">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6688,7 +6702,7 @@
       <c r="Z191" s="3"/>
       <c r="AA191" s="3"/>
     </row>
-    <row r="192" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="192">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6717,7 +6731,7 @@
       <c r="Z192" s="3"/>
       <c r="AA192" s="3"/>
     </row>
-    <row r="193" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="193">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6746,7 +6760,7 @@
       <c r="Z193" s="3"/>
       <c r="AA193" s="3"/>
     </row>
-    <row r="194" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="194">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6775,7 +6789,7 @@
       <c r="Z194" s="3"/>
       <c r="AA194" s="3"/>
     </row>
-    <row r="195" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="195">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6804,7 +6818,7 @@
       <c r="Z195" s="3"/>
       <c r="AA195" s="3"/>
     </row>
-    <row r="196" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="196">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6833,7 +6847,7 @@
       <c r="Z196" s="3"/>
       <c r="AA196" s="3"/>
     </row>
-    <row r="197" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="197">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6862,7 +6876,7 @@
       <c r="Z197" s="3"/>
       <c r="AA197" s="3"/>
     </row>
-    <row r="198" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="198">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -6891,7 +6905,7 @@
       <c r="Z198" s="3"/>
       <c r="AA198" s="3"/>
     </row>
-    <row r="199" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="199">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -6920,7 +6934,7 @@
       <c r="Z199" s="3"/>
       <c r="AA199" s="3"/>
     </row>
-    <row r="200" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="200">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6949,7 +6963,7 @@
       <c r="Z200" s="3"/>
       <c r="AA200" s="3"/>
     </row>
-    <row r="201" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="201">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -6978,7 +6992,7 @@
       <c r="Z201" s="3"/>
       <c r="AA201" s="3"/>
     </row>
-    <row r="202" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="202">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -7007,7 +7021,7 @@
       <c r="Z202" s="3"/>
       <c r="AA202" s="3"/>
     </row>
-    <row r="203" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="203">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -7036,7 +7050,7 @@
       <c r="Z203" s="3"/>
       <c r="AA203" s="3"/>
     </row>
-    <row r="204" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="204">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -7065,7 +7079,7 @@
       <c r="Z204" s="3"/>
       <c r="AA204" s="3"/>
     </row>
-    <row r="205" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="205">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7094,7 +7108,7 @@
       <c r="Z205" s="3"/>
       <c r="AA205" s="3"/>
     </row>
-    <row r="206" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="206">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7123,7 +7137,7 @@
       <c r="Z206" s="3"/>
       <c r="AA206" s="3"/>
     </row>
-    <row r="207" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="207">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7152,7 +7166,7 @@
       <c r="Z207" s="3"/>
       <c r="AA207" s="3"/>
     </row>
-    <row r="208" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="208">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7181,7 +7195,7 @@
       <c r="Z208" s="3"/>
       <c r="AA208" s="3"/>
     </row>
-    <row r="209" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="209">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7210,7 +7224,7 @@
       <c r="Z209" s="3"/>
       <c r="AA209" s="3"/>
     </row>
-    <row r="210" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="210">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7239,7 +7253,7 @@
       <c r="Z210" s="3"/>
       <c r="AA210" s="3"/>
     </row>
-    <row r="211" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="211">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7268,7 +7282,7 @@
       <c r="Z211" s="3"/>
       <c r="AA211" s="3"/>
     </row>
-    <row r="212" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="212">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7297,7 +7311,7 @@
       <c r="Z212" s="3"/>
       <c r="AA212" s="3"/>
     </row>
-    <row r="213" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="213">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7326,7 +7340,7 @@
       <c r="Z213" s="3"/>
       <c r="AA213" s="3"/>
     </row>
-    <row r="214" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="214">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7355,7 +7369,7 @@
       <c r="Z214" s="3"/>
       <c r="AA214" s="3"/>
     </row>
-    <row r="215" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="215">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7384,7 +7398,7 @@
       <c r="Z215" s="3"/>
       <c r="AA215" s="3"/>
     </row>
-    <row r="216" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="216">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7413,7 +7427,7 @@
       <c r="Z216" s="3"/>
       <c r="AA216" s="3"/>
     </row>
-    <row r="217" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="217">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7442,7 +7456,7 @@
       <c r="Z217" s="3"/>
       <c r="AA217" s="3"/>
     </row>
-    <row r="218" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="218">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7471,7 +7485,7 @@
       <c r="Z218" s="3"/>
       <c r="AA218" s="3"/>
     </row>
-    <row r="219" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="219">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7500,7 +7514,7 @@
       <c r="Z219" s="3"/>
       <c r="AA219" s="3"/>
     </row>
-    <row r="220" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="220">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7529,7 +7543,7 @@
       <c r="Z220" s="3"/>
       <c r="AA220" s="3"/>
     </row>
-    <row r="221" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="221">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -7558,7 +7572,7 @@
       <c r="Z221" s="3"/>
       <c r="AA221" s="3"/>
     </row>
-    <row r="222" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="222">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -7587,7 +7601,7 @@
       <c r="Z222" s="3"/>
       <c r="AA222" s="3"/>
     </row>
-    <row r="223" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="223">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -7616,7 +7630,7 @@
       <c r="Z223" s="3"/>
       <c r="AA223" s="3"/>
     </row>
-    <row r="224" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="224">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -7645,7 +7659,7 @@
       <c r="Z224" s="3"/>
       <c r="AA224" s="3"/>
     </row>
-    <row r="225" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="225">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -7674,7 +7688,7 @@
       <c r="Z225" s="3"/>
       <c r="AA225" s="3"/>
     </row>
-    <row r="226" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="226">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -7703,7 +7717,7 @@
       <c r="Z226" s="3"/>
       <c r="AA226" s="3"/>
     </row>
-    <row r="227" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="227">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -7732,7 +7746,7 @@
       <c r="Z227" s="3"/>
       <c r="AA227" s="3"/>
     </row>
-    <row r="228" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="228">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -7761,7 +7775,7 @@
       <c r="Z228" s="3"/>
       <c r="AA228" s="3"/>
     </row>
-    <row r="229" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="229">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -7790,7 +7804,7 @@
       <c r="Z229" s="3"/>
       <c r="AA229" s="3"/>
     </row>
-    <row r="230" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="230">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -7819,7 +7833,7 @@
       <c r="Z230" s="3"/>
       <c r="AA230" s="3"/>
     </row>
-    <row r="231" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="231">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -7848,7 +7862,7 @@
       <c r="Z231" s="3"/>
       <c r="AA231" s="3"/>
     </row>
-    <row r="232" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="232">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -7877,7 +7891,7 @@
       <c r="Z232" s="3"/>
       <c r="AA232" s="3"/>
     </row>
-    <row r="233" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="233">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -7906,7 +7920,7 @@
       <c r="Z233" s="3"/>
       <c r="AA233" s="3"/>
     </row>
-    <row r="234" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="234">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -7935,7 +7949,7 @@
       <c r="Z234" s="3"/>
       <c r="AA234" s="3"/>
     </row>
-    <row r="235" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="235">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -7964,7 +7978,7 @@
       <c r="Z235" s="3"/>
       <c r="AA235" s="3"/>
     </row>
-    <row r="236" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="236">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -7993,7 +8007,7 @@
       <c r="Z236" s="3"/>
       <c r="AA236" s="3"/>
     </row>
-    <row r="237" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="237">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -8022,7 +8036,7 @@
       <c r="Z237" s="3"/>
       <c r="AA237" s="3"/>
     </row>
-    <row r="238" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="238">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -8051,7 +8065,7 @@
       <c r="Z238" s="3"/>
       <c r="AA238" s="3"/>
     </row>
-    <row r="239" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="239">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -8080,7 +8094,7 @@
       <c r="Z239" s="3"/>
       <c r="AA239" s="3"/>
     </row>
-    <row r="240" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="240">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -8109,7 +8123,7 @@
       <c r="Z240" s="3"/>
       <c r="AA240" s="3"/>
     </row>
-    <row r="241" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="241">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -8138,7 +8152,7 @@
       <c r="Z241" s="3"/>
       <c r="AA241" s="3"/>
     </row>
-    <row r="242" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="242">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -8167,7 +8181,7 @@
       <c r="Z242" s="3"/>
       <c r="AA242" s="3"/>
     </row>
-    <row r="243" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="243">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -8196,7 +8210,7 @@
       <c r="Z243" s="3"/>
       <c r="AA243" s="3"/>
     </row>
-    <row r="244" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="244">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -8225,7 +8239,7 @@
       <c r="Z244" s="3"/>
       <c r="AA244" s="3"/>
     </row>
-    <row r="245" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="245">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -8254,7 +8268,7 @@
       <c r="Z245" s="3"/>
       <c r="AA245" s="3"/>
     </row>
-    <row r="246" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="246">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -8283,7 +8297,7 @@
       <c r="Z246" s="3"/>
       <c r="AA246" s="3"/>
     </row>
-    <row r="247" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="247">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -8312,7 +8326,7 @@
       <c r="Z247" s="3"/>
       <c r="AA247" s="3"/>
     </row>
-    <row r="248" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="248">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -8341,7 +8355,7 @@
       <c r="Z248" s="3"/>
       <c r="AA248" s="3"/>
     </row>
-    <row r="249" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="249">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -8370,7 +8384,7 @@
       <c r="Z249" s="3"/>
       <c r="AA249" s="3"/>
     </row>
-    <row r="250" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="250">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -8399,7 +8413,7 @@
       <c r="Z250" s="3"/>
       <c r="AA250" s="3"/>
     </row>
-    <row r="251" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="251">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -8428,7 +8442,7 @@
       <c r="Z251" s="3"/>
       <c r="AA251" s="3"/>
     </row>
-    <row r="252" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="252">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -8457,7 +8471,7 @@
       <c r="Z252" s="3"/>
       <c r="AA252" s="3"/>
     </row>
-    <row r="253" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="253">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -8486,7 +8500,7 @@
       <c r="Z253" s="3"/>
       <c r="AA253" s="3"/>
     </row>
-    <row r="254" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="254">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -8515,7 +8529,7 @@
       <c r="Z254" s="3"/>
       <c r="AA254" s="3"/>
     </row>
-    <row r="255" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="255">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -8544,7 +8558,7 @@
       <c r="Z255" s="3"/>
       <c r="AA255" s="3"/>
     </row>
-    <row r="256" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="256">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -8573,7 +8587,7 @@
       <c r="Z256" s="3"/>
       <c r="AA256" s="3"/>
     </row>
-    <row r="257" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="257">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -8602,7 +8616,7 @@
       <c r="Z257" s="3"/>
       <c r="AA257" s="3"/>
     </row>
-    <row r="258" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="258">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -8631,7 +8645,7 @@
       <c r="Z258" s="3"/>
       <c r="AA258" s="3"/>
     </row>
-    <row r="259" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="259">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -8660,7 +8674,7 @@
       <c r="Z259" s="3"/>
       <c r="AA259" s="3"/>
     </row>
-    <row r="260" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="260">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -8689,7 +8703,7 @@
       <c r="Z260" s="3"/>
       <c r="AA260" s="3"/>
     </row>
-    <row r="261" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="261">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -8718,7 +8732,7 @@
       <c r="Z261" s="3"/>
       <c r="AA261" s="3"/>
     </row>
-    <row r="262" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="262">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -8747,7 +8761,7 @@
       <c r="Z262" s="3"/>
       <c r="AA262" s="3"/>
     </row>
-    <row r="263" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="263">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -8776,7 +8790,7 @@
       <c r="Z263" s="3"/>
       <c r="AA263" s="3"/>
     </row>
-    <row r="264" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="264">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -8805,7 +8819,7 @@
       <c r="Z264" s="3"/>
       <c r="AA264" s="3"/>
     </row>
-    <row r="265" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="265">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -8834,7 +8848,7 @@
       <c r="Z265" s="3"/>
       <c r="AA265" s="3"/>
     </row>
-    <row r="266" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="266">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -8863,7 +8877,7 @@
       <c r="Z266" s="3"/>
       <c r="AA266" s="3"/>
     </row>
-    <row r="267" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="267">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -8892,7 +8906,7 @@
       <c r="Z267" s="3"/>
       <c r="AA267" s="3"/>
     </row>
-    <row r="268" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="268">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -8921,7 +8935,7 @@
       <c r="Z268" s="3"/>
       <c r="AA268" s="3"/>
     </row>
-    <row r="269" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="269">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -8950,7 +8964,7 @@
       <c r="Z269" s="3"/>
       <c r="AA269" s="3"/>
     </row>
-    <row r="270" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="270">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -8979,7 +8993,7 @@
       <c r="Z270" s="3"/>
       <c r="AA270" s="3"/>
     </row>
-    <row r="271" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="271">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -9008,7 +9022,7 @@
       <c r="Z271" s="3"/>
       <c r="AA271" s="3"/>
     </row>
-    <row r="272" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="272">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -9037,7 +9051,7 @@
       <c r="Z272" s="3"/>
       <c r="AA272" s="3"/>
     </row>
-    <row r="273" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="273">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -9066,7 +9080,7 @@
       <c r="Z273" s="3"/>
       <c r="AA273" s="3"/>
     </row>
-    <row r="274" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="274">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -9095,7 +9109,7 @@
       <c r="Z274" s="3"/>
       <c r="AA274" s="3"/>
     </row>
-    <row r="275" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="275">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -9124,7 +9138,7 @@
       <c r="Z275" s="3"/>
       <c r="AA275" s="3"/>
     </row>
-    <row r="276" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="276">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -9153,7 +9167,7 @@
       <c r="Z276" s="3"/>
       <c r="AA276" s="3"/>
     </row>
-    <row r="277" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="277">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -9182,7 +9196,7 @@
       <c r="Z277" s="3"/>
       <c r="AA277" s="3"/>
     </row>
-    <row r="278" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="278">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -9211,7 +9225,7 @@
       <c r="Z278" s="3"/>
       <c r="AA278" s="3"/>
     </row>
-    <row r="279" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="279">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -9240,7 +9254,7 @@
       <c r="Z279" s="3"/>
       <c r="AA279" s="3"/>
     </row>
-    <row r="280" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="280">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -9269,7 +9283,7 @@
       <c r="Z280" s="3"/>
       <c r="AA280" s="3"/>
     </row>
-    <row r="281" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="281">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -9298,7 +9312,7 @@
       <c r="Z281" s="3"/>
       <c r="AA281" s="3"/>
     </row>
-    <row r="282" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="282">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -9327,7 +9341,7 @@
       <c r="Z282" s="3"/>
       <c r="AA282" s="3"/>
     </row>
-    <row r="283" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="283">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -9356,7 +9370,7 @@
       <c r="Z283" s="3"/>
       <c r="AA283" s="3"/>
     </row>
-    <row r="284" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="284">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -9385,7 +9399,7 @@
       <c r="Z284" s="3"/>
       <c r="AA284" s="3"/>
     </row>
-    <row r="285" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="285">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -9414,7 +9428,7 @@
       <c r="Z285" s="3"/>
       <c r="AA285" s="3"/>
     </row>
-    <row r="286" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="286">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -9443,7 +9457,7 @@
       <c r="Z286" s="3"/>
       <c r="AA286" s="3"/>
     </row>
-    <row r="287" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="287">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -9472,7 +9486,7 @@
       <c r="Z287" s="3"/>
       <c r="AA287" s="3"/>
     </row>
-    <row r="288" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="288">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -9501,7 +9515,7 @@
       <c r="Z288" s="3"/>
       <c r="AA288" s="3"/>
     </row>
-    <row r="289" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="289">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -9530,7 +9544,7 @@
       <c r="Z289" s="3"/>
       <c r="AA289" s="3"/>
     </row>
-    <row r="290" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="290">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -9559,7 +9573,7 @@
       <c r="Z290" s="3"/>
       <c r="AA290" s="3"/>
     </row>
-    <row r="291" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="291">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -9588,7 +9602,7 @@
       <c r="Z291" s="3"/>
       <c r="AA291" s="3"/>
     </row>
-    <row r="292" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="292">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -9617,7 +9631,7 @@
       <c r="Z292" s="3"/>
       <c r="AA292" s="3"/>
     </row>
-    <row r="293" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="293">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -9646,7 +9660,7 @@
       <c r="Z293" s="3"/>
       <c r="AA293" s="3"/>
     </row>
-    <row r="294" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="294">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -9675,7 +9689,7 @@
       <c r="Z294" s="3"/>
       <c r="AA294" s="3"/>
     </row>
-    <row r="295" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="295">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -9704,7 +9718,7 @@
       <c r="Z295" s="3"/>
       <c r="AA295" s="3"/>
     </row>
-    <row r="296" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="296">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -9733,7 +9747,7 @@
       <c r="Z296" s="3"/>
       <c r="AA296" s="3"/>
     </row>
-    <row r="297" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="297">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -9762,7 +9776,7 @@
       <c r="Z297" s="3"/>
       <c r="AA297" s="3"/>
     </row>
-    <row r="298" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="298">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -9791,7 +9805,7 @@
       <c r="Z298" s="3"/>
       <c r="AA298" s="3"/>
     </row>
-    <row r="299" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="299">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -9820,7 +9834,7 @@
       <c r="Z299" s="3"/>
       <c r="AA299" s="3"/>
     </row>
-    <row r="300" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="300">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -9849,7 +9863,7 @@
       <c r="Z300" s="3"/>
       <c r="AA300" s="3"/>
     </row>
-    <row r="301" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="301">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -9878,7 +9892,7 @@
       <c r="Z301" s="3"/>
       <c r="AA301" s="3"/>
     </row>
-    <row r="302" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="302">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -9907,7 +9921,7 @@
       <c r="Z302" s="3"/>
       <c r="AA302" s="3"/>
     </row>
-    <row r="303" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="303">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -9936,7 +9950,7 @@
       <c r="Z303" s="3"/>
       <c r="AA303" s="3"/>
     </row>
-    <row r="304" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="304">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -9965,7 +9979,7 @@
       <c r="Z304" s="3"/>
       <c r="AA304" s="3"/>
     </row>
-    <row r="305" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="305">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -9994,7 +10008,7 @@
       <c r="Z305" s="3"/>
       <c r="AA305" s="3"/>
     </row>
-    <row r="306" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="306">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -10023,7 +10037,7 @@
       <c r="Z306" s="3"/>
       <c r="AA306" s="3"/>
     </row>
-    <row r="307" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="307">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -10052,7 +10066,7 @@
       <c r="Z307" s="3"/>
       <c r="AA307" s="3"/>
     </row>
-    <row r="308" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="308">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -10081,7 +10095,7 @@
       <c r="Z308" s="3"/>
       <c r="AA308" s="3"/>
     </row>
-    <row r="309" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="309">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -10110,7 +10124,7 @@
       <c r="Z309" s="3"/>
       <c r="AA309" s="3"/>
     </row>
-    <row r="310" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="310">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -10139,7 +10153,7 @@
       <c r="Z310" s="3"/>
       <c r="AA310" s="3"/>
     </row>
-    <row r="311" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="311">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -10168,7 +10182,7 @@
       <c r="Z311" s="3"/>
       <c r="AA311" s="3"/>
     </row>
-    <row r="312" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="312">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -10197,7 +10211,7 @@
       <c r="Z312" s="3"/>
       <c r="AA312" s="3"/>
     </row>
-    <row r="313" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="313">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -10226,7 +10240,7 @@
       <c r="Z313" s="3"/>
       <c r="AA313" s="3"/>
     </row>
-    <row r="314" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="314">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -10255,7 +10269,7 @@
       <c r="Z314" s="3"/>
       <c r="AA314" s="3"/>
     </row>
-    <row r="315" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="315">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -10284,7 +10298,7 @@
       <c r="Z315" s="3"/>
       <c r="AA315" s="3"/>
     </row>
-    <row r="316" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="316">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -10313,7 +10327,7 @@
       <c r="Z316" s="3"/>
       <c r="AA316" s="3"/>
     </row>
-    <row r="317" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="317">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -10342,7 +10356,7 @@
       <c r="Z317" s="3"/>
       <c r="AA317" s="3"/>
     </row>
-    <row r="318" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="318">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -10371,7 +10385,7 @@
       <c r="Z318" s="3"/>
       <c r="AA318" s="3"/>
     </row>
-    <row r="319" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="319">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -10400,7 +10414,7 @@
       <c r="Z319" s="3"/>
       <c r="AA319" s="3"/>
     </row>
-    <row r="320" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="320">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -10429,7 +10443,7 @@
       <c r="Z320" s="3"/>
       <c r="AA320" s="3"/>
     </row>
-    <row r="321" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="321">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -10458,7 +10472,7 @@
       <c r="Z321" s="3"/>
       <c r="AA321" s="3"/>
     </row>
-    <row r="322" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="322">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -10487,7 +10501,7 @@
       <c r="Z322" s="3"/>
       <c r="AA322" s="3"/>
     </row>
-    <row r="323" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="323">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -10516,7 +10530,7 @@
       <c r="Z323" s="3"/>
       <c r="AA323" s="3"/>
     </row>
-    <row r="324" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="324">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -10545,7 +10559,7 @@
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
     </row>
-    <row r="325" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="325">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -10574,7 +10588,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
     </row>
-    <row r="326" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="326">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -10603,7 +10617,7 @@
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
     </row>
-    <row r="327" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="327">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -10632,7 +10646,7 @@
       <c r="Z327" s="3"/>
       <c r="AA327" s="3"/>
     </row>
-    <row r="328" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="328">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -10661,7 +10675,7 @@
       <c r="Z328" s="3"/>
       <c r="AA328" s="3"/>
     </row>
-    <row r="329" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="329">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -10690,7 +10704,7 @@
       <c r="Z329" s="3"/>
       <c r="AA329" s="3"/>
     </row>
-    <row r="330" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="330">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -10719,7 +10733,7 @@
       <c r="Z330" s="3"/>
       <c r="AA330" s="3"/>
     </row>
-    <row r="331" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="331">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -10748,7 +10762,7 @@
       <c r="Z331" s="3"/>
       <c r="AA331" s="3"/>
     </row>
-    <row r="332" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="332">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -10777,7 +10791,7 @@
       <c r="Z332" s="3"/>
       <c r="AA332" s="3"/>
     </row>
-    <row r="333" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="333">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -10806,7 +10820,7 @@
       <c r="Z333" s="3"/>
       <c r="AA333" s="3"/>
     </row>
-    <row r="334" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="334">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -10835,7 +10849,7 @@
       <c r="Z334" s="3"/>
       <c r="AA334" s="3"/>
     </row>
-    <row r="335" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="335">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -10864,7 +10878,7 @@
       <c r="Z335" s="3"/>
       <c r="AA335" s="3"/>
     </row>
-    <row r="336" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="336">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -10893,7 +10907,7 @@
       <c r="Z336" s="3"/>
       <c r="AA336" s="3"/>
     </row>
-    <row r="337" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="337">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -10922,7 +10936,7 @@
       <c r="Z337" s="3"/>
       <c r="AA337" s="3"/>
     </row>
-    <row r="338" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="338">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -10951,7 +10965,7 @@
       <c r="Z338" s="3"/>
       <c r="AA338" s="3"/>
     </row>
-    <row r="339" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="339">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -10980,7 +10994,7 @@
       <c r="Z339" s="3"/>
       <c r="AA339" s="3"/>
     </row>
-    <row r="340" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="340">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -11009,7 +11023,7 @@
       <c r="Z340" s="3"/>
       <c r="AA340" s="3"/>
     </row>
-    <row r="341" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="341">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -11038,7 +11052,7 @@
       <c r="Z341" s="3"/>
       <c r="AA341" s="3"/>
     </row>
-    <row r="342" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="342">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -11067,7 +11081,7 @@
       <c r="Z342" s="3"/>
       <c r="AA342" s="3"/>
     </row>
-    <row r="343" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="343">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -11096,7 +11110,7 @@
       <c r="Z343" s="3"/>
       <c r="AA343" s="3"/>
     </row>
-    <row r="344" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="344">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -11125,7 +11139,7 @@
       <c r="Z344" s="3"/>
       <c r="AA344" s="3"/>
     </row>
-    <row r="345" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="345">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -11154,7 +11168,7 @@
       <c r="Z345" s="3"/>
       <c r="AA345" s="3"/>
     </row>
-    <row r="346" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="346">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -11183,7 +11197,7 @@
       <c r="Z346" s="3"/>
       <c r="AA346" s="3"/>
     </row>
-    <row r="347" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="347">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -11212,7 +11226,7 @@
       <c r="Z347" s="3"/>
       <c r="AA347" s="3"/>
     </row>
-    <row r="348" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="348">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -11241,7 +11255,7 @@
       <c r="Z348" s="3"/>
       <c r="AA348" s="3"/>
     </row>
-    <row r="349" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="349">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -11270,7 +11284,7 @@
       <c r="Z349" s="3"/>
       <c r="AA349" s="3"/>
     </row>
-    <row r="350" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="350">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -11299,7 +11313,7 @@
       <c r="Z350" s="3"/>
       <c r="AA350" s="3"/>
     </row>
-    <row r="351" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="351">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -11328,7 +11342,7 @@
       <c r="Z351" s="3"/>
       <c r="AA351" s="3"/>
     </row>
-    <row r="352" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="352">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -11357,7 +11371,7 @@
       <c r="Z352" s="3"/>
       <c r="AA352" s="3"/>
     </row>
-    <row r="353" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="353">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -11386,7 +11400,7 @@
       <c r="Z353" s="3"/>
       <c r="AA353" s="3"/>
     </row>
-    <row r="354" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="354">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -11415,7 +11429,7 @@
       <c r="Z354" s="3"/>
       <c r="AA354" s="3"/>
     </row>
-    <row r="355" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="355">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -11444,7 +11458,7 @@
       <c r="Z355" s="3"/>
       <c r="AA355" s="3"/>
     </row>
-    <row r="356" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="356">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -11473,7 +11487,7 @@
       <c r="Z356" s="3"/>
       <c r="AA356" s="3"/>
     </row>
-    <row r="357" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="357">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -11502,7 +11516,7 @@
       <c r="Z357" s="3"/>
       <c r="AA357" s="3"/>
     </row>
-    <row r="358" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="358">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -11531,7 +11545,7 @@
       <c r="Z358" s="3"/>
       <c r="AA358" s="3"/>
     </row>
-    <row r="359" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="359">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -11560,7 +11574,7 @@
       <c r="Z359" s="3"/>
       <c r="AA359" s="3"/>
     </row>
-    <row r="360" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="360">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -11589,7 +11603,7 @@
       <c r="Z360" s="3"/>
       <c r="AA360" s="3"/>
     </row>
-    <row r="361" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="361">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -11618,7 +11632,7 @@
       <c r="Z361" s="3"/>
       <c r="AA361" s="3"/>
     </row>
-    <row r="362" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="362">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -11647,7 +11661,7 @@
       <c r="Z362" s="3"/>
       <c r="AA362" s="3"/>
     </row>
-    <row r="363" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="363">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -11676,7 +11690,7 @@
       <c r="Z363" s="3"/>
       <c r="AA363" s="3"/>
     </row>
-    <row r="364" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="364">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -11705,7 +11719,7 @@
       <c r="Z364" s="3"/>
       <c r="AA364" s="3"/>
     </row>
-    <row r="365" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="365">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -11734,7 +11748,7 @@
       <c r="Z365" s="3"/>
       <c r="AA365" s="3"/>
     </row>
-    <row r="366" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="366">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -11763,7 +11777,7 @@
       <c r="Z366" s="3"/>
       <c r="AA366" s="3"/>
     </row>
-    <row r="367" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="367">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -11792,7 +11806,7 @@
       <c r="Z367" s="3"/>
       <c r="AA367" s="3"/>
     </row>
-    <row r="368" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="368">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -11821,7 +11835,7 @@
       <c r="Z368" s="3"/>
       <c r="AA368" s="3"/>
     </row>
-    <row r="369" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="369">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -11850,7 +11864,7 @@
       <c r="Z369" s="3"/>
       <c r="AA369" s="3"/>
     </row>
-    <row r="370" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="370">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -11879,7 +11893,7 @@
       <c r="Z370" s="3"/>
       <c r="AA370" s="3"/>
     </row>
-    <row r="371" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="371">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -11908,7 +11922,7 @@
       <c r="Z371" s="3"/>
       <c r="AA371" s="3"/>
     </row>
-    <row r="372" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="372">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -11937,7 +11951,7 @@
       <c r="Z372" s="3"/>
       <c r="AA372" s="3"/>
     </row>
-    <row r="373" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="373">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -11966,7 +11980,7 @@
       <c r="Z373" s="3"/>
       <c r="AA373" s="3"/>
     </row>
-    <row r="374" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="374">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -11995,7 +12009,7 @@
       <c r="Z374" s="3"/>
       <c r="AA374" s="3"/>
     </row>
-    <row r="375" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="375">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -12024,7 +12038,7 @@
       <c r="Z375" s="3"/>
       <c r="AA375" s="3"/>
     </row>
-    <row r="376" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="376">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -12053,7 +12067,7 @@
       <c r="Z376" s="3"/>
       <c r="AA376" s="3"/>
     </row>
-    <row r="377" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="377">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -12082,7 +12096,7 @@
       <c r="Z377" s="3"/>
       <c r="AA377" s="3"/>
     </row>
-    <row r="378" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="378">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -12111,7 +12125,7 @@
       <c r="Z378" s="3"/>
       <c r="AA378" s="3"/>
     </row>
-    <row r="379" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="379">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -12140,7 +12154,7 @@
       <c r="Z379" s="3"/>
       <c r="AA379" s="3"/>
     </row>
-    <row r="380" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="380">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -12169,7 +12183,7 @@
       <c r="Z380" s="3"/>
       <c r="AA380" s="3"/>
     </row>
-    <row r="381" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="381">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -12198,7 +12212,7 @@
       <c r="Z381" s="3"/>
       <c r="AA381" s="3"/>
     </row>
-    <row r="382" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="382">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -12227,7 +12241,7 @@
       <c r="Z382" s="3"/>
       <c r="AA382" s="3"/>
     </row>
-    <row r="383" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="383">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -12256,7 +12270,7 @@
       <c r="Z383" s="3"/>
       <c r="AA383" s="3"/>
     </row>
-    <row r="384" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="384">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -12285,7 +12299,7 @@
       <c r="Z384" s="3"/>
       <c r="AA384" s="3"/>
     </row>
-    <row r="385" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="385">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -12314,7 +12328,7 @@
       <c r="Z385" s="3"/>
       <c r="AA385" s="3"/>
     </row>
-    <row r="386" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="386">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -12343,7 +12357,7 @@
       <c r="Z386" s="3"/>
       <c r="AA386" s="3"/>
     </row>
-    <row r="387" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="387">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -12372,7 +12386,7 @@
       <c r="Z387" s="3"/>
       <c r="AA387" s="3"/>
     </row>
-    <row r="388" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="388">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -12401,7 +12415,7 @@
       <c r="Z388" s="3"/>
       <c r="AA388" s="3"/>
     </row>
-    <row r="389" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="389">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -12430,7 +12444,7 @@
       <c r="Z389" s="3"/>
       <c r="AA389" s="3"/>
     </row>
-    <row r="390" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="390">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -12459,7 +12473,7 @@
       <c r="Z390" s="3"/>
       <c r="AA390" s="3"/>
     </row>
-    <row r="391" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="391">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -12488,7 +12502,7 @@
       <c r="Z391" s="3"/>
       <c r="AA391" s="3"/>
     </row>
-    <row r="392" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="392">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -12517,7 +12531,7 @@
       <c r="Z392" s="3"/>
       <c r="AA392" s="3"/>
     </row>
-    <row r="393" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="393">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -12546,7 +12560,7 @@
       <c r="Z393" s="3"/>
       <c r="AA393" s="3"/>
     </row>
-    <row r="394" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="394">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -12575,7 +12589,7 @@
       <c r="Z394" s="3"/>
       <c r="AA394" s="3"/>
     </row>
-    <row r="395" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="395">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -12604,7 +12618,7 @@
       <c r="Z395" s="3"/>
       <c r="AA395" s="3"/>
     </row>
-    <row r="396" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="396">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -12633,7 +12647,7 @@
       <c r="Z396" s="3"/>
       <c r="AA396" s="3"/>
     </row>
-    <row r="397" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="397">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -12662,7 +12676,7 @@
       <c r="Z397" s="3"/>
       <c r="AA397" s="3"/>
     </row>
-    <row r="398" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="398">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -12691,7 +12705,7 @@
       <c r="Z398" s="3"/>
       <c r="AA398" s="3"/>
     </row>
-    <row r="399" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="399">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -12720,7 +12734,7 @@
       <c r="Z399" s="3"/>
       <c r="AA399" s="3"/>
     </row>
-    <row r="400" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="400">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -12749,7 +12763,7 @@
       <c r="Z400" s="3"/>
       <c r="AA400" s="3"/>
     </row>
-    <row r="401" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="401">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -12778,7 +12792,7 @@
       <c r="Z401" s="3"/>
       <c r="AA401" s="3"/>
     </row>
-    <row r="402" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="402">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -12807,7 +12821,7 @@
       <c r="Z402" s="3"/>
       <c r="AA402" s="3"/>
     </row>
-    <row r="403" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="403">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -12836,7 +12850,7 @@
       <c r="Z403" s="3"/>
       <c r="AA403" s="3"/>
     </row>
-    <row r="404" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="404">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -12865,7 +12879,7 @@
       <c r="Z404" s="3"/>
       <c r="AA404" s="3"/>
     </row>
-    <row r="405" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="405">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -12894,7 +12908,7 @@
       <c r="Z405" s="3"/>
       <c r="AA405" s="3"/>
     </row>
-    <row r="406" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="406">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -12923,7 +12937,7 @@
       <c r="Z406" s="3"/>
       <c r="AA406" s="3"/>
     </row>
-    <row r="407" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="407">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -12952,7 +12966,7 @@
       <c r="Z407" s="3"/>
       <c r="AA407" s="3"/>
     </row>
-    <row r="408" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="408">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -12981,7 +12995,7 @@
       <c r="Z408" s="3"/>
       <c r="AA408" s="3"/>
     </row>
-    <row r="409" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="409">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -13010,7 +13024,7 @@
       <c r="Z409" s="3"/>
       <c r="AA409" s="3"/>
     </row>
-    <row r="410" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="410">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -13039,7 +13053,7 @@
       <c r="Z410" s="3"/>
       <c r="AA410" s="3"/>
     </row>
-    <row r="411" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="411">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -13068,7 +13082,7 @@
       <c r="Z411" s="3"/>
       <c r="AA411" s="3"/>
     </row>
-    <row r="412" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="412">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -13097,7 +13111,7 @@
       <c r="Z412" s="3"/>
       <c r="AA412" s="3"/>
     </row>
-    <row r="413" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="413">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -13126,7 +13140,7 @@
       <c r="Z413" s="3"/>
       <c r="AA413" s="3"/>
     </row>
-    <row r="414" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="414">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -13155,7 +13169,7 @@
       <c r="Z414" s="3"/>
       <c r="AA414" s="3"/>
     </row>
-    <row r="415" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="415">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -13184,7 +13198,7 @@
       <c r="Z415" s="3"/>
       <c r="AA415" s="3"/>
     </row>
-    <row r="416" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="416">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -13213,7 +13227,7 @@
       <c r="Z416" s="3"/>
       <c r="AA416" s="3"/>
     </row>
-    <row r="417" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="417">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -13242,7 +13256,7 @@
       <c r="Z417" s="3"/>
       <c r="AA417" s="3"/>
     </row>
-    <row r="418" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="418">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -13271,7 +13285,7 @@
       <c r="Z418" s="3"/>
       <c r="AA418" s="3"/>
     </row>
-    <row r="419" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="419">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -13300,7 +13314,7 @@
       <c r="Z419" s="3"/>
       <c r="AA419" s="3"/>
     </row>
-    <row r="420" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="420">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -13329,7 +13343,7 @@
       <c r="Z420" s="3"/>
       <c r="AA420" s="3"/>
     </row>
-    <row r="421" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="421">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -13358,7 +13372,7 @@
       <c r="Z421" s="3"/>
       <c r="AA421" s="3"/>
     </row>
-    <row r="422" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="422">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -13387,7 +13401,7 @@
       <c r="Z422" s="3"/>
       <c r="AA422" s="3"/>
     </row>
-    <row r="423" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="423">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -13416,7 +13430,7 @@
       <c r="Z423" s="3"/>
       <c r="AA423" s="3"/>
     </row>
-    <row r="424" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="424">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -13445,7 +13459,7 @@
       <c r="Z424" s="3"/>
       <c r="AA424" s="3"/>
     </row>
-    <row r="425" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="425">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -13474,7 +13488,7 @@
       <c r="Z425" s="3"/>
       <c r="AA425" s="3"/>
     </row>
-    <row r="426" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="426">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -13503,7 +13517,7 @@
       <c r="Z426" s="3"/>
       <c r="AA426" s="3"/>
     </row>
-    <row r="427" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="427">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -13532,7 +13546,7 @@
       <c r="Z427" s="3"/>
       <c r="AA427" s="3"/>
     </row>
-    <row r="428" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="428">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -13561,7 +13575,7 @@
       <c r="Z428" s="3"/>
       <c r="AA428" s="3"/>
     </row>
-    <row r="429" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="429">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -13590,7 +13604,7 @@
       <c r="Z429" s="3"/>
       <c r="AA429" s="3"/>
     </row>
-    <row r="430" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="430">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -13619,7 +13633,7 @@
       <c r="Z430" s="3"/>
       <c r="AA430" s="3"/>
     </row>
-    <row r="431" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="431">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -13648,7 +13662,7 @@
       <c r="Z431" s="3"/>
       <c r="AA431" s="3"/>
     </row>
-    <row r="432" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="432">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -13677,7 +13691,7 @@
       <c r="Z432" s="3"/>
       <c r="AA432" s="3"/>
     </row>
-    <row r="433" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="433">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -13706,7 +13720,7 @@
       <c r="Z433" s="3"/>
       <c r="AA433" s="3"/>
     </row>
-    <row r="434" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="434">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -13735,7 +13749,7 @@
       <c r="Z434" s="3"/>
       <c r="AA434" s="3"/>
     </row>
-    <row r="435" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="435">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -13764,7 +13778,7 @@
       <c r="Z435" s="3"/>
       <c r="AA435" s="3"/>
     </row>
-    <row r="436" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="436">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -13793,7 +13807,7 @@
       <c r="Z436" s="3"/>
       <c r="AA436" s="3"/>
     </row>
-    <row r="437" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="437">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -13822,7 +13836,7 @@
       <c r="Z437" s="3"/>
       <c r="AA437" s="3"/>
     </row>
-    <row r="438" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="438">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -13851,7 +13865,7 @@
       <c r="Z438" s="3"/>
       <c r="AA438" s="3"/>
     </row>
-    <row r="439" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="439">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -13880,7 +13894,7 @@
       <c r="Z439" s="3"/>
       <c r="AA439" s="3"/>
     </row>
-    <row r="440" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="440">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -13909,7 +13923,7 @@
       <c r="Z440" s="3"/>
       <c r="AA440" s="3"/>
     </row>
-    <row r="441" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="441">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -13938,7 +13952,7 @@
       <c r="Z441" s="3"/>
       <c r="AA441" s="3"/>
     </row>
-    <row r="442" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="442">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -13967,7 +13981,7 @@
       <c r="Z442" s="3"/>
       <c r="AA442" s="3"/>
     </row>
-    <row r="443" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="443">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -13996,7 +14010,7 @@
       <c r="Z443" s="3"/>
       <c r="AA443" s="3"/>
     </row>
-    <row r="444" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="444">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -14025,7 +14039,7 @@
       <c r="Z444" s="3"/>
       <c r="AA444" s="3"/>
     </row>
-    <row r="445" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="445">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -14054,7 +14068,7 @@
       <c r="Z445" s="3"/>
       <c r="AA445" s="3"/>
     </row>
-    <row r="446" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="446">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -14083,7 +14097,7 @@
       <c r="Z446" s="3"/>
       <c r="AA446" s="3"/>
     </row>
-    <row r="447" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="447">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -14112,7 +14126,7 @@
       <c r="Z447" s="3"/>
       <c r="AA447" s="3"/>
     </row>
-    <row r="448" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="448">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -14141,7 +14155,7 @@
       <c r="Z448" s="3"/>
       <c r="AA448" s="3"/>
     </row>
-    <row r="449" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="449">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -14170,7 +14184,7 @@
       <c r="Z449" s="3"/>
       <c r="AA449" s="3"/>
     </row>
-    <row r="450" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="450">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -14199,7 +14213,7 @@
       <c r="Z450" s="3"/>
       <c r="AA450" s="3"/>
     </row>
-    <row r="451" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="451">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -14228,7 +14242,7 @@
       <c r="Z451" s="3"/>
       <c r="AA451" s="3"/>
     </row>
-    <row r="452" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="452">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -14257,7 +14271,7 @@
       <c r="Z452" s="3"/>
       <c r="AA452" s="3"/>
     </row>
-    <row r="453" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="453">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -14286,7 +14300,7 @@
       <c r="Z453" s="3"/>
       <c r="AA453" s="3"/>
     </row>
-    <row r="454" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="454">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -14315,7 +14329,7 @@
       <c r="Z454" s="3"/>
       <c r="AA454" s="3"/>
     </row>
-    <row r="455" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="455">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -14344,7 +14358,7 @@
       <c r="Z455" s="3"/>
       <c r="AA455" s="3"/>
     </row>
-    <row r="456" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="456">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -14373,7 +14387,7 @@
       <c r="Z456" s="3"/>
       <c r="AA456" s="3"/>
     </row>
-    <row r="457" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="457">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -14402,7 +14416,7 @@
       <c r="Z457" s="3"/>
       <c r="AA457" s="3"/>
     </row>
-    <row r="458" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="458">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -14431,7 +14445,7 @@
       <c r="Z458" s="3"/>
       <c r="AA458" s="3"/>
     </row>
-    <row r="459" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="459">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -14460,7 +14474,7 @@
       <c r="Z459" s="3"/>
       <c r="AA459" s="3"/>
     </row>
-    <row r="460" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="460">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -14489,7 +14503,7 @@
       <c r="Z460" s="3"/>
       <c r="AA460" s="3"/>
     </row>
-    <row r="461" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="461">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -14518,7 +14532,7 @@
       <c r="Z461" s="3"/>
       <c r="AA461" s="3"/>
     </row>
-    <row r="462" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="462">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -14547,7 +14561,7 @@
       <c r="Z462" s="3"/>
       <c r="AA462" s="3"/>
     </row>
-    <row r="463" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="463">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -14576,7 +14590,7 @@
       <c r="Z463" s="3"/>
       <c r="AA463" s="3"/>
     </row>
-    <row r="464" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="464">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -14605,7 +14619,7 @@
       <c r="Z464" s="3"/>
       <c r="AA464" s="3"/>
     </row>
-    <row r="465" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="465">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -14634,7 +14648,7 @@
       <c r="Z465" s="3"/>
       <c r="AA465" s="3"/>
     </row>
-    <row r="466" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="466">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -14663,7 +14677,7 @@
       <c r="Z466" s="3"/>
       <c r="AA466" s="3"/>
     </row>
-    <row r="467" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="467">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -14692,7 +14706,7 @@
       <c r="Z467" s="3"/>
       <c r="AA467" s="3"/>
     </row>
-    <row r="468" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="468">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -14721,7 +14735,7 @@
       <c r="Z468" s="3"/>
       <c r="AA468" s="3"/>
     </row>
-    <row r="469" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="469">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -14750,7 +14764,7 @@
       <c r="Z469" s="3"/>
       <c r="AA469" s="3"/>
     </row>
-    <row r="470" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="470">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -14779,7 +14793,7 @@
       <c r="Z470" s="3"/>
       <c r="AA470" s="3"/>
     </row>
-    <row r="471" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="471">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -14808,7 +14822,7 @@
       <c r="Z471" s="3"/>
       <c r="AA471" s="3"/>
     </row>
-    <row r="472" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="472">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -14837,7 +14851,7 @@
       <c r="Z472" s="3"/>
       <c r="AA472" s="3"/>
     </row>
-    <row r="473" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="473">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -14866,7 +14880,7 @@
       <c r="Z473" s="3"/>
       <c r="AA473" s="3"/>
     </row>
-    <row r="474" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="474">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -14895,7 +14909,7 @@
       <c r="Z474" s="3"/>
       <c r="AA474" s="3"/>
     </row>
-    <row r="475" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="475">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -14924,7 +14938,7 @@
       <c r="Z475" s="3"/>
       <c r="AA475" s="3"/>
     </row>
-    <row r="476" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="476">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -14953,7 +14967,7 @@
       <c r="Z476" s="3"/>
       <c r="AA476" s="3"/>
     </row>
-    <row r="477" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="477">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -14982,7 +14996,7 @@
       <c r="Z477" s="3"/>
       <c r="AA477" s="3"/>
     </row>
-    <row r="478" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="478">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -15011,7 +15025,7 @@
       <c r="Z478" s="3"/>
       <c r="AA478" s="3"/>
     </row>
-    <row r="479" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="479">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -15040,7 +15054,7 @@
       <c r="Z479" s="3"/>
       <c r="AA479" s="3"/>
     </row>
-    <row r="480" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="480">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -15069,7 +15083,7 @@
       <c r="Z480" s="3"/>
       <c r="AA480" s="3"/>
     </row>
-    <row r="481" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="481">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -15098,7 +15112,7 @@
       <c r="Z481" s="3"/>
       <c r="AA481" s="3"/>
     </row>
-    <row r="482" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="482">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -15127,7 +15141,7 @@
       <c r="Z482" s="3"/>
       <c r="AA482" s="3"/>
     </row>
-    <row r="483" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="483">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -15156,7 +15170,7 @@
       <c r="Z483" s="3"/>
       <c r="AA483" s="3"/>
     </row>
-    <row r="484" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="484">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -15185,7 +15199,7 @@
       <c r="Z484" s="3"/>
       <c r="AA484" s="3"/>
     </row>
-    <row r="485" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="485">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -15214,7 +15228,7 @@
       <c r="Z485" s="3"/>
       <c r="AA485" s="3"/>
     </row>
-    <row r="486" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="486">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -15243,7 +15257,7 @@
       <c r="Z486" s="3"/>
       <c r="AA486" s="3"/>
     </row>
-    <row r="487" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="487">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -15272,7 +15286,7 @@
       <c r="Z487" s="3"/>
       <c r="AA487" s="3"/>
     </row>
-    <row r="488" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="488">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -15301,7 +15315,7 @@
       <c r="Z488" s="3"/>
       <c r="AA488" s="3"/>
     </row>
-    <row r="489" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="489">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -15330,7 +15344,7 @@
       <c r="Z489" s="3"/>
       <c r="AA489" s="3"/>
     </row>
-    <row r="490" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="490">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -15359,7 +15373,7 @@
       <c r="Z490" s="3"/>
       <c r="AA490" s="3"/>
     </row>
-    <row r="491" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="491">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -15388,7 +15402,7 @@
       <c r="Z491" s="3"/>
       <c r="AA491" s="3"/>
     </row>
-    <row r="492" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="492">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -15417,7 +15431,7 @@
       <c r="Z492" s="3"/>
       <c r="AA492" s="3"/>
     </row>
-    <row r="493" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="493">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -15446,7 +15460,7 @@
       <c r="Z493" s="3"/>
       <c r="AA493" s="3"/>
     </row>
-    <row r="494" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="494">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -15475,7 +15489,7 @@
       <c r="Z494" s="3"/>
       <c r="AA494" s="3"/>
     </row>
-    <row r="495" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="495">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -15504,7 +15518,7 @@
       <c r="Z495" s="3"/>
       <c r="AA495" s="3"/>
     </row>
-    <row r="496" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="496">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -15533,7 +15547,7 @@
       <c r="Z496" s="3"/>
       <c r="AA496" s="3"/>
     </row>
-    <row r="497" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="497">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -15562,7 +15576,7 @@
       <c r="Z497" s="3"/>
       <c r="AA497" s="3"/>
     </row>
-    <row r="498" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="498">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -15591,7 +15605,7 @@
       <c r="Z498" s="3"/>
       <c r="AA498" s="3"/>
     </row>
-    <row r="499" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="499">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -15620,7 +15634,7 @@
       <c r="Z499" s="3"/>
       <c r="AA499" s="3"/>
     </row>
-    <row r="500" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="500">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -15649,7 +15663,7 @@
       <c r="Z500" s="3"/>
       <c r="AA500" s="3"/>
     </row>
-    <row r="501" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="501">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -15678,7 +15692,7 @@
       <c r="Z501" s="3"/>
       <c r="AA501" s="3"/>
     </row>
-    <row r="502" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="502">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -15707,7 +15721,7 @@
       <c r="Z502" s="3"/>
       <c r="AA502" s="3"/>
     </row>
-    <row r="503" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="503">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -15736,7 +15750,7 @@
       <c r="Z503" s="3"/>
       <c r="AA503" s="3"/>
     </row>
-    <row r="504" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="504">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -15765,7 +15779,7 @@
       <c r="Z504" s="3"/>
       <c r="AA504" s="3"/>
     </row>
-    <row r="505" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="505">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -15794,7 +15808,7 @@
       <c r="Z505" s="3"/>
       <c r="AA505" s="3"/>
     </row>
-    <row r="506" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="506">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -15823,7 +15837,7 @@
       <c r="Z506" s="3"/>
       <c r="AA506" s="3"/>
     </row>
-    <row r="507" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="507">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -15852,7 +15866,7 @@
       <c r="Z507" s="3"/>
       <c r="AA507" s="3"/>
     </row>
-    <row r="508" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="508">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -15881,7 +15895,7 @@
       <c r="Z508" s="3"/>
       <c r="AA508" s="3"/>
     </row>
-    <row r="509" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="509">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -15910,7 +15924,7 @@
       <c r="Z509" s="3"/>
       <c r="AA509" s="3"/>
     </row>
-    <row r="510" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="510">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -15939,7 +15953,7 @@
       <c r="Z510" s="3"/>
       <c r="AA510" s="3"/>
     </row>
-    <row r="511" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="511">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -15968,7 +15982,7 @@
       <c r="Z511" s="3"/>
       <c r="AA511" s="3"/>
     </row>
-    <row r="512" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="512">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -15997,7 +16011,7 @@
       <c r="Z512" s="3"/>
       <c r="AA512" s="3"/>
     </row>
-    <row r="513" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="513">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -16026,7 +16040,7 @@
       <c r="Z513" s="3"/>
       <c r="AA513" s="3"/>
     </row>
-    <row r="514" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="514">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -16055,7 +16069,7 @@
       <c r="Z514" s="3"/>
       <c r="AA514" s="3"/>
     </row>
-    <row r="515" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="515">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -16084,7 +16098,7 @@
       <c r="Z515" s="3"/>
       <c r="AA515" s="3"/>
     </row>
-    <row r="516" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="516">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -16113,7 +16127,7 @@
       <c r="Z516" s="3"/>
       <c r="AA516" s="3"/>
     </row>
-    <row r="517" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="517">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -16142,7 +16156,7 @@
       <c r="Z517" s="3"/>
       <c r="AA517" s="3"/>
     </row>
-    <row r="518" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="518">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -16171,7 +16185,7 @@
       <c r="Z518" s="3"/>
       <c r="AA518" s="3"/>
     </row>
-    <row r="519" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="519">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -16200,7 +16214,7 @@
       <c r="Z519" s="3"/>
       <c r="AA519" s="3"/>
     </row>
-    <row r="520" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="520">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -16229,7 +16243,7 @@
       <c r="Z520" s="3"/>
       <c r="AA520" s="3"/>
     </row>
-    <row r="521" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="521">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -16258,7 +16272,7 @@
       <c r="Z521" s="3"/>
       <c r="AA521" s="3"/>
     </row>
-    <row r="522" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="522">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -16287,7 +16301,7 @@
       <c r="Z522" s="3"/>
       <c r="AA522" s="3"/>
     </row>
-    <row r="523" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="523">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -16316,7 +16330,7 @@
       <c r="Z523" s="3"/>
       <c r="AA523" s="3"/>
     </row>
-    <row r="524" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="524">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -16345,7 +16359,7 @@
       <c r="Z524" s="3"/>
       <c r="AA524" s="3"/>
     </row>
-    <row r="525" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="525">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -16374,7 +16388,7 @@
       <c r="Z525" s="3"/>
       <c r="AA525" s="3"/>
     </row>
-    <row r="526" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="526">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -16403,7 +16417,7 @@
       <c r="Z526" s="3"/>
       <c r="AA526" s="3"/>
     </row>
-    <row r="527" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="527">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -16432,7 +16446,7 @@
       <c r="Z527" s="3"/>
       <c r="AA527" s="3"/>
     </row>
-    <row r="528" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="528">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -16461,7 +16475,7 @@
       <c r="Z528" s="3"/>
       <c r="AA528" s="3"/>
     </row>
-    <row r="529" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="529">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -16490,7 +16504,7 @@
       <c r="Z529" s="3"/>
       <c r="AA529" s="3"/>
     </row>
-    <row r="530" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="530">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -16519,7 +16533,7 @@
       <c r="Z530" s="3"/>
       <c r="AA530" s="3"/>
     </row>
-    <row r="531" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="531">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -16548,7 +16562,7 @@
       <c r="Z531" s="3"/>
       <c r="AA531" s="3"/>
     </row>
-    <row r="532" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="532">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -16577,7 +16591,7 @@
       <c r="Z532" s="3"/>
       <c r="AA532" s="3"/>
     </row>
-    <row r="533" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="533">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -16606,7 +16620,7 @@
       <c r="Z533" s="3"/>
       <c r="AA533" s="3"/>
     </row>
-    <row r="534" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="534">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -16635,7 +16649,7 @@
       <c r="Z534" s="3"/>
       <c r="AA534" s="3"/>
     </row>
-    <row r="535" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="535">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -16664,7 +16678,7 @@
       <c r="Z535" s="3"/>
       <c r="AA535" s="3"/>
     </row>
-    <row r="536" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="536">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -16693,7 +16707,7 @@
       <c r="Z536" s="3"/>
       <c r="AA536" s="3"/>
     </row>
-    <row r="537" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="537">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -16722,7 +16736,7 @@
       <c r="Z537" s="3"/>
       <c r="AA537" s="3"/>
     </row>
-    <row r="538" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="538">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -16751,7 +16765,7 @@
       <c r="Z538" s="3"/>
       <c r="AA538" s="3"/>
     </row>
-    <row r="539" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="539">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -16780,7 +16794,7 @@
       <c r="Z539" s="3"/>
       <c r="AA539" s="3"/>
     </row>
-    <row r="540" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="540">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -16809,7 +16823,7 @@
       <c r="Z540" s="3"/>
       <c r="AA540" s="3"/>
     </row>
-    <row r="541" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="541">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -16838,7 +16852,7 @@
       <c r="Z541" s="3"/>
       <c r="AA541" s="3"/>
     </row>
-    <row r="542" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="542">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -16867,7 +16881,7 @@
       <c r="Z542" s="3"/>
       <c r="AA542" s="3"/>
     </row>
-    <row r="543" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="543">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -16896,7 +16910,7 @@
       <c r="Z543" s="3"/>
       <c r="AA543" s="3"/>
     </row>
-    <row r="544" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="544">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -16925,7 +16939,7 @@
       <c r="Z544" s="3"/>
       <c r="AA544" s="3"/>
     </row>
-    <row r="545" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="545">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -16954,7 +16968,7 @@
       <c r="Z545" s="3"/>
       <c r="AA545" s="3"/>
     </row>
-    <row r="546" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="546">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -16983,7 +16997,7 @@
       <c r="Z546" s="3"/>
       <c r="AA546" s="3"/>
     </row>
-    <row r="547" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="547">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -17012,7 +17026,7 @@
       <c r="Z547" s="3"/>
       <c r="AA547" s="3"/>
     </row>
-    <row r="548" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="548">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -17041,7 +17055,7 @@
       <c r="Z548" s="3"/>
       <c r="AA548" s="3"/>
     </row>
-    <row r="549" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="549">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -17070,7 +17084,7 @@
       <c r="Z549" s="3"/>
       <c r="AA549" s="3"/>
     </row>
-    <row r="550" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="550">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -17099,7 +17113,7 @@
       <c r="Z550" s="3"/>
       <c r="AA550" s="3"/>
     </row>
-    <row r="551" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="551">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -17128,7 +17142,7 @@
       <c r="Z551" s="3"/>
       <c r="AA551" s="3"/>
     </row>
-    <row r="552" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="552">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -17157,7 +17171,7 @@
       <c r="Z552" s="3"/>
       <c r="AA552" s="3"/>
     </row>
-    <row r="553" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="553">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -17186,7 +17200,7 @@
       <c r="Z553" s="3"/>
       <c r="AA553" s="3"/>
     </row>
-    <row r="554" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="554">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -17215,7 +17229,7 @@
       <c r="Z554" s="3"/>
       <c r="AA554" s="3"/>
     </row>
-    <row r="555" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="555">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -17244,7 +17258,7 @@
       <c r="Z555" s="3"/>
       <c r="AA555" s="3"/>
     </row>
-    <row r="556" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="556">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -17273,7 +17287,7 @@
       <c r="Z556" s="3"/>
       <c r="AA556" s="3"/>
     </row>
-    <row r="557" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="557">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -17302,7 +17316,7 @@
       <c r="Z557" s="3"/>
       <c r="AA557" s="3"/>
     </row>
-    <row r="558" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="558">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -17331,7 +17345,7 @@
       <c r="Z558" s="3"/>
       <c r="AA558" s="3"/>
     </row>
-    <row r="559" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="559">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -17360,7 +17374,7 @@
       <c r="Z559" s="3"/>
       <c r="AA559" s="3"/>
     </row>
-    <row r="560" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="560">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -17389,7 +17403,7 @@
       <c r="Z560" s="3"/>
       <c r="AA560" s="3"/>
     </row>
-    <row r="561" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="561">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -17418,7 +17432,7 @@
       <c r="Z561" s="3"/>
       <c r="AA561" s="3"/>
     </row>
-    <row r="562" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="562">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -17447,7 +17461,7 @@
       <c r="Z562" s="3"/>
       <c r="AA562" s="3"/>
     </row>
-    <row r="563" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="563">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -17476,7 +17490,7 @@
       <c r="Z563" s="3"/>
       <c r="AA563" s="3"/>
     </row>
-    <row r="564" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="564">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -17505,7 +17519,7 @@
       <c r="Z564" s="3"/>
       <c r="AA564" s="3"/>
     </row>
-    <row r="565" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="565">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -17534,7 +17548,7 @@
       <c r="Z565" s="3"/>
       <c r="AA565" s="3"/>
     </row>
-    <row r="566" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="566">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -17563,7 +17577,7 @@
       <c r="Z566" s="3"/>
       <c r="AA566" s="3"/>
     </row>
-    <row r="567" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="567">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -17592,7 +17606,7 @@
       <c r="Z567" s="3"/>
       <c r="AA567" s="3"/>
     </row>
-    <row r="568" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="568">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -17621,7 +17635,7 @@
       <c r="Z568" s="3"/>
       <c r="AA568" s="3"/>
     </row>
-    <row r="569" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="569">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -17650,7 +17664,7 @@
       <c r="Z569" s="3"/>
       <c r="AA569" s="3"/>
     </row>
-    <row r="570" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="570">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -17679,7 +17693,7 @@
       <c r="Z570" s="3"/>
       <c r="AA570" s="3"/>
     </row>
-    <row r="571" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="571">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -17708,7 +17722,7 @@
       <c r="Z571" s="3"/>
       <c r="AA571" s="3"/>
     </row>
-    <row r="572" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="572">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -17737,7 +17751,7 @@
       <c r="Z572" s="3"/>
       <c r="AA572" s="3"/>
     </row>
-    <row r="573" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="573">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -17766,7 +17780,7 @@
       <c r="Z573" s="3"/>
       <c r="AA573" s="3"/>
     </row>
-    <row r="574" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="574">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -17795,7 +17809,7 @@
       <c r="Z574" s="3"/>
       <c r="AA574" s="3"/>
     </row>
-    <row r="575" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="575">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -17824,7 +17838,7 @@
       <c r="Z575" s="3"/>
       <c r="AA575" s="3"/>
     </row>
-    <row r="576" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="576">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -17853,7 +17867,7 @@
       <c r="Z576" s="3"/>
       <c r="AA576" s="3"/>
     </row>
-    <row r="577" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="577">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -17882,7 +17896,7 @@
       <c r="Z577" s="3"/>
       <c r="AA577" s="3"/>
     </row>
-    <row r="578" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="578">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -17911,7 +17925,7 @@
       <c r="Z578" s="3"/>
       <c r="AA578" s="3"/>
     </row>
-    <row r="579" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="579">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -17940,7 +17954,7 @@
       <c r="Z579" s="3"/>
       <c r="AA579" s="3"/>
     </row>
-    <row r="580" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="580">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -17969,7 +17983,7 @@
       <c r="Z580" s="3"/>
       <c r="AA580" s="3"/>
     </row>
-    <row r="581" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="581">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -17998,7 +18012,7 @@
       <c r="Z581" s="3"/>
       <c r="AA581" s="3"/>
     </row>
-    <row r="582" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="582">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -18027,7 +18041,7 @@
       <c r="Z582" s="3"/>
       <c r="AA582" s="3"/>
     </row>
-    <row r="583" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="583">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -18056,7 +18070,7 @@
       <c r="Z583" s="3"/>
       <c r="AA583" s="3"/>
     </row>
-    <row r="584" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="584">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -18085,7 +18099,7 @@
       <c r="Z584" s="3"/>
       <c r="AA584" s="3"/>
     </row>
-    <row r="585" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="585">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -18114,7 +18128,7 @@
       <c r="Z585" s="3"/>
       <c r="AA585" s="3"/>
     </row>
-    <row r="586" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="586">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -18143,7 +18157,7 @@
       <c r="Z586" s="3"/>
       <c r="AA586" s="3"/>
     </row>
-    <row r="587" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="587">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -18172,7 +18186,7 @@
       <c r="Z587" s="3"/>
       <c r="AA587" s="3"/>
     </row>
-    <row r="588" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="588">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -18201,7 +18215,7 @@
       <c r="Z588" s="3"/>
       <c r="AA588" s="3"/>
     </row>
-    <row r="589" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="589">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -18230,7 +18244,7 @@
       <c r="Z589" s="3"/>
       <c r="AA589" s="3"/>
     </row>
-    <row r="590" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="590">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -18259,7 +18273,7 @@
       <c r="Z590" s="3"/>
       <c r="AA590" s="3"/>
     </row>
-    <row r="591" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="591">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -18288,7 +18302,7 @@
       <c r="Z591" s="3"/>
       <c r="AA591" s="3"/>
     </row>
-    <row r="592" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="592">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -18317,7 +18331,7 @@
       <c r="Z592" s="3"/>
       <c r="AA592" s="3"/>
     </row>
-    <row r="593" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="593">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -18346,7 +18360,7 @@
       <c r="Z593" s="3"/>
       <c r="AA593" s="3"/>
     </row>
-    <row r="594" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="594">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -18375,7 +18389,7 @@
       <c r="Z594" s="3"/>
       <c r="AA594" s="3"/>
     </row>
-    <row r="595" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="595">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -18404,7 +18418,7 @@
       <c r="Z595" s="3"/>
       <c r="AA595" s="3"/>
     </row>
-    <row r="596" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="596">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -18433,7 +18447,7 @@
       <c r="Z596" s="3"/>
       <c r="AA596" s="3"/>
     </row>
-    <row r="597" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="597">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -18462,7 +18476,7 @@
       <c r="Z597" s="3"/>
       <c r="AA597" s="3"/>
     </row>
-    <row r="598" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="598">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -18491,7 +18505,7 @@
       <c r="Z598" s="3"/>
       <c r="AA598" s="3"/>
     </row>
-    <row r="599" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="599">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -18520,7 +18534,7 @@
       <c r="Z599" s="3"/>
       <c r="AA599" s="3"/>
     </row>
-    <row r="600" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="600">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -18549,7 +18563,7 @@
       <c r="Z600" s="3"/>
       <c r="AA600" s="3"/>
     </row>
-    <row r="601" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="601">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -18578,7 +18592,7 @@
       <c r="Z601" s="3"/>
       <c r="AA601" s="3"/>
     </row>
-    <row r="602" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="602">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -18607,7 +18621,7 @@
       <c r="Z602" s="3"/>
       <c r="AA602" s="3"/>
     </row>
-    <row r="603" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="603">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -18636,7 +18650,7 @@
       <c r="Z603" s="3"/>
       <c r="AA603" s="3"/>
     </row>
-    <row r="604" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="604">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -18665,7 +18679,7 @@
       <c r="Z604" s="3"/>
       <c r="AA604" s="3"/>
     </row>
-    <row r="605" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="605">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -18694,7 +18708,7 @@
       <c r="Z605" s="3"/>
       <c r="AA605" s="3"/>
     </row>
-    <row r="606" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="606">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -18723,7 +18737,7 @@
       <c r="Z606" s="3"/>
       <c r="AA606" s="3"/>
     </row>
-    <row r="607" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="607">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -18752,7 +18766,7 @@
       <c r="Z607" s="3"/>
       <c r="AA607" s="3"/>
     </row>
-    <row r="608" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="608">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -18781,7 +18795,7 @@
       <c r="Z608" s="3"/>
       <c r="AA608" s="3"/>
     </row>
-    <row r="609" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="609">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -18810,7 +18824,7 @@
       <c r="Z609" s="3"/>
       <c r="AA609" s="3"/>
     </row>
-    <row r="610" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="610">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -18839,7 +18853,7 @@
       <c r="Z610" s="3"/>
       <c r="AA610" s="3"/>
     </row>
-    <row r="611" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="611">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -18868,7 +18882,7 @@
       <c r="Z611" s="3"/>
       <c r="AA611" s="3"/>
     </row>
-    <row r="612" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="612">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -18897,7 +18911,7 @@
       <c r="Z612" s="3"/>
       <c r="AA612" s="3"/>
     </row>
-    <row r="613" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="613">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -18926,7 +18940,7 @@
       <c r="Z613" s="3"/>
       <c r="AA613" s="3"/>
     </row>
-    <row r="614" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="614">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -18955,7 +18969,7 @@
       <c r="Z614" s="3"/>
       <c r="AA614" s="3"/>
     </row>
-    <row r="615" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="615">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -18984,7 +18998,7 @@
       <c r="Z615" s="3"/>
       <c r="AA615" s="3"/>
     </row>
-    <row r="616" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="616">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -19013,7 +19027,7 @@
       <c r="Z616" s="3"/>
       <c r="AA616" s="3"/>
     </row>
-    <row r="617" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="617">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -19042,7 +19056,7 @@
       <c r="Z617" s="3"/>
       <c r="AA617" s="3"/>
     </row>
-    <row r="618" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="618">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -19071,7 +19085,7 @@
       <c r="Z618" s="3"/>
       <c r="AA618" s="3"/>
     </row>
-    <row r="619" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="619">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -19100,7 +19114,7 @@
       <c r="Z619" s="3"/>
       <c r="AA619" s="3"/>
     </row>
-    <row r="620" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="620">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -19129,7 +19143,7 @@
       <c r="Z620" s="3"/>
       <c r="AA620" s="3"/>
     </row>
-    <row r="621" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="621">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -19158,7 +19172,7 @@
       <c r="Z621" s="3"/>
       <c r="AA621" s="3"/>
     </row>
-    <row r="622" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="622">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -19187,7 +19201,7 @@
       <c r="Z622" s="3"/>
       <c r="AA622" s="3"/>
     </row>
-    <row r="623" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="623">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -19216,7 +19230,7 @@
       <c r="Z623" s="3"/>
       <c r="AA623" s="3"/>
     </row>
-    <row r="624" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="624">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -19245,7 +19259,7 @@
       <c r="Z624" s="3"/>
       <c r="AA624" s="3"/>
     </row>
-    <row r="625" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="625">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -19274,7 +19288,7 @@
       <c r="Z625" s="3"/>
       <c r="AA625" s="3"/>
     </row>
-    <row r="626" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="626">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -19303,7 +19317,7 @@
       <c r="Z626" s="3"/>
       <c r="AA626" s="3"/>
     </row>
-    <row r="627" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="627">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -19332,7 +19346,7 @@
       <c r="Z627" s="3"/>
       <c r="AA627" s="3"/>
     </row>
-    <row r="628" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="628">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -19361,7 +19375,7 @@
       <c r="Z628" s="3"/>
       <c r="AA628" s="3"/>
     </row>
-    <row r="629" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="629">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -19390,7 +19404,7 @@
       <c r="Z629" s="3"/>
       <c r="AA629" s="3"/>
     </row>
-    <row r="630" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="630">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -19419,7 +19433,7 @@
       <c r="Z630" s="3"/>
       <c r="AA630" s="3"/>
     </row>
-    <row r="631" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="631">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -19448,7 +19462,7 @@
       <c r="Z631" s="3"/>
       <c r="AA631" s="3"/>
     </row>
-    <row r="632" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="632">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -19477,7 +19491,7 @@
       <c r="Z632" s="3"/>
       <c r="AA632" s="3"/>
     </row>
-    <row r="633" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="633">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -19506,7 +19520,7 @@
       <c r="Z633" s="3"/>
       <c r="AA633" s="3"/>
     </row>
-    <row r="634" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="634">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -19535,7 +19549,7 @@
       <c r="Z634" s="3"/>
       <c r="AA634" s="3"/>
     </row>
-    <row r="635" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="635">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -19564,7 +19578,7 @@
       <c r="Z635" s="3"/>
       <c r="AA635" s="3"/>
     </row>
-    <row r="636" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="636">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -19593,7 +19607,7 @@
       <c r="Z636" s="3"/>
       <c r="AA636" s="3"/>
     </row>
-    <row r="637" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="637">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -19622,7 +19636,7 @@
       <c r="Z637" s="3"/>
       <c r="AA637" s="3"/>
     </row>
-    <row r="638" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="638">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -19651,7 +19665,7 @@
       <c r="Z638" s="3"/>
       <c r="AA638" s="3"/>
     </row>
-    <row r="639" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="639">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -19680,7 +19694,7 @@
       <c r="Z639" s="3"/>
       <c r="AA639" s="3"/>
     </row>
-    <row r="640" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="640">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -19709,7 +19723,7 @@
       <c r="Z640" s="3"/>
       <c r="AA640" s="3"/>
     </row>
-    <row r="641" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="641">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -19738,7 +19752,7 @@
       <c r="Z641" s="3"/>
       <c r="AA641" s="3"/>
     </row>
-    <row r="642" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="642">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -19767,7 +19781,7 @@
       <c r="Z642" s="3"/>
       <c r="AA642" s="3"/>
     </row>
-    <row r="643" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="643">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -19796,7 +19810,7 @@
       <c r="Z643" s="3"/>
       <c r="AA643" s="3"/>
     </row>
-    <row r="644" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="644">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -19825,7 +19839,7 @@
       <c r="Z644" s="3"/>
       <c r="AA644" s="3"/>
     </row>
-    <row r="645" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="645">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -19854,7 +19868,7 @@
       <c r="Z645" s="3"/>
       <c r="AA645" s="3"/>
     </row>
-    <row r="646" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="646">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -19883,7 +19897,7 @@
       <c r="Z646" s="3"/>
       <c r="AA646" s="3"/>
     </row>
-    <row r="647" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="647">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -19912,7 +19926,7 @@
       <c r="Z647" s="3"/>
       <c r="AA647" s="3"/>
     </row>
-    <row r="648" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="648">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -19941,7 +19955,7 @@
       <c r="Z648" s="3"/>
       <c r="AA648" s="3"/>
     </row>
-    <row r="649" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="649">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -19970,7 +19984,7 @@
       <c r="Z649" s="3"/>
       <c r="AA649" s="3"/>
     </row>
-    <row r="650" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="650">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -19999,7 +20013,7 @@
       <c r="Z650" s="3"/>
       <c r="AA650" s="3"/>
     </row>
-    <row r="651" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="651">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -20028,7 +20042,7 @@
       <c r="Z651" s="3"/>
       <c r="AA651" s="3"/>
     </row>
-    <row r="652" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="652">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -20057,7 +20071,7 @@
       <c r="Z652" s="3"/>
       <c r="AA652" s="3"/>
     </row>
-    <row r="653" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="653">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -20086,7 +20100,7 @@
       <c r="Z653" s="3"/>
       <c r="AA653" s="3"/>
     </row>
-    <row r="654" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="654">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -20115,7 +20129,7 @@
       <c r="Z654" s="3"/>
       <c r="AA654" s="3"/>
     </row>
-    <row r="655" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="655">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -20144,7 +20158,7 @@
       <c r="Z655" s="3"/>
       <c r="AA655" s="3"/>
     </row>
-    <row r="656" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="656">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -20173,7 +20187,7 @@
       <c r="Z656" s="3"/>
       <c r="AA656" s="3"/>
     </row>
-    <row r="657" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="657">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -20202,7 +20216,7 @@
       <c r="Z657" s="3"/>
       <c r="AA657" s="3"/>
     </row>
-    <row r="658" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="658">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -20231,7 +20245,7 @@
       <c r="Z658" s="3"/>
       <c r="AA658" s="3"/>
     </row>
-    <row r="659" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="659">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -20260,7 +20274,7 @@
       <c r="Z659" s="3"/>
       <c r="AA659" s="3"/>
     </row>
-    <row r="660" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="660">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -20289,7 +20303,7 @@
       <c r="Z660" s="3"/>
       <c r="AA660" s="3"/>
     </row>
-    <row r="661" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="661">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -20318,7 +20332,7 @@
       <c r="Z661" s="3"/>
       <c r="AA661" s="3"/>
     </row>
-    <row r="662" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="662">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -20347,7 +20361,7 @@
       <c r="Z662" s="3"/>
       <c r="AA662" s="3"/>
     </row>
-    <row r="663" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="663">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -20376,7 +20390,7 @@
       <c r="Z663" s="3"/>
       <c r="AA663" s="3"/>
     </row>
-    <row r="664" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="664">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -20405,7 +20419,7 @@
       <c r="Z664" s="3"/>
       <c r="AA664" s="3"/>
     </row>
-    <row r="665" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="665">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -20434,7 +20448,7 @@
       <c r="Z665" s="3"/>
       <c r="AA665" s="3"/>
     </row>
-    <row r="666" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="666">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -20463,7 +20477,7 @@
       <c r="Z666" s="3"/>
       <c r="AA666" s="3"/>
     </row>
-    <row r="667" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="667">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -20492,7 +20506,7 @@
       <c r="Z667" s="3"/>
       <c r="AA667" s="3"/>
     </row>
-    <row r="668" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="668">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -20521,7 +20535,7 @@
       <c r="Z668" s="3"/>
       <c r="AA668" s="3"/>
     </row>
-    <row r="669" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="669">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -20550,7 +20564,7 @@
       <c r="Z669" s="3"/>
       <c r="AA669" s="3"/>
     </row>
-    <row r="670" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="670">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -20579,7 +20593,7 @@
       <c r="Z670" s="3"/>
       <c r="AA670" s="3"/>
     </row>
-    <row r="671" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="671">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -20608,7 +20622,7 @@
       <c r="Z671" s="3"/>
       <c r="AA671" s="3"/>
     </row>
-    <row r="672" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="672">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -20637,7 +20651,7 @@
       <c r="Z672" s="3"/>
       <c r="AA672" s="3"/>
     </row>
-    <row r="673" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="673">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -20666,7 +20680,7 @@
       <c r="Z673" s="3"/>
       <c r="AA673" s="3"/>
     </row>
-    <row r="674" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="674">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -20695,7 +20709,7 @@
       <c r="Z674" s="3"/>
       <c r="AA674" s="3"/>
     </row>
-    <row r="675" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="675">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -20724,7 +20738,7 @@
       <c r="Z675" s="3"/>
       <c r="AA675" s="3"/>
     </row>
-    <row r="676" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="676">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -20753,7 +20767,7 @@
       <c r="Z676" s="3"/>
       <c r="AA676" s="3"/>
     </row>
-    <row r="677" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="677">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -20782,7 +20796,7 @@
       <c r="Z677" s="3"/>
       <c r="AA677" s="3"/>
     </row>
-    <row r="678" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="678">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -20811,7 +20825,7 @@
       <c r="Z678" s="3"/>
       <c r="AA678" s="3"/>
     </row>
-    <row r="679" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="679">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -20840,7 +20854,7 @@
       <c r="Z679" s="3"/>
       <c r="AA679" s="3"/>
     </row>
-    <row r="680" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="680">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -20869,7 +20883,7 @@
       <c r="Z680" s="3"/>
       <c r="AA680" s="3"/>
     </row>
-    <row r="681" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="681">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -20898,7 +20912,7 @@
       <c r="Z681" s="3"/>
       <c r="AA681" s="3"/>
     </row>
-    <row r="682" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="682">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -20927,7 +20941,7 @@
       <c r="Z682" s="3"/>
       <c r="AA682" s="3"/>
     </row>
-    <row r="683" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="683">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -20956,7 +20970,7 @@
       <c r="Z683" s="3"/>
       <c r="AA683" s="3"/>
     </row>
-    <row r="684" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="684">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -20985,7 +20999,7 @@
       <c r="Z684" s="3"/>
       <c r="AA684" s="3"/>
     </row>
-    <row r="685" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="685">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -21014,7 +21028,7 @@
       <c r="Z685" s="3"/>
       <c r="AA685" s="3"/>
     </row>
-    <row r="686" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="686">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -21043,7 +21057,7 @@
       <c r="Z686" s="3"/>
       <c r="AA686" s="3"/>
     </row>
-    <row r="687" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="687">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -21072,7 +21086,7 @@
       <c r="Z687" s="3"/>
       <c r="AA687" s="3"/>
     </row>
-    <row r="688" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="688">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -21101,7 +21115,7 @@
       <c r="Z688" s="3"/>
       <c r="AA688" s="3"/>
     </row>
-    <row r="689" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="689">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -21130,7 +21144,7 @@
       <c r="Z689" s="3"/>
       <c r="AA689" s="3"/>
     </row>
-    <row r="690" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="690">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -21159,7 +21173,7 @@
       <c r="Z690" s="3"/>
       <c r="AA690" s="3"/>
     </row>
-    <row r="691" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="691">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -21188,7 +21202,7 @@
       <c r="Z691" s="3"/>
       <c r="AA691" s="3"/>
     </row>
-    <row r="692" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="692">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -21217,7 +21231,7 @@
       <c r="Z692" s="3"/>
       <c r="AA692" s="3"/>
     </row>
-    <row r="693" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="693">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -21246,7 +21260,7 @@
       <c r="Z693" s="3"/>
       <c r="AA693" s="3"/>
     </row>
-    <row r="694" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="694">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -21275,7 +21289,7 @@
       <c r="Z694" s="3"/>
       <c r="AA694" s="3"/>
     </row>
-    <row r="695" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="695">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -21304,7 +21318,7 @@
       <c r="Z695" s="3"/>
       <c r="AA695" s="3"/>
     </row>
-    <row r="696" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="696">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -21333,7 +21347,7 @@
       <c r="Z696" s="3"/>
       <c r="AA696" s="3"/>
     </row>
-    <row r="697" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="697">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -21362,7 +21376,7 @@
       <c r="Z697" s="3"/>
       <c r="AA697" s="3"/>
     </row>
-    <row r="698" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="698">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -21391,7 +21405,7 @@
       <c r="Z698" s="3"/>
       <c r="AA698" s="3"/>
     </row>
-    <row r="699" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="699">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -21420,7 +21434,7 @@
       <c r="Z699" s="3"/>
       <c r="AA699" s="3"/>
     </row>
-    <row r="700" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="700">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -21449,7 +21463,7 @@
       <c r="Z700" s="3"/>
       <c r="AA700" s="3"/>
     </row>
-    <row r="701" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="701">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -21478,7 +21492,7 @@
       <c r="Z701" s="3"/>
       <c r="AA701" s="3"/>
     </row>
-    <row r="702" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="702">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -21507,7 +21521,7 @@
       <c r="Z702" s="3"/>
       <c r="AA702" s="3"/>
     </row>
-    <row r="703" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="703">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -21536,7 +21550,7 @@
       <c r="Z703" s="3"/>
       <c r="AA703" s="3"/>
     </row>
-    <row r="704" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="704">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -21565,7 +21579,7 @@
       <c r="Z704" s="3"/>
       <c r="AA704" s="3"/>
     </row>
-    <row r="705" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="705">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -21594,7 +21608,7 @@
       <c r="Z705" s="3"/>
       <c r="AA705" s="3"/>
     </row>
-    <row r="706" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="706">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -21623,7 +21637,7 @@
       <c r="Z706" s="3"/>
       <c r="AA706" s="3"/>
     </row>
-    <row r="707" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="707">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -21652,7 +21666,7 @@
       <c r="Z707" s="3"/>
       <c r="AA707" s="3"/>
     </row>
-    <row r="708" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="708">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -21681,7 +21695,7 @@
       <c r="Z708" s="3"/>
       <c r="AA708" s="3"/>
     </row>
-    <row r="709" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="709">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -21710,7 +21724,7 @@
       <c r="Z709" s="3"/>
       <c r="AA709" s="3"/>
     </row>
-    <row r="710" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="710">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -21739,7 +21753,7 @@
       <c r="Z710" s="3"/>
       <c r="AA710" s="3"/>
     </row>
-    <row r="711" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="711">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -21768,7 +21782,7 @@
       <c r="Z711" s="3"/>
       <c r="AA711" s="3"/>
     </row>
-    <row r="712" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="712">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -21797,7 +21811,7 @@
       <c r="Z712" s="3"/>
       <c r="AA712" s="3"/>
     </row>
-    <row r="713" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="713">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -21826,7 +21840,7 @@
       <c r="Z713" s="3"/>
       <c r="AA713" s="3"/>
     </row>
-    <row r="714" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="714">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -21855,7 +21869,7 @@
       <c r="Z714" s="3"/>
       <c r="AA714" s="3"/>
     </row>
-    <row r="715" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="715">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -21884,7 +21898,7 @@
       <c r="Z715" s="3"/>
       <c r="AA715" s="3"/>
     </row>
-    <row r="716" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="716">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -21913,7 +21927,7 @@
       <c r="Z716" s="3"/>
       <c r="AA716" s="3"/>
     </row>
-    <row r="717" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="717">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -21942,7 +21956,7 @@
       <c r="Z717" s="3"/>
       <c r="AA717" s="3"/>
     </row>
-    <row r="718" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="718">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -21971,7 +21985,7 @@
       <c r="Z718" s="3"/>
       <c r="AA718" s="3"/>
     </row>
-    <row r="719" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="719">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -22000,7 +22014,7 @@
       <c r="Z719" s="3"/>
       <c r="AA719" s="3"/>
     </row>
-    <row r="720" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="720">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -22029,7 +22043,7 @@
       <c r="Z720" s="3"/>
       <c r="AA720" s="3"/>
     </row>
-    <row r="721" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="721">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -22058,7 +22072,7 @@
       <c r="Z721" s="3"/>
       <c r="AA721" s="3"/>
     </row>
-    <row r="722" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="722">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -22087,7 +22101,7 @@
       <c r="Z722" s="3"/>
       <c r="AA722" s="3"/>
     </row>
-    <row r="723" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="723">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -22116,7 +22130,7 @@
       <c r="Z723" s="3"/>
       <c r="AA723" s="3"/>
     </row>
-    <row r="724" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="724">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -22145,7 +22159,7 @@
       <c r="Z724" s="3"/>
       <c r="AA724" s="3"/>
     </row>
-    <row r="725" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="725">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -22174,7 +22188,7 @@
       <c r="Z725" s="3"/>
       <c r="AA725" s="3"/>
     </row>
-    <row r="726" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="726">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -22203,7 +22217,7 @@
       <c r="Z726" s="3"/>
       <c r="AA726" s="3"/>
     </row>
-    <row r="727" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="727">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -22232,7 +22246,7 @@
       <c r="Z727" s="3"/>
       <c r="AA727" s="3"/>
     </row>
-    <row r="728" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="728">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -22261,7 +22275,7 @@
       <c r="Z728" s="3"/>
       <c r="AA728" s="3"/>
     </row>
-    <row r="729" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="729">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -22290,7 +22304,7 @@
       <c r="Z729" s="3"/>
       <c r="AA729" s="3"/>
     </row>
-    <row r="730" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="730">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -22319,7 +22333,7 @@
       <c r="Z730" s="3"/>
       <c r="AA730" s="3"/>
     </row>
-    <row r="731" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="731">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -22348,7 +22362,7 @@
       <c r="Z731" s="3"/>
       <c r="AA731" s="3"/>
     </row>
-    <row r="732" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="732">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -22377,7 +22391,7 @@
       <c r="Z732" s="3"/>
       <c r="AA732" s="3"/>
     </row>
-    <row r="733" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="733">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -22406,7 +22420,7 @@
       <c r="Z733" s="3"/>
       <c r="AA733" s="3"/>
     </row>
-    <row r="734" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="734">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -22435,7 +22449,7 @@
       <c r="Z734" s="3"/>
       <c r="AA734" s="3"/>
     </row>
-    <row r="735" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="735">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -22464,7 +22478,7 @@
       <c r="Z735" s="3"/>
       <c r="AA735" s="3"/>
     </row>
-    <row r="736" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="736">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -22493,7 +22507,7 @@
       <c r="Z736" s="3"/>
       <c r="AA736" s="3"/>
     </row>
-    <row r="737" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="737">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -22522,7 +22536,7 @@
       <c r="Z737" s="3"/>
       <c r="AA737" s="3"/>
     </row>
-    <row r="738" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="738">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -22551,7 +22565,7 @@
       <c r="Z738" s="3"/>
       <c r="AA738" s="3"/>
     </row>
-    <row r="739" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="739">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -22580,7 +22594,7 @@
       <c r="Z739" s="3"/>
       <c r="AA739" s="3"/>
     </row>
-    <row r="740" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="740">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -22609,7 +22623,7 @@
       <c r="Z740" s="3"/>
       <c r="AA740" s="3"/>
     </row>
-    <row r="741" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="741">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -22638,7 +22652,7 @@
       <c r="Z741" s="3"/>
       <c r="AA741" s="3"/>
     </row>
-    <row r="742" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="742">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -22667,7 +22681,7 @@
       <c r="Z742" s="3"/>
       <c r="AA742" s="3"/>
     </row>
-    <row r="743" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="743">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -22696,7 +22710,7 @@
       <c r="Z743" s="3"/>
       <c r="AA743" s="3"/>
     </row>
-    <row r="744" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="744">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -22725,7 +22739,7 @@
       <c r="Z744" s="3"/>
       <c r="AA744" s="3"/>
     </row>
-    <row r="745" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="745">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -22754,7 +22768,7 @@
       <c r="Z745" s="3"/>
       <c r="AA745" s="3"/>
     </row>
-    <row r="746" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="746">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -22783,7 +22797,7 @@
       <c r="Z746" s="3"/>
       <c r="AA746" s="3"/>
     </row>
-    <row r="747" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="747">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -22812,7 +22826,7 @@
       <c r="Z747" s="3"/>
       <c r="AA747" s="3"/>
     </row>
-    <row r="748" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="748">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -22841,7 +22855,7 @@
       <c r="Z748" s="3"/>
       <c r="AA748" s="3"/>
     </row>
-    <row r="749" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="749">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -22870,7 +22884,7 @@
       <c r="Z749" s="3"/>
       <c r="AA749" s="3"/>
     </row>
-    <row r="750" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="750">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -22899,7 +22913,7 @@
       <c r="Z750" s="3"/>
       <c r="AA750" s="3"/>
     </row>
-    <row r="751" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="751">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -22928,7 +22942,7 @@
       <c r="Z751" s="3"/>
       <c r="AA751" s="3"/>
     </row>
-    <row r="752" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="752">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -22957,7 +22971,7 @@
       <c r="Z752" s="3"/>
       <c r="AA752" s="3"/>
     </row>
-    <row r="753" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="753">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -22986,7 +23000,7 @@
       <c r="Z753" s="3"/>
       <c r="AA753" s="3"/>
     </row>
-    <row r="754" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="754">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -23015,7 +23029,7 @@
       <c r="Z754" s="3"/>
       <c r="AA754" s="3"/>
     </row>
-    <row r="755" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="755">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -23044,7 +23058,7 @@
       <c r="Z755" s="3"/>
       <c r="AA755" s="3"/>
     </row>
-    <row r="756" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="756">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -23073,7 +23087,7 @@
       <c r="Z756" s="3"/>
       <c r="AA756" s="3"/>
     </row>
-    <row r="757" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="757">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -23102,7 +23116,7 @@
       <c r="Z757" s="3"/>
       <c r="AA757" s="3"/>
     </row>
-    <row r="758" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="758">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -23131,7 +23145,7 @@
       <c r="Z758" s="3"/>
       <c r="AA758" s="3"/>
     </row>
-    <row r="759" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="759">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -23160,7 +23174,7 @@
       <c r="Z759" s="3"/>
       <c r="AA759" s="3"/>
     </row>
-    <row r="760" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="760">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -23189,7 +23203,7 @@
       <c r="Z760" s="3"/>
       <c r="AA760" s="3"/>
     </row>
-    <row r="761" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="761">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -23218,7 +23232,7 @@
       <c r="Z761" s="3"/>
       <c r="AA761" s="3"/>
     </row>
-    <row r="762" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="762">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -23247,7 +23261,7 @@
       <c r="Z762" s="3"/>
       <c r="AA762" s="3"/>
     </row>
-    <row r="763" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="763">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -23276,7 +23290,7 @@
       <c r="Z763" s="3"/>
       <c r="AA763" s="3"/>
     </row>
-    <row r="764" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="764">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -23305,7 +23319,7 @@
       <c r="Z764" s="3"/>
       <c r="AA764" s="3"/>
     </row>
-    <row r="765" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="765">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -23334,7 +23348,7 @@
       <c r="Z765" s="3"/>
       <c r="AA765" s="3"/>
     </row>
-    <row r="766" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="766">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -23363,7 +23377,7 @@
       <c r="Z766" s="3"/>
       <c r="AA766" s="3"/>
     </row>
-    <row r="767" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="767">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -23392,7 +23406,7 @@
       <c r="Z767" s="3"/>
       <c r="AA767" s="3"/>
     </row>
-    <row r="768" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="768">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -23421,7 +23435,7 @@
       <c r="Z768" s="3"/>
       <c r="AA768" s="3"/>
     </row>
-    <row r="769" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="769">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -23450,7 +23464,7 @@
       <c r="Z769" s="3"/>
       <c r="AA769" s="3"/>
     </row>
-    <row r="770" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="770">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -23479,7 +23493,7 @@
       <c r="Z770" s="3"/>
       <c r="AA770" s="3"/>
     </row>
-    <row r="771" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="771">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -23508,7 +23522,7 @@
       <c r="Z771" s="3"/>
       <c r="AA771" s="3"/>
     </row>
-    <row r="772" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="772">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -23537,7 +23551,7 @@
       <c r="Z772" s="3"/>
       <c r="AA772" s="3"/>
     </row>
-    <row r="773" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="773">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -23566,7 +23580,7 @@
       <c r="Z773" s="3"/>
       <c r="AA773" s="3"/>
     </row>
-    <row r="774" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="774">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -23595,7 +23609,7 @@
       <c r="Z774" s="3"/>
       <c r="AA774" s="3"/>
     </row>
-    <row r="775" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="775">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -23624,7 +23638,7 @@
       <c r="Z775" s="3"/>
       <c r="AA775" s="3"/>
     </row>
-    <row r="776" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="776">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -23653,7 +23667,7 @@
       <c r="Z776" s="3"/>
       <c r="AA776" s="3"/>
     </row>
-    <row r="777" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="777">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -23682,7 +23696,7 @@
       <c r="Z777" s="3"/>
       <c r="AA777" s="3"/>
     </row>
-    <row r="778" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="778">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -23711,7 +23725,7 @@
       <c r="Z778" s="3"/>
       <c r="AA778" s="3"/>
     </row>
-    <row r="779" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="779">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -23740,7 +23754,7 @@
       <c r="Z779" s="3"/>
       <c r="AA779" s="3"/>
     </row>
-    <row r="780" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="780">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -23769,7 +23783,7 @@
       <c r="Z780" s="3"/>
       <c r="AA780" s="3"/>
     </row>
-    <row r="781" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="781">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -23798,7 +23812,7 @@
       <c r="Z781" s="3"/>
       <c r="AA781" s="3"/>
     </row>
-    <row r="782" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="782">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -23827,7 +23841,7 @@
       <c r="Z782" s="3"/>
       <c r="AA782" s="3"/>
     </row>
-    <row r="783" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="783">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -23856,7 +23870,7 @@
       <c r="Z783" s="3"/>
       <c r="AA783" s="3"/>
     </row>
-    <row r="784" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="784">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -23885,7 +23899,7 @@
       <c r="Z784" s="3"/>
       <c r="AA784" s="3"/>
     </row>
-    <row r="785" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="785">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -23914,7 +23928,7 @@
       <c r="Z785" s="3"/>
       <c r="AA785" s="3"/>
     </row>
-    <row r="786" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="786">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -23943,7 +23957,7 @@
       <c r="Z786" s="3"/>
       <c r="AA786" s="3"/>
     </row>
-    <row r="787" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="787">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -23972,7 +23986,7 @@
       <c r="Z787" s="3"/>
       <c r="AA787" s="3"/>
     </row>
-    <row r="788" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="788">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -24001,7 +24015,7 @@
       <c r="Z788" s="3"/>
       <c r="AA788" s="3"/>
     </row>
-    <row r="789" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="789">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -24030,7 +24044,7 @@
       <c r="Z789" s="3"/>
       <c r="AA789" s="3"/>
     </row>
-    <row r="790" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="790">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -24059,7 +24073,7 @@
       <c r="Z790" s="3"/>
       <c r="AA790" s="3"/>
     </row>
-    <row r="791" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="791">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -24088,7 +24102,7 @@
       <c r="Z791" s="3"/>
       <c r="AA791" s="3"/>
     </row>
-    <row r="792" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="792">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -24117,7 +24131,7 @@
       <c r="Z792" s="3"/>
       <c r="AA792" s="3"/>
     </row>
-    <row r="793" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="793">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -24146,7 +24160,7 @@
       <c r="Z793" s="3"/>
       <c r="AA793" s="3"/>
     </row>
-    <row r="794" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="794">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -24175,7 +24189,7 @@
       <c r="Z794" s="3"/>
       <c r="AA794" s="3"/>
     </row>
-    <row r="795" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="795">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -24204,7 +24218,7 @@
       <c r="Z795" s="3"/>
       <c r="AA795" s="3"/>
     </row>
-    <row r="796" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="796">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -24233,7 +24247,7 @@
       <c r="Z796" s="3"/>
       <c r="AA796" s="3"/>
     </row>
-    <row r="797" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="797">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -24262,7 +24276,7 @@
       <c r="Z797" s="3"/>
       <c r="AA797" s="3"/>
     </row>
-    <row r="798" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="798">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -24291,7 +24305,7 @@
       <c r="Z798" s="3"/>
       <c r="AA798" s="3"/>
     </row>
-    <row r="799" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="799">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -24320,7 +24334,7 @@
       <c r="Z799" s="3"/>
       <c r="AA799" s="3"/>
     </row>
-    <row r="800" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="800">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -24349,7 +24363,7 @@
       <c r="Z800" s="3"/>
       <c r="AA800" s="3"/>
     </row>
-    <row r="801" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="801">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -24378,7 +24392,7 @@
       <c r="Z801" s="3"/>
       <c r="AA801" s="3"/>
     </row>
-    <row r="802" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="802">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -24407,7 +24421,7 @@
       <c r="Z802" s="3"/>
       <c r="AA802" s="3"/>
     </row>
-    <row r="803" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="803">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -24436,7 +24450,7 @@
       <c r="Z803" s="3"/>
       <c r="AA803" s="3"/>
     </row>
-    <row r="804" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="804">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -24465,7 +24479,7 @@
       <c r="Z804" s="3"/>
       <c r="AA804" s="3"/>
     </row>
-    <row r="805" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="805">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -24494,7 +24508,7 @@
       <c r="Z805" s="3"/>
       <c r="AA805" s="3"/>
     </row>
-    <row r="806" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="806">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -24523,7 +24537,7 @@
       <c r="Z806" s="3"/>
       <c r="AA806" s="3"/>
     </row>
-    <row r="807" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="807">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -24552,7 +24566,7 @@
       <c r="Z807" s="3"/>
       <c r="AA807" s="3"/>
     </row>
-    <row r="808" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="808">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -24581,7 +24595,7 @@
       <c r="Z808" s="3"/>
       <c r="AA808" s="3"/>
     </row>
-    <row r="809" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="809">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -24610,7 +24624,7 @@
       <c r="Z809" s="3"/>
       <c r="AA809" s="3"/>
     </row>
-    <row r="810" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="810">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -24639,7 +24653,7 @@
       <c r="Z810" s="3"/>
       <c r="AA810" s="3"/>
     </row>
-    <row r="811" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="811">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -24668,7 +24682,7 @@
       <c r="Z811" s="3"/>
       <c r="AA811" s="3"/>
     </row>
-    <row r="812" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="812">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -24697,7 +24711,7 @@
       <c r="Z812" s="3"/>
       <c r="AA812" s="3"/>
     </row>
-    <row r="813" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="813">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -24726,7 +24740,7 @@
       <c r="Z813" s="3"/>
       <c r="AA813" s="3"/>
     </row>
-    <row r="814" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="814">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -24755,7 +24769,7 @@
       <c r="Z814" s="3"/>
       <c r="AA814" s="3"/>
     </row>
-    <row r="815" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="815">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -24784,7 +24798,7 @@
       <c r="Z815" s="3"/>
       <c r="AA815" s="3"/>
     </row>
-    <row r="816" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="816">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -24813,7 +24827,7 @@
       <c r="Z816" s="3"/>
       <c r="AA816" s="3"/>
     </row>
-    <row r="817" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="817">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -24842,7 +24856,7 @@
       <c r="Z817" s="3"/>
       <c r="AA817" s="3"/>
     </row>
-    <row r="818" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="818">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -24871,7 +24885,7 @@
       <c r="Z818" s="3"/>
       <c r="AA818" s="3"/>
     </row>
-    <row r="819" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="819">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -24900,7 +24914,7 @@
       <c r="Z819" s="3"/>
       <c r="AA819" s="3"/>
     </row>
-    <row r="820" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="820">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -24929,7 +24943,7 @@
       <c r="Z820" s="3"/>
       <c r="AA820" s="3"/>
     </row>
-    <row r="821" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="821">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -24958,7 +24972,7 @@
       <c r="Z821" s="3"/>
       <c r="AA821" s="3"/>
     </row>
-    <row r="822" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="822">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -24987,7 +25001,7 @@
       <c r="Z822" s="3"/>
       <c r="AA822" s="3"/>
     </row>
-    <row r="823" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="823">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -25016,7 +25030,7 @@
       <c r="Z823" s="3"/>
       <c r="AA823" s="3"/>
     </row>
-    <row r="824" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="824">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -25045,7 +25059,7 @@
       <c r="Z824" s="3"/>
       <c r="AA824" s="3"/>
     </row>
-    <row r="825" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="825">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -25074,7 +25088,7 @@
       <c r="Z825" s="3"/>
       <c r="AA825" s="3"/>
     </row>
-    <row r="826" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="826">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -25103,7 +25117,7 @@
       <c r="Z826" s="3"/>
       <c r="AA826" s="3"/>
     </row>
-    <row r="827" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="827">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -25132,7 +25146,7 @@
       <c r="Z827" s="3"/>
       <c r="AA827" s="3"/>
     </row>
-    <row r="828" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="828">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -25161,7 +25175,7 @@
       <c r="Z828" s="3"/>
       <c r="AA828" s="3"/>
     </row>
-    <row r="829" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="829">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -25190,7 +25204,7 @@
       <c r="Z829" s="3"/>
       <c r="AA829" s="3"/>
     </row>
-    <row r="830" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="830">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -25219,7 +25233,7 @@
       <c r="Z830" s="3"/>
       <c r="AA830" s="3"/>
     </row>
-    <row r="831" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="831">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -25248,7 +25262,7 @@
       <c r="Z831" s="3"/>
       <c r="AA831" s="3"/>
     </row>
-    <row r="832" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="832">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -25277,7 +25291,7 @@
       <c r="Z832" s="3"/>
       <c r="AA832" s="3"/>
     </row>
-    <row r="833" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="833">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -25306,7 +25320,7 @@
       <c r="Z833" s="3"/>
       <c r="AA833" s="3"/>
     </row>
-    <row r="834" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="834">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -25335,7 +25349,7 @@
       <c r="Z834" s="3"/>
       <c r="AA834" s="3"/>
     </row>
-    <row r="835" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="835">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -25364,7 +25378,7 @@
       <c r="Z835" s="3"/>
       <c r="AA835" s="3"/>
     </row>
-    <row r="836" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="836">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -25393,7 +25407,7 @@
       <c r="Z836" s="3"/>
       <c r="AA836" s="3"/>
     </row>
-    <row r="837" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="837">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -25422,7 +25436,7 @@
       <c r="Z837" s="3"/>
       <c r="AA837" s="3"/>
     </row>
-    <row r="838" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="838">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -25451,7 +25465,7 @@
       <c r="Z838" s="3"/>
       <c r="AA838" s="3"/>
     </row>
-    <row r="839" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="839">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -25480,7 +25494,7 @@
       <c r="Z839" s="3"/>
       <c r="AA839" s="3"/>
     </row>
-    <row r="840" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="840">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -25509,7 +25523,7 @@
       <c r="Z840" s="3"/>
       <c r="AA840" s="3"/>
     </row>
-    <row r="841" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="841">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -25538,7 +25552,7 @@
       <c r="Z841" s="3"/>
       <c r="AA841" s="3"/>
     </row>
-    <row r="842" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="842">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -25567,7 +25581,7 @@
       <c r="Z842" s="3"/>
       <c r="AA842" s="3"/>
     </row>
-    <row r="843" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="843">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -25596,7 +25610,7 @@
       <c r="Z843" s="3"/>
       <c r="AA843" s="3"/>
     </row>
-    <row r="844" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="844">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -25625,7 +25639,7 @@
       <c r="Z844" s="3"/>
       <c r="AA844" s="3"/>
     </row>
-    <row r="845" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="845">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -25654,7 +25668,7 @@
       <c r="Z845" s="3"/>
       <c r="AA845" s="3"/>
     </row>
-    <row r="846" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="846">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -25683,7 +25697,7 @@
       <c r="Z846" s="3"/>
       <c r="AA846" s="3"/>
     </row>
-    <row r="847" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="847">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -25712,7 +25726,7 @@
       <c r="Z847" s="3"/>
       <c r="AA847" s="3"/>
     </row>
-    <row r="848" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="848">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -25741,7 +25755,7 @@
       <c r="Z848" s="3"/>
       <c r="AA848" s="3"/>
     </row>
-    <row r="849" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="849">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -25770,7 +25784,7 @@
       <c r="Z849" s="3"/>
       <c r="AA849" s="3"/>
     </row>
-    <row r="850" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="850">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -25799,7 +25813,7 @@
       <c r="Z850" s="3"/>
       <c r="AA850" s="3"/>
     </row>
-    <row r="851" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="851">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -25828,7 +25842,7 @@
       <c r="Z851" s="3"/>
       <c r="AA851" s="3"/>
     </row>
-    <row r="852" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="852">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -25857,7 +25871,7 @@
       <c r="Z852" s="3"/>
       <c r="AA852" s="3"/>
     </row>
-    <row r="853" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="853">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -25886,7 +25900,7 @@
       <c r="Z853" s="3"/>
       <c r="AA853" s="3"/>
     </row>
-    <row r="854" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="854">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -25915,7 +25929,7 @@
       <c r="Z854" s="3"/>
       <c r="AA854" s="3"/>
     </row>
-    <row r="855" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="855">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -25944,7 +25958,7 @@
       <c r="Z855" s="3"/>
       <c r="AA855" s="3"/>
     </row>
-    <row r="856" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="856">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -25973,7 +25987,7 @@
       <c r="Z856" s="3"/>
       <c r="AA856" s="3"/>
     </row>
-    <row r="857" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="857">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -26002,7 +26016,7 @@
       <c r="Z857" s="3"/>
       <c r="AA857" s="3"/>
     </row>
-    <row r="858" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="858">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -26031,7 +26045,7 @@
       <c r="Z858" s="3"/>
       <c r="AA858" s="3"/>
     </row>
-    <row r="859" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="859">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -26060,7 +26074,7 @@
       <c r="Z859" s="3"/>
       <c r="AA859" s="3"/>
     </row>
-    <row r="860" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="860">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -26089,7 +26103,7 @@
       <c r="Z860" s="3"/>
       <c r="AA860" s="3"/>
     </row>
-    <row r="861" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="861">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -26118,7 +26132,7 @@
       <c r="Z861" s="3"/>
       <c r="AA861" s="3"/>
     </row>
-    <row r="862" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="862">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -26147,7 +26161,7 @@
       <c r="Z862" s="3"/>
       <c r="AA862" s="3"/>
     </row>
-    <row r="863" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="863">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -26176,7 +26190,7 @@
       <c r="Z863" s="3"/>
       <c r="AA863" s="3"/>
     </row>
-    <row r="864" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="864">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -26205,7 +26219,7 @@
       <c r="Z864" s="3"/>
       <c r="AA864" s="3"/>
     </row>
-    <row r="865" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="865">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -26234,7 +26248,7 @@
       <c r="Z865" s="3"/>
       <c r="AA865" s="3"/>
     </row>
-    <row r="866" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="866">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -26263,7 +26277,7 @@
       <c r="Z866" s="3"/>
       <c r="AA866" s="3"/>
     </row>
-    <row r="867" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="867">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -26292,7 +26306,7 @@
       <c r="Z867" s="3"/>
       <c r="AA867" s="3"/>
     </row>
-    <row r="868" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="868">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -26321,7 +26335,7 @@
       <c r="Z868" s="3"/>
       <c r="AA868" s="3"/>
     </row>
-    <row r="869" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="869">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -26350,7 +26364,7 @@
       <c r="Z869" s="3"/>
       <c r="AA869" s="3"/>
     </row>
-    <row r="870" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="870">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -26379,7 +26393,7 @@
       <c r="Z870" s="3"/>
       <c r="AA870" s="3"/>
     </row>
-    <row r="871" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="871">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -26408,7 +26422,7 @@
       <c r="Z871" s="3"/>
       <c r="AA871" s="3"/>
     </row>
-    <row r="872" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="872">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -26437,7 +26451,7 @@
       <c r="Z872" s="3"/>
       <c r="AA872" s="3"/>
     </row>
-    <row r="873" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="873">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -26466,7 +26480,7 @@
       <c r="Z873" s="3"/>
       <c r="AA873" s="3"/>
     </row>
-    <row r="874" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="874">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -26495,7 +26509,7 @@
       <c r="Z874" s="3"/>
       <c r="AA874" s="3"/>
     </row>
-    <row r="875" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="875">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -26524,7 +26538,7 @@
       <c r="Z875" s="3"/>
       <c r="AA875" s="3"/>
     </row>
-    <row r="876" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="876">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -26553,7 +26567,7 @@
       <c r="Z876" s="3"/>
       <c r="AA876" s="3"/>
     </row>
-    <row r="877" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="877">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -26582,7 +26596,7 @@
       <c r="Z877" s="3"/>
       <c r="AA877" s="3"/>
     </row>
-    <row r="878" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="878">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -26611,7 +26625,7 @@
       <c r="Z878" s="3"/>
       <c r="AA878" s="3"/>
     </row>
-    <row r="879" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="879">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -26640,7 +26654,7 @@
       <c r="Z879" s="3"/>
       <c r="AA879" s="3"/>
     </row>
-    <row r="880" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="880">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -26669,7 +26683,7 @@
       <c r="Z880" s="3"/>
       <c r="AA880" s="3"/>
     </row>
-    <row r="881" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="881">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -26698,7 +26712,7 @@
       <c r="Z881" s="3"/>
       <c r="AA881" s="3"/>
     </row>
-    <row r="882" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="882">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -26727,7 +26741,7 @@
       <c r="Z882" s="3"/>
       <c r="AA882" s="3"/>
     </row>
-    <row r="883" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="883">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -26756,7 +26770,7 @@
       <c r="Z883" s="3"/>
       <c r="AA883" s="3"/>
     </row>
-    <row r="884" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="884">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -26785,7 +26799,7 @@
       <c r="Z884" s="3"/>
       <c r="AA884" s="3"/>
     </row>
-    <row r="885" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="885">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -26814,7 +26828,7 @@
       <c r="Z885" s="3"/>
       <c r="AA885" s="3"/>
     </row>
-    <row r="886" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="886">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -26843,7 +26857,7 @@
       <c r="Z886" s="3"/>
       <c r="AA886" s="3"/>
     </row>
-    <row r="887" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="887">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -26872,7 +26886,7 @@
       <c r="Z887" s="3"/>
       <c r="AA887" s="3"/>
     </row>
-    <row r="888" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="888">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -26901,7 +26915,7 @@
       <c r="Z888" s="3"/>
       <c r="AA888" s="3"/>
     </row>
-    <row r="889" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="889">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -26930,7 +26944,7 @@
       <c r="Z889" s="3"/>
       <c r="AA889" s="3"/>
     </row>
-    <row r="890" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="890">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -26959,7 +26973,7 @@
       <c r="Z890" s="3"/>
       <c r="AA890" s="3"/>
     </row>
-    <row r="891" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="891">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -26988,7 +27002,7 @@
       <c r="Z891" s="3"/>
       <c r="AA891" s="3"/>
     </row>
-    <row r="892" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="892">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -27017,7 +27031,7 @@
       <c r="Z892" s="3"/>
       <c r="AA892" s="3"/>
     </row>
-    <row r="893" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="893">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -27046,7 +27060,7 @@
       <c r="Z893" s="3"/>
       <c r="AA893" s="3"/>
     </row>
-    <row r="894" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="894">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -27075,7 +27089,7 @@
       <c r="Z894" s="3"/>
       <c r="AA894" s="3"/>
     </row>
-    <row r="895" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="895">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -27104,7 +27118,7 @@
       <c r="Z895" s="3"/>
       <c r="AA895" s="3"/>
     </row>
-    <row r="896" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="896">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -27133,7 +27147,7 @@
       <c r="Z896" s="3"/>
       <c r="AA896" s="3"/>
     </row>
-    <row r="897" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="897">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -27162,7 +27176,7 @@
       <c r="Z897" s="3"/>
       <c r="AA897" s="3"/>
     </row>
-    <row r="898" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="898">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -27191,7 +27205,7 @@
       <c r="Z898" s="3"/>
       <c r="AA898" s="3"/>
     </row>
-    <row r="899" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="899">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -27220,7 +27234,7 @@
       <c r="Z899" s="3"/>
       <c r="AA899" s="3"/>
     </row>
-    <row r="900" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="900">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -27249,7 +27263,7 @@
       <c r="Z900" s="3"/>
       <c r="AA900" s="3"/>
     </row>
-    <row r="901" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="901">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -27278,7 +27292,7 @@
       <c r="Z901" s="3"/>
       <c r="AA901" s="3"/>
     </row>
-    <row r="902" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="902">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -27307,7 +27321,7 @@
       <c r="Z902" s="3"/>
       <c r="AA902" s="3"/>
     </row>
-    <row r="903" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="903">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -27336,7 +27350,7 @@
       <c r="Z903" s="3"/>
       <c r="AA903" s="3"/>
     </row>
-    <row r="904" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="904">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -27365,7 +27379,7 @@
       <c r="Z904" s="3"/>
       <c r="AA904" s="3"/>
     </row>
-    <row r="905" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="905">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -27394,7 +27408,7 @@
       <c r="Z905" s="3"/>
       <c r="AA905" s="3"/>
     </row>
-    <row r="906" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="906">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -27423,7 +27437,7 @@
       <c r="Z906" s="3"/>
       <c r="AA906" s="3"/>
     </row>
-    <row r="907" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="907">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -27452,7 +27466,7 @@
       <c r="Z907" s="3"/>
       <c r="AA907" s="3"/>
     </row>
-    <row r="908" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="908">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -27481,7 +27495,7 @@
       <c r="Z908" s="3"/>
       <c r="AA908" s="3"/>
     </row>
-    <row r="909" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="909">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -27510,7 +27524,7 @@
       <c r="Z909" s="3"/>
       <c r="AA909" s="3"/>
     </row>
-    <row r="910" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="910">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -27539,7 +27553,7 @@
       <c r="Z910" s="3"/>
       <c r="AA910" s="3"/>
     </row>
-    <row r="911" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="911">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -27568,7 +27582,7 @@
       <c r="Z911" s="3"/>
       <c r="AA911" s="3"/>
     </row>
-    <row r="912" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="912">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -27597,7 +27611,7 @@
       <c r="Z912" s="3"/>
       <c r="AA912" s="3"/>
     </row>
-    <row r="913" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="913">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -27626,7 +27640,7 @@
       <c r="Z913" s="3"/>
       <c r="AA913" s="3"/>
     </row>
-    <row r="914" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="914">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -27655,7 +27669,7 @@
       <c r="Z914" s="3"/>
       <c r="AA914" s="3"/>
     </row>
-    <row r="915" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="915">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -27684,7 +27698,7 @@
       <c r="Z915" s="3"/>
       <c r="AA915" s="3"/>
     </row>
-    <row r="916" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="916">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -27713,7 +27727,7 @@
       <c r="Z916" s="3"/>
       <c r="AA916" s="3"/>
     </row>
-    <row r="917" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="917">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -27742,7 +27756,7 @@
       <c r="Z917" s="3"/>
       <c r="AA917" s="3"/>
     </row>
-    <row r="918" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="918">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -27771,7 +27785,7 @@
       <c r="Z918" s="3"/>
       <c r="AA918" s="3"/>
     </row>
-    <row r="919" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="919">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -27800,7 +27814,7 @@
       <c r="Z919" s="3"/>
       <c r="AA919" s="3"/>
     </row>
-    <row r="920" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="920">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -27829,7 +27843,7 @@
       <c r="Z920" s="3"/>
       <c r="AA920" s="3"/>
     </row>
-    <row r="921" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="921">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -27858,7 +27872,7 @@
       <c r="Z921" s="3"/>
       <c r="AA921" s="3"/>
     </row>
-    <row r="922" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="922">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -27887,7 +27901,7 @@
       <c r="Z922" s="3"/>
       <c r="AA922" s="3"/>
     </row>
-    <row r="923" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="923">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -27916,7 +27930,7 @@
       <c r="Z923" s="3"/>
       <c r="AA923" s="3"/>
     </row>
-    <row r="924" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="924">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -27945,7 +27959,7 @@
       <c r="Z924" s="3"/>
       <c r="AA924" s="3"/>
     </row>
-    <row r="925" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="925">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -27974,7 +27988,7 @@
       <c r="Z925" s="3"/>
       <c r="AA925" s="3"/>
     </row>
-    <row r="926" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="926">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -28003,7 +28017,7 @@
       <c r="Z926" s="3"/>
       <c r="AA926" s="3"/>
     </row>
-    <row r="927" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="927">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -28032,7 +28046,7 @@
       <c r="Z927" s="3"/>
       <c r="AA927" s="3"/>
     </row>
-    <row r="928" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="928">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -28061,7 +28075,7 @@
       <c r="Z928" s="3"/>
       <c r="AA928" s="3"/>
     </row>
-    <row r="929" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="929">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -28090,7 +28104,7 @@
       <c r="Z929" s="3"/>
       <c r="AA929" s="3"/>
     </row>
-    <row r="930" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="930">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -28119,7 +28133,7 @@
       <c r="Z930" s="3"/>
       <c r="AA930" s="3"/>
     </row>
-    <row r="931" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="931">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -28148,7 +28162,7 @@
       <c r="Z931" s="3"/>
       <c r="AA931" s="3"/>
     </row>
-    <row r="932" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="932">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -28177,7 +28191,7 @@
       <c r="Z932" s="3"/>
       <c r="AA932" s="3"/>
     </row>
-    <row r="933" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="933">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -28206,7 +28220,7 @@
       <c r="Z933" s="3"/>
       <c r="AA933" s="3"/>
     </row>
-    <row r="934" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="934">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -28235,7 +28249,7 @@
       <c r="Z934" s="3"/>
       <c r="AA934" s="3"/>
     </row>
-    <row r="935" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="935">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -28264,7 +28278,7 @@
       <c r="Z935" s="3"/>
       <c r="AA935" s="3"/>
     </row>
-    <row r="936" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="936">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -28293,7 +28307,7 @@
       <c r="Z936" s="3"/>
       <c r="AA936" s="3"/>
     </row>
-    <row r="937" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="937">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -28322,7 +28336,7 @@
       <c r="Z937" s="3"/>
       <c r="AA937" s="3"/>
     </row>
-    <row r="938" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="938">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -28351,7 +28365,7 @@
       <c r="Z938" s="3"/>
       <c r="AA938" s="3"/>
     </row>
-    <row r="939" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="939">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -28380,7 +28394,7 @@
       <c r="Z939" s="3"/>
       <c r="AA939" s="3"/>
     </row>
-    <row r="940" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="940">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -28409,7 +28423,7 @@
       <c r="Z940" s="3"/>
       <c r="AA940" s="3"/>
     </row>
-    <row r="941" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="941">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -28438,7 +28452,7 @@
       <c r="Z941" s="3"/>
       <c r="AA941" s="3"/>
     </row>
-    <row r="942" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="942">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -28467,7 +28481,7 @@
       <c r="Z942" s="3"/>
       <c r="AA942" s="3"/>
     </row>
-    <row r="943" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="943">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -28496,7 +28510,7 @@
       <c r="Z943" s="3"/>
       <c r="AA943" s="3"/>
     </row>
-    <row r="944" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="944">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -28525,7 +28539,7 @@
       <c r="Z944" s="3"/>
       <c r="AA944" s="3"/>
     </row>
-    <row r="945" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="945">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -28554,7 +28568,7 @@
       <c r="Z945" s="3"/>
       <c r="AA945" s="3"/>
     </row>
-    <row r="946" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="946">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -28583,7 +28597,7 @@
       <c r="Z946" s="3"/>
       <c r="AA946" s="3"/>
     </row>
-    <row r="947" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="947">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -28612,7 +28626,7 @@
       <c r="Z947" s="3"/>
       <c r="AA947" s="3"/>
     </row>
-    <row r="948" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="948">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -28641,7 +28655,7 @@
       <c r="Z948" s="3"/>
       <c r="AA948" s="3"/>
     </row>
-    <row r="949" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="949">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -28670,7 +28684,7 @@
       <c r="Z949" s="3"/>
       <c r="AA949" s="3"/>
     </row>
-    <row r="950" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="950">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -28699,7 +28713,7 @@
       <c r="Z950" s="3"/>
       <c r="AA950" s="3"/>
     </row>
-    <row r="951" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="951">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -28728,7 +28742,7 @@
       <c r="Z951" s="3"/>
       <c r="AA951" s="3"/>
     </row>
-    <row r="952" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="952">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -28757,7 +28771,7 @@
       <c r="Z952" s="3"/>
       <c r="AA952" s="3"/>
     </row>
-    <row r="953" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="953">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -28786,7 +28800,7 @@
       <c r="Z953" s="3"/>
       <c r="AA953" s="3"/>
     </row>
-    <row r="954" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="954">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -28816,7 +28830,6 @@
       <c r="AA954" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Week_7/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_7/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t>Week_1</t>
   </si>
@@ -198,6 +198,9 @@
   <si>
     <t>Revised User Testing Report</t>
   </si>
+  <si>
+    <t>Add Doctors Pages</t>
+  </si>
 </sst>
 </file>
 
@@ -350,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -533,6 +536,13 @@
     </xf>
     <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -3509,9 +3519,15 @@
     </row>
     <row r="82">
       <c r="A82" s="63"/>
-      <c r="B82" s="63"/>
-      <c r="C82" s="63"/>
-      <c r="D82" s="63"/>
+      <c r="B82" s="64" t="s">
+        <v>62</v>
+      </c>
+      <c r="C82" s="60">
+        <v>46083.0</v>
+      </c>
+      <c r="D82" s="65">
+        <v>3.75</v>
+      </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -3537,15 +3553,10 @@
       <c r="AA82" s="3"/>
     </row>
     <row r="83">
-      <c r="A83" s="64"/>
-      <c r="B83" s="65" t="s">
-        <v>15</v>
-      </c>
+      <c r="A83" s="66"/>
+      <c r="B83" s="66"/>
       <c r="C83" s="66"/>
-      <c r="D83" s="58">
-        <f>sum(D77:D81)</f>
-        <v>10.6</v>
-      </c>
+      <c r="D83" s="66"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -3571,10 +3582,15 @@
       <c r="AA83" s="3"/>
     </row>
     <row r="84">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
+      <c r="A84" s="67"/>
+      <c r="B84" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="69"/>
+      <c r="D84" s="58">
+        <f>sum(D77:D82)</f>
+        <v>14.35</v>
+      </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -28829,6 +28845,35 @@
       <c r="Z954" s="3"/>
       <c r="AA954" s="3"/>
     </row>
+    <row r="955">
+      <c r="A955" s="3"/>
+      <c r="B955" s="3"/>
+      <c r="C955" s="3"/>
+      <c r="D955" s="3"/>
+      <c r="E955" s="3"/>
+      <c r="F955" s="3"/>
+      <c r="G955" s="3"/>
+      <c r="H955" s="3"/>
+      <c r="I955" s="3"/>
+      <c r="J955" s="3"/>
+      <c r="K955" s="3"/>
+      <c r="L955" s="3"/>
+      <c r="M955" s="3"/>
+      <c r="N955" s="3"/>
+      <c r="O955" s="3"/>
+      <c r="P955" s="3"/>
+      <c r="Q955" s="3"/>
+      <c r="R955" s="3"/>
+      <c r="S955" s="3"/>
+      <c r="T955" s="3"/>
+      <c r="U955" s="3"/>
+      <c r="V955" s="3"/>
+      <c r="W955" s="3"/>
+      <c r="X955" s="3"/>
+      <c r="Y955" s="3"/>
+      <c r="Z955" s="3"/>
+      <c r="AA955" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Week_7/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_7/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="67">
   <si>
     <t>Week_1</t>
   </si>
@@ -201,6 +201,18 @@
   <si>
     <t>Add Doctors Pages</t>
   </si>
+  <si>
+    <t>Mentor Meeting</t>
+  </si>
+  <si>
+    <t>Mentor Meeting Thank you email</t>
+  </si>
+  <si>
+    <t>Mentor meeting Notes for Bernie</t>
+  </si>
+  <si>
+    <t>Week_8</t>
+  </si>
 </sst>
 </file>
 
@@ -353,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="77">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -554,6 +566,23 @@
     <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3553,10 +3582,16 @@
       <c r="AA82" s="3"/>
     </row>
     <row r="83">
-      <c r="A83" s="66"/>
-      <c r="B83" s="66"/>
-      <c r="C83" s="66"/>
-      <c r="D83" s="66"/>
+      <c r="A83" s="63"/>
+      <c r="B83" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="C83" s="60">
+        <v>46085.0</v>
+      </c>
+      <c r="D83" s="65">
+        <v>0.75</v>
+      </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -3582,14 +3617,15 @@
       <c r="AA83" s="3"/>
     </row>
     <row r="84">
-      <c r="A84" s="67"/>
-      <c r="B84" s="68" t="s">
-        <v>15</v>
+      <c r="A84" s="63"/>
+      <c r="B84" s="64" t="s">
+        <v>64</v>
       </c>
-      <c r="C84" s="69"/>
-      <c r="D84" s="58">
-        <f>sum(D77:D82)</f>
-        <v>14.35</v>
+      <c r="C84" s="60">
+        <v>46085.0</v>
+      </c>
+      <c r="D84" s="65">
+        <v>0.25</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -3616,10 +3652,16 @@
       <c r="AA84" s="3"/>
     </row>
     <row r="85">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
+      <c r="A85" s="63"/>
+      <c r="B85" s="64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C85" s="60">
+        <v>46085.0</v>
+      </c>
+      <c r="D85" s="65">
+        <v>0.5</v>
+      </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -3645,10 +3687,10 @@
       <c r="AA85" s="3"/>
     </row>
     <row r="86">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
+      <c r="A86" s="66"/>
+      <c r="B86" s="66"/>
+      <c r="C86" s="66"/>
+      <c r="D86" s="66"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -3674,10 +3716,15 @@
       <c r="AA86" s="3"/>
     </row>
     <row r="87">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
+      <c r="A87" s="67"/>
+      <c r="B87" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="69"/>
+      <c r="D87" s="58">
+        <f>sum(D77:D82)</f>
+        <v>14.35</v>
+      </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -3761,10 +3808,18 @@
       <c r="AA89" s="3"/>
     </row>
     <row r="90">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
+      <c r="A90" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B90" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="40" t="s">
+        <v>3</v>
+      </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
@@ -3790,10 +3845,10 @@
       <c r="AA90" s="3"/>
     </row>
     <row r="91">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
+      <c r="A91" s="41"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="71"/>
+      <c r="D91" s="44"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
@@ -3819,10 +3874,10 @@
       <c r="AA91" s="3"/>
     </row>
     <row r="92">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
+      <c r="A92" s="41"/>
+      <c r="B92" s="72"/>
+      <c r="C92" s="71"/>
+      <c r="D92" s="44"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
@@ -3848,10 +3903,10 @@
       <c r="AA92" s="3"/>
     </row>
     <row r="93">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
+      <c r="A93" s="41"/>
+      <c r="B93" s="72"/>
+      <c r="C93" s="71"/>
+      <c r="D93" s="44"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
@@ -3877,10 +3932,10 @@
       <c r="AA93" s="3"/>
     </row>
     <row r="94">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
+      <c r="A94" s="41"/>
+      <c r="B94" s="72"/>
+      <c r="C94" s="71"/>
+      <c r="D94" s="44"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -3906,10 +3961,10 @@
       <c r="AA94" s="3"/>
     </row>
     <row r="95">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
+      <c r="A95" s="41"/>
+      <c r="B95" s="70"/>
+      <c r="C95" s="71"/>
+      <c r="D95" s="44"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -3935,10 +3990,10 @@
       <c r="AA95" s="3"/>
     </row>
     <row r="96">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
+      <c r="A96" s="73"/>
+      <c r="B96" s="74"/>
+      <c r="C96" s="71"/>
+      <c r="D96" s="75"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -3964,10 +4019,10 @@
       <c r="AA96" s="3"/>
     </row>
     <row r="97">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
+      <c r="A97" s="73"/>
+      <c r="B97" s="74"/>
+      <c r="C97" s="71"/>
+      <c r="D97" s="75"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -3993,10 +4048,10 @@
       <c r="AA97" s="3"/>
     </row>
     <row r="98">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
+      <c r="A98" s="73"/>
+      <c r="B98" s="74"/>
+      <c r="C98" s="71"/>
+      <c r="D98" s="75"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -4022,10 +4077,10 @@
       <c r="AA98" s="3"/>
     </row>
     <row r="99">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
+      <c r="A99" s="73"/>
+      <c r="B99" s="74"/>
+      <c r="C99" s="71"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -4051,10 +4106,10 @@
       <c r="AA99" s="3"/>
     </row>
     <row r="100">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
+      <c r="A100" s="76"/>
+      <c r="B100" s="76"/>
+      <c r="C100" s="76"/>
+      <c r="D100" s="76"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -4080,10 +4135,15 @@
       <c r="AA100" s="3"/>
     </row>
     <row r="101">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
+      <c r="A101" s="45"/>
+      <c r="B101" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="47"/>
+      <c r="D101" s="41">
+        <f>sum(D91:D96)</f>
+        <v>0</v>
+      </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -28874,6 +28934,93 @@
       <c r="Z955" s="3"/>
       <c r="AA955" s="3"/>
     </row>
+    <row r="956">
+      <c r="A956" s="3"/>
+      <c r="B956" s="3"/>
+      <c r="C956" s="3"/>
+      <c r="D956" s="3"/>
+      <c r="E956" s="3"/>
+      <c r="F956" s="3"/>
+      <c r="G956" s="3"/>
+      <c r="H956" s="3"/>
+      <c r="I956" s="3"/>
+      <c r="J956" s="3"/>
+      <c r="K956" s="3"/>
+      <c r="L956" s="3"/>
+      <c r="M956" s="3"/>
+      <c r="N956" s="3"/>
+      <c r="O956" s="3"/>
+      <c r="P956" s="3"/>
+      <c r="Q956" s="3"/>
+      <c r="R956" s="3"/>
+      <c r="S956" s="3"/>
+      <c r="T956" s="3"/>
+      <c r="U956" s="3"/>
+      <c r="V956" s="3"/>
+      <c r="W956" s="3"/>
+      <c r="X956" s="3"/>
+      <c r="Y956" s="3"/>
+      <c r="Z956" s="3"/>
+      <c r="AA956" s="3"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="3"/>
+      <c r="B957" s="3"/>
+      <c r="C957" s="3"/>
+      <c r="D957" s="3"/>
+      <c r="E957" s="3"/>
+      <c r="F957" s="3"/>
+      <c r="G957" s="3"/>
+      <c r="H957" s="3"/>
+      <c r="I957" s="3"/>
+      <c r="J957" s="3"/>
+      <c r="K957" s="3"/>
+      <c r="L957" s="3"/>
+      <c r="M957" s="3"/>
+      <c r="N957" s="3"/>
+      <c r="O957" s="3"/>
+      <c r="P957" s="3"/>
+      <c r="Q957" s="3"/>
+      <c r="R957" s="3"/>
+      <c r="S957" s="3"/>
+      <c r="T957" s="3"/>
+      <c r="U957" s="3"/>
+      <c r="V957" s="3"/>
+      <c r="W957" s="3"/>
+      <c r="X957" s="3"/>
+      <c r="Y957" s="3"/>
+      <c r="Z957" s="3"/>
+      <c r="AA957" s="3"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="3"/>
+      <c r="B958" s="3"/>
+      <c r="C958" s="3"/>
+      <c r="D958" s="3"/>
+      <c r="E958" s="3"/>
+      <c r="F958" s="3"/>
+      <c r="G958" s="3"/>
+      <c r="H958" s="3"/>
+      <c r="I958" s="3"/>
+      <c r="J958" s="3"/>
+      <c r="K958" s="3"/>
+      <c r="L958" s="3"/>
+      <c r="M958" s="3"/>
+      <c r="N958" s="3"/>
+      <c r="O958" s="3"/>
+      <c r="P958" s="3"/>
+      <c r="Q958" s="3"/>
+      <c r="R958" s="3"/>
+      <c r="S958" s="3"/>
+      <c r="T958" s="3"/>
+      <c r="U958" s="3"/>
+      <c r="V958" s="3"/>
+      <c r="W958" s="3"/>
+      <c r="X958" s="3"/>
+      <c r="Y958" s="3"/>
+      <c r="Z958" s="3"/>
+      <c r="AA958" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
